--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2784" uniqueCount="1371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2829" uniqueCount="1398">
   <si>
     <t>검진 예약·접수 관리 프로그램 — 단위시험 목록</t>
   </si>
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 02:23</t>
+    <t>2026-09-15 03:36</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_02_23_42.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_03_36_24.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -3914,6 +3914,24 @@
     <t>빈 화면으로는 조회 한 줄의 칸 폭도 좌우 비율도 볼 수 없다 — 종료일 DateEdit 이 잘린 결함이 실제로 이 캡처에서 드러났다.</t>
   </si>
   <si>
+    <t>DbFixture</t>
+  </si>
+  <si>
+    <t>시험 어셈블리는 병렬로 돌지 않는다</t>
+  </si>
+  <si>
+    <t>시험 어셈블리의 [assembly: Parallelize] 선언 유무</t>
+  </si>
+  <si>
+    <t>이 폴더의 시험은 운영기준 한 행과 시간대 정원을 공유한다. 병렬로 돌면 한 시험이 연 창을 다른 시험이 되돌리고, 그 순간 남은 시험은 다른 제품을 재게 된다. 오늘 MSTest 는 순차이지만 선언 한 줄이면 바뀌고 그 한 줄은 조용하다 — 시험은 여전히 green 이고 무엇이 어긋났는지 아무도 못 본다.</t>
+  </si>
+  <si>
+    <t>어셈블리에 ParallelizeAttribute 가 0건이다.</t>
+  </si>
+  <si>
+    <t>Integration/DbFixture.cs</t>
+  </si>
+  <si>
     <t>PatientRepositoryDb</t>
   </si>
   <si>
@@ -4125,6 +4143,69 @@
   </si>
   <si>
     <t>RS0 결과코드 0, RS1 업무상세·RS2 국가검사·RS3 추가검사·RS5 추가검사구성이 모두 null 이 아니고, RS4 가능한업무가 정확히 5행이다. 예약접수가 0건인 DB 에서는 판정할 것이 없으므로 Inconclusive 로 남기고 PASS 로 세지 않는다.</t>
+  </si>
+  <si>
+    <t>WriteRepositoryDb</t>
+  </si>
+  <si>
+    <t>SP HOL 02 와 SP HOL 04 는 한 행을 심고 고치고 지운다</t>
+  </si>
+  <si>
+    <t>실물 DB — 자체휴무일 저장(SP-HOL-02)의 성공 경로 둘과 삭제(SP-HOL-04)</t>
+  </si>
+  <si>
+    <t>지금 도는 것은 저장의 101 실패 경로뿐이고 그 시험 자신이 「아무것도 쓰지 않는다」고 적는다 — 코드 검증이 잠금·Transaction 앞에서 끝난다. 그래서 등록도 수정도 삭제도 실물에서 한 번도 쓰인 적이 없다. 셋을 한 시험에 이은 것은 심는 것이 곧 지우는 준비이기 때문이고, 삭제가 요구하는 행버전은 저장이 준 BINARY(8) 을 그대로 되돌려 보내야만 맞는다 (05 §16.3).</t>
+  </si>
+  <si>
+    <t>CREATE_HOLIDAY 가 결과코드 0 에 RS1 휴무일자·행버전 8바이트를 내고, 목록 조회가 그 날짜를 휴무구분 자체휴무일 1행으로 싣는다. UPDATE_HOLIDAY 가 결과코드 0 에 새 행버전을 내고, 그 행버전으로 삭제하면 결과코드 0 이며 RS1 이 없고(05 §12.8) 목록에서 사라진다.</t>
+  </si>
+  <si>
+    <t>05 §16.3 · 05 §12.8</t>
+  </si>
+  <si>
+    <t>Integration/WriteRepositoryDbTests.cs</t>
+  </si>
+  <si>
+    <t>SP RCP 02 는 접수 뒤 AEX 만 바꾸고 상태를 옮기지 않는다</t>
+  </si>
+  <si>
+    <t>실물 DB — 접수 뒤 추가검사 변경(SP-RCP-02)의 실제 변경 경로와 그 No-op</t>
+  </si>
+  <si>
+    <t>이 SP 도 C# 에서 한 번도 실행된 적이 없고, 그 앞에 RCP 상태 업무가 필요해 예약→접수까지 세우지 않으면 닿지 못한다. 05 §12.2 가 「예약일·시간대·TGT·NEX 를 변경하거나 재평가하지 않는다」로 못박았으므로 DLG-RCP-02 는 AEX 일곱과 동시성 토큰만 보낸다 — 그 좁은 계약이 실물에서도 참인지, 상태가 RCP 로 남는지는 붙어 봐야 안다. 여기서 상태가 옮겨지면 접수한 사람이 목록에서 사라진다.</t>
+  </si>
+  <si>
+    <t>접수완료가 결과코드 0 · 상태 RCP 이고, 상세 RS5 가 선택가능하다고 적은 추가검사 하나를 켜면 결과코드 0 · 상태 RCP 유지 · 행버전이 달라지며, 같은 값을 한 번 더 보내면 결과코드 1 에 행버전이 그대로다.</t>
+  </si>
+  <si>
+    <t>SP RSV 01 은 변경범위 다섯을 계약된 Cardinality 로 낸다</t>
+  </si>
+  <si>
+    <t>실물 DB — 예약가능정보 조회(SP-RSV-01)의 변경범위 다섯과 그 Result Set 형상</t>
+  </si>
+  <si>
+    <t>05 §9.4 가 「무엇이 바뀌었는지 보내지 않는다 — 원하는 상태를 통째로 보내면 DB 가 현재 행과 견주어 잰다」로 정했고, 그 판정에 따라 RS2~RS5 가 서기도 하고 0행이 되기도 한다 (05 §9.11). 화면은 그 형상에 기대어 시간대 칸과 추가검사 칸을 그리므로, 변경범위 하나가 어긋나면 화면이 빈 칸을 「선택지가 없다」로 읽는다. 문서 대조 게이트는 05 를 볼 뿐 DB 를 보지 않아 이 틈을 못 막는다.</t>
+  </si>
+  <si>
+    <t>다섯 호출이 각각 변경범위 ALL·NONE·SLOT·EXTRA·SLOT_EXTRA 를 돌려주고, RS2 시간대정보·RS3 검진대상·RS4 국가검사항목·RS5 추가검사항목의 행수가 05 §9.11 표 그대로다. ALL 은 「0 또는 …」의 0 쪽을 허용하지 않는다 — 새로 만든 수검자이고 창이 열려 있으므로 일정 평가가 가능한 쪽이 참이어야 한다.</t>
+  </si>
+  <si>
+    <t>05 §9.4 · 05 §9.11</t>
+  </si>
+  <si>
+    <t>SP RSV 03 은 AEX 를 바꾸면 새 행버전을 내고 같은 값에는 1 이다</t>
+  </si>
+  <si>
+    <t>실물 DB — 예약 변경(SP-RSV-03)의 AEX 실제 변경 경로와 그 No-op</t>
+  </si>
+  <si>
+    <t>이 SP 는 C# 에서 한 번도 실행된 적이 없다. 05 §11.2 가 「AEX 실제 변경이면 행버전이 자동으로 바뀌고 새 행버전을 반환한다」, 「동일집합이면 UPDATE 없이 결과코드 1 과 기존 행버전」으로 갈랐는데, 그 둘이 뒤섞이면 화면이 낡은 토큰을 쥔 채 다음 저장에서 601 로 막히거나 — 더 나쁘게 — 남의 변경을 덮어쓴다. 행버전은 BINARY(8) 왕복이라 문자열로 바꾸는 순간 조용히 깨진다 (05 §16.3).</t>
+  </si>
+  <si>
+    <t>선택 가능한 추가검사 하나를 켜서 보내면 결과코드 0 · 상태코드 RSV 유지 · 행버전이 달라지고, 그 새 행버전으로 같은 값을 한 번 더 보내면 결과코드 1 에 행버전이 그대로다.</t>
+  </si>
+  <si>
+    <t>05 §11.2 · 05 §16.3</t>
   </si>
 </sst>
 </file>
@@ -4678,13 +4759,13 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4698,13 +4779,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C14" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="D14" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -4753,7 +4834,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K306"/>
+  <dimension ref="A1:K311"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -5215,7 +5296,7 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="s">
         <v>96</v>
@@ -7420,7 +7501,7 @@
         <v>10</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="s">
         <v>300</v>
@@ -8785,7 +8866,7 @@
         <v>10</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115" t="s">
         <v>504</v>
@@ -8820,7 +8901,7 @@
         <v>10</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K116" t="s">
         <v>504</v>
@@ -9940,7 +10021,7 @@
         <v>10</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" t="s">
         <v>656</v>
@@ -10885,7 +10966,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -12110,7 +12191,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>739</v>
+        <v>807</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12320,7 +12401,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12355,7 +12436,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12390,7 +12471,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12425,7 +12506,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12460,7 +12541,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1138</v>
+        <v>899</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12495,7 +12576,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12530,7 +12611,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12565,7 +12646,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1264</v>
+        <v>1187</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12600,7 +12681,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12635,7 +12716,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12670,7 +12751,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12705,7 +12786,7 @@
         <v>10</v>
       </c>
       <c r="J227">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="K227" t="s">
         <v>1004</v>
@@ -12740,7 +12821,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12775,7 +12856,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -12810,7 +12891,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -12845,7 +12926,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="K231" t="s">
         <v>1053</v>
@@ -12880,7 +12961,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="K232" t="s">
         <v>1053</v>
@@ -12915,7 +12996,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="K233" t="s">
         <v>1053</v>
@@ -12950,7 +13031,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="K234" t="s">
         <v>1053</v>
@@ -13055,7 +13136,7 @@
         <v>10</v>
       </c>
       <c r="J237">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="K237" t="s">
         <v>1081</v>
@@ -13160,7 +13241,7 @@
         <v>10</v>
       </c>
       <c r="J240">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="K240" t="s">
         <v>1081</v>
@@ -13195,7 +13276,7 @@
         <v>10</v>
       </c>
       <c r="J241">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="K241" t="s">
         <v>1081</v>
@@ -13230,7 +13311,7 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="K242" t="s">
         <v>1103</v>
@@ -13265,7 +13346,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="K243" t="s">
         <v>1081</v>
@@ -13300,7 +13381,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K244" t="s">
         <v>1103</v>
@@ -13335,7 +13416,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K245" t="s">
         <v>1103</v>
@@ -13440,7 +13521,7 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="K248" t="s">
         <v>1081</v>
@@ -13475,7 +13556,7 @@
         <v>10</v>
       </c>
       <c r="J249">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K249" t="s">
         <v>1081</v>
@@ -13510,7 +13591,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="K250" t="s">
         <v>1081</v>
@@ -13545,7 +13626,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K251" t="s">
         <v>1103</v>
@@ -13580,7 +13661,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="K252" t="s">
         <v>1081</v>
@@ -13615,7 +13696,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K253" t="s">
         <v>1081</v>
@@ -13650,7 +13731,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="K254" t="s">
         <v>1152</v>
@@ -13685,7 +13766,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="K255" t="s">
         <v>1152</v>
@@ -13720,7 +13801,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="K256" t="s">
         <v>1152</v>
@@ -13755,7 +13836,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="K257" t="s">
         <v>1166</v>
@@ -13790,7 +13871,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>106</v>
+        <v>141</v>
       </c>
       <c r="K258" t="s">
         <v>1166</v>
@@ -13825,7 +13906,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="K259" t="s">
         <v>1166</v>
@@ -13860,7 +13941,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="K260" t="s">
         <v>1166</v>
@@ -13895,7 +13976,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K261" t="s">
         <v>1166</v>
@@ -13930,7 +14011,7 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K262" t="s">
         <v>1166</v>
@@ -13965,7 +14046,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K263" t="s">
         <v>1166</v>
@@ -14000,7 +14081,7 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="K264" t="s">
         <v>1166</v>
@@ -14035,7 +14116,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K265" t="s">
         <v>1166</v>
@@ -14140,7 +14221,7 @@
         <v>10</v>
       </c>
       <c r="J268">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="K268" t="s">
         <v>1201</v>
@@ -14210,7 +14291,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K270" t="s">
         <v>1201</v>
@@ -14245,7 +14326,7 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K271" t="s">
         <v>1223</v>
@@ -14280,7 +14361,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="K272" t="s">
         <v>1223</v>
@@ -14315,7 +14396,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="K273" t="s">
         <v>1223</v>
@@ -14350,7 +14431,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K274" t="s">
         <v>1223</v>
@@ -14385,7 +14466,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K275" t="s">
         <v>1223</v>
@@ -14420,7 +14501,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="K276" t="s">
         <v>1223</v>
@@ -14490,7 +14571,7 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="K278" t="s">
         <v>1249</v>
@@ -14525,7 +14606,7 @@
         <v>10</v>
       </c>
       <c r="J279">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K279" t="s">
         <v>1249</v>
@@ -14560,7 +14641,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="K280" t="s">
         <v>1263</v>
@@ -14595,7 +14676,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="K281" t="s">
         <v>1263</v>
@@ -14630,7 +14711,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K282" t="s">
         <v>1263</v>
@@ -14665,7 +14746,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="K283" t="s">
         <v>1263</v>
@@ -14700,7 +14781,7 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="K284" t="s">
         <v>1263</v>
@@ -14735,7 +14816,7 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="K285" t="s">
         <v>1263</v>
@@ -14770,7 +14851,7 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>257</v>
+        <v>234</v>
       </c>
       <c r="K286" t="s">
         <v>1263</v>
@@ -14805,7 +14886,7 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="K287" t="s">
         <v>1263</v>
@@ -14840,7 +14921,7 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="K288" t="s">
         <v>1263</v>
@@ -14875,7 +14956,7 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K289" t="s">
         <v>1263</v>
@@ -14910,7 +14991,7 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K290" t="s">
         <v>1263</v>
@@ -14936,7 +15017,7 @@
         <v>1304</v>
       </c>
       <c r="G291" t="s">
-        <v>626</v>
+        <v>24</v>
       </c>
       <c r="H291">
         <v>1</v>
@@ -14945,7 +15026,7 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K291" t="s">
         <v>1305</v>
@@ -14956,22 +15037,22 @@
         <v>18</v>
       </c>
       <c r="B292" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E292" s="4" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="G292" t="s">
-        <v>1310</v>
+        <v>626</v>
       </c>
       <c r="H292">
         <v>1</v>
@@ -14980,10 +15061,10 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="K292" t="s">
-        <v>1305</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -14991,34 +15072,34 @@
         <v>18</v>
       </c>
       <c r="B293" t="s">
-        <v>1300</v>
+        <v>1306</v>
       </c>
       <c r="C293" s="4" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D293" s="4" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E293" s="4" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F293" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="G293" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H293">
+        <v>1</v>
+      </c>
+      <c r="I293" t="s">
+        <v>10</v>
+      </c>
+      <c r="J293">
+        <v>52</v>
+      </c>
+      <c r="K293" t="s">
         <v>1311</v>
-      </c>
-      <c r="D293" s="4" t="s">
-        <v>1312</v>
-      </c>
-      <c r="E293" s="4" t="s">
-        <v>1313</v>
-      </c>
-      <c r="F293" s="4" t="s">
-        <v>1314</v>
-      </c>
-      <c r="G293" t="s">
-        <v>212</v>
-      </c>
-      <c r="H293">
-        <v>1</v>
-      </c>
-      <c r="I293" t="s">
-        <v>10</v>
-      </c>
-      <c r="J293">
-        <v>5</v>
-      </c>
-      <c r="K293" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -15026,22 +15107,22 @@
         <v>18</v>
       </c>
       <c r="B294" t="s">
-        <v>1315</v>
+        <v>1306</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="E294" s="4" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="G294" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="H294">
         <v>1</v>
@@ -15050,10 +15131,10 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>409</v>
+        <v>4</v>
       </c>
       <c r="K294" t="s">
-        <v>1320</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -15061,19 +15142,19 @@
         <v>18</v>
       </c>
       <c r="B295" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="E295" s="4" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="G295" t="s">
         <v>24</v>
@@ -15085,10 +15166,10 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>3</v>
+        <v>377</v>
       </c>
       <c r="K295" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -15096,19 +15177,19 @@
         <v>18</v>
       </c>
       <c r="B296" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E296" s="4" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="G296" t="s">
         <v>24</v>
@@ -15120,10 +15201,10 @@
         <v>10</v>
       </c>
       <c r="J296">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K296" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -15131,19 +15212,19 @@
         <v>18</v>
       </c>
       <c r="B297" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="E297" s="4" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="F297" s="4" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="G297" t="s">
         <v>24</v>
@@ -15155,10 +15236,10 @@
         <v>10</v>
       </c>
       <c r="J297">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K297" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -15166,19 +15247,19 @@
         <v>18</v>
       </c>
       <c r="B298" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="E298" s="4" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="F298" s="4" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="G298" t="s">
         <v>24</v>
@@ -15193,7 +15274,7 @@
         <v>8</v>
       </c>
       <c r="K298" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -15201,22 +15282,22 @@
         <v>18</v>
       </c>
       <c r="B299" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="E299" s="4" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="G299" t="s">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="H299">
         <v>1</v>
@@ -15225,10 +15306,10 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K299" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -15236,22 +15317,22 @@
         <v>18</v>
       </c>
       <c r="B300" t="s">
-        <v>1315</v>
+        <v>1321</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="E300" s="4" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="G300" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="H300">
         <v>1</v>
@@ -15260,10 +15341,10 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K300" t="s">
-        <v>1320</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -15271,22 +15352,22 @@
         <v>18</v>
       </c>
       <c r="B301" t="s">
-        <v>1345</v>
+        <v>1321</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="E301" s="4" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="G301" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H301">
         <v>1</v>
@@ -15295,10 +15376,10 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K301" t="s">
-        <v>1350</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -15306,22 +15387,22 @@
         <v>18</v>
       </c>
       <c r="B302" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="E302" s="4" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="G302" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="H302">
         <v>1</v>
@@ -15330,10 +15411,10 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K302" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -15341,34 +15422,34 @@
         <v>18</v>
       </c>
       <c r="B303" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="D303" s="4" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E303" s="4" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F303" s="4" t="s">
+        <v>1360</v>
+      </c>
+      <c r="G303" t="s">
+        <v>141</v>
+      </c>
+      <c r="H303">
+        <v>1</v>
+      </c>
+      <c r="I303" t="s">
+        <v>10</v>
+      </c>
+      <c r="J303">
+        <v>7</v>
+      </c>
+      <c r="K303" t="s">
         <v>1356</v>
-      </c>
-      <c r="E303" s="4" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F303" s="4" t="s">
-        <v>1358</v>
-      </c>
-      <c r="G303" t="s">
-        <v>180</v>
-      </c>
-      <c r="H303">
-        <v>1</v>
-      </c>
-      <c r="I303" t="s">
-        <v>10</v>
-      </c>
-      <c r="J303">
-        <v>4</v>
-      </c>
-      <c r="K303" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -15376,19 +15457,19 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E304" s="4" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="G304" t="s">
         <v>180</v>
@@ -15400,10 +15481,10 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K304" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -15411,22 +15492,22 @@
         <v>18</v>
       </c>
       <c r="B305" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="E305" s="4" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="G305" t="s">
-        <v>866</v>
+        <v>180</v>
       </c>
       <c r="H305">
         <v>1</v>
@@ -15438,7 +15519,7 @@
         <v>1</v>
       </c>
       <c r="K305" t="s">
-        <v>1350</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -15446,34 +15527,209 @@
         <v>18</v>
       </c>
       <c r="B306" t="s">
-        <v>1345</v>
+        <v>1351</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="E306" s="4" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="G306" t="s">
+        <v>866</v>
+      </c>
+      <c r="H306">
+        <v>1</v>
+      </c>
+      <c r="I306" t="s">
+        <v>10</v>
+      </c>
+      <c r="J306">
+        <v>1</v>
+      </c>
+      <c r="K306" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>18</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G307" t="s">
         <v>398</v>
       </c>
-      <c r="H306">
-        <v>1</v>
-      </c>
-      <c r="I306" t="s">
-        <v>10</v>
-      </c>
-      <c r="J306">
+      <c r="H307">
+        <v>1</v>
+      </c>
+      <c r="I307" t="s">
+        <v>10</v>
+      </c>
+      <c r="J307">
         <v>3</v>
       </c>
-      <c r="K306" t="s">
-        <v>1350</v>
+      <c r="K307" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>18</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>1379</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>1381</v>
+      </c>
+      <c r="G308" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H308">
+        <v>1</v>
+      </c>
+      <c r="I308" t="s">
+        <v>10</v>
+      </c>
+      <c r="J308">
+        <v>8</v>
+      </c>
+      <c r="K308" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>18</v>
+      </c>
+      <c r="B309" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>1384</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E309" s="4" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G309" t="s">
+        <v>424</v>
+      </c>
+      <c r="H309">
+        <v>1</v>
+      </c>
+      <c r="I309" t="s">
+        <v>10</v>
+      </c>
+      <c r="J309">
+        <v>71</v>
+      </c>
+      <c r="K309" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>18</v>
+      </c>
+      <c r="B310" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>1389</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="G310" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H310">
+        <v>1</v>
+      </c>
+      <c r="I310" t="s">
+        <v>10</v>
+      </c>
+      <c r="J310">
+        <v>26</v>
+      </c>
+      <c r="K310" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>18</v>
+      </c>
+      <c r="B311" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G311" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H311">
+        <v>1</v>
+      </c>
+      <c r="I311" t="s">
+        <v>10</v>
+      </c>
+      <c r="J311">
+        <v>137</v>
+      </c>
+      <c r="K311" t="s">
+        <v>1383</v>
       </c>
     </row>
   </sheetData>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2829" uniqueCount="1398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2865" uniqueCount="1416">
   <si>
     <t>검진 예약·접수 관리 프로그램 — 단위시험 목록</t>
   </si>
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 03:36</t>
+    <t>2026-09-15 05:32</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_03_36_24.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_05_31_50.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -3786,6 +3786,60 @@
   </si>
   <si>
     <t>네 역할이 서로 다른 네 가지 색을 낸다 (같은 색이 하나도 없다).</t>
+  </si>
+  <si>
+    <t>ScenarioCapture</t>
+  </si>
+  <si>
+    <t>S01 등록에서 접수까지를 화면 네 장으로 남긴다</t>
+  </si>
+  <si>
+    <t>S01 정상 업무 흐름 — 등록 → 예약 → 조회 → 접수를 화면으로 네 장</t>
+  </si>
+  <si>
+    <t>브리프 §9 가 화면 측 증빙을 요구한다. 받는 사람은 저장소를 열지 않으므로 「시험이 PASS 했다」는 문장만으로는 업무가 처리되는 것을 볼 수 없다. 한 장짜리 화면 사진도 배치만 보일 뿐 처리를 보이지 못한다 — 같은 조회 조건으로 전·후를 나란히 떠야 「없던 줄이 생겼다 · 상태가 옮겨졌다」가 그림에서 읽힌다.</t>
+  </si>
+  <si>
+    <t>그 수검자 차트번호로 조회하면 예약 전 0행, 예약 후 1행 RSV, 접수 후 1행 RCP 이고 네 장이 전부 10KB 를 넘는 실제 그림이다 (폼이 안 그려지면 파일만 생기고 빈다).</t>
+  </si>
+  <si>
+    <t>Visual/ScenarioCaptureTests.cs</t>
+  </si>
+  <si>
+    <t>S03 예약취소 뒤 화면을 남긴다</t>
+  </si>
+  <si>
+    <t>S03 예약취소 — 취소 뒤 화면 한 장</t>
+  </si>
+  <si>
+    <t>브리프 §4 「예약 정보를 변경하거나 취소하는 경우」다. 취소가 행을 지우는 것이 아니라 상태를 옮기는 것이라는 점이 이 그림의 요점이다 — 줄이 사라졌다면 감사 기록도 함께 사라진 것이고, 그것은 RP-10 위반이다. 그림은 줄이 남아 있고 상태만 바뀐 것을 보인다.</t>
+  </si>
+  <si>
+    <t>취소가 결과코드 0 이고, 그 차트번호 조회가 여전히 1행이며 상태코드가 CNR 이다.</t>
+  </si>
+  <si>
+    <t>S04 재접수가 막힌 뒤 화면을 남긴다</t>
+  </si>
+  <si>
+    <t>S04 재접수 차단 — 이미 접수된 건을 다시 접수한 뒤 화면 한 장</t>
+  </si>
+  <si>
+    <t>브리프 §4 「이미 접수된 예약을 다시 접수하려는 경우」다. 막혔다는 증거는 대화상자 문구가 아니라 아무것도 바뀌지 않았다는 것이다 — 두 번 접수되면 같은 사람이 두 번 온 것으로 집계되고 정원도 두 번 깎인다. 그림은 시도 뒤에도 줄이 하나이고 상태가 그대로임을 보인다.</t>
+  </si>
+  <si>
+    <t>두 번째 접수가 결과코드 502 로 막히고, 그 뒤 조회가 1행 RCP 그대로다.</t>
+  </si>
+  <si>
+    <t>S05 접수취소 뒤 화면을 남긴다</t>
+  </si>
+  <si>
+    <t>S05 접수취소 — 접수 뒤 취소한 화면 한 장</t>
+  </si>
+  <si>
+    <t>브리프 §4 「접수 후 취소가 필요한 경우」다. 접수취소가 예약(RSV)으로 되돌아가지 않고 CNC 로 간다는 것이 이 그림의 요점이다 — 되돌리면 그 사람이 내원했다는 사실이 지워지고 정원 계산과 실적 집계가 어긋난다.</t>
+  </si>
+  <si>
+    <t>접수취소가 결과코드 0 이고, 조회가 1행이며 상태코드가 RSV 가 아니라 CNC 다.</t>
   </si>
   <si>
     <t>ShellCapture</t>
@@ -4739,13 +4793,13 @@
         <v>17</v>
       </c>
       <c r="B12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D12">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4779,13 +4833,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C14" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D14" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -4834,7 +4888,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K311"/>
+  <dimension ref="A1:K315"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -6171,7 +6225,7 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K38" t="s">
         <v>189</v>
@@ -6416,7 +6470,7 @@
         <v>10</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="s">
         <v>219</v>
@@ -6626,7 +6680,7 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="s">
         <v>256</v>
@@ -8901,7 +8955,7 @@
         <v>10</v>
       </c>
       <c r="J116">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K116" t="s">
         <v>504</v>
@@ -9321,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="J128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="s">
         <v>558</v>
@@ -9951,7 +10005,7 @@
         <v>10</v>
       </c>
       <c r="J146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="s">
         <v>656</v>
@@ -10966,7 +11020,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -12191,7 +12245,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>807</v>
+        <v>723</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12401,7 +12455,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12436,7 +12490,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12471,7 +12525,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12506,7 +12560,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>669</v>
+        <v>788</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12541,7 +12595,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>899</v>
+        <v>1010</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12576,7 +12630,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12611,7 +12665,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12646,7 +12700,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1187</v>
+        <v>1695</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12681,7 +12735,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12716,7 +12770,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12751,7 +12805,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12786,7 +12840,7 @@
         <v>10</v>
       </c>
       <c r="J227">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="K227" t="s">
         <v>1004</v>
@@ -12821,7 +12875,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12891,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -12926,7 +12980,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>161</v>
+        <v>341</v>
       </c>
       <c r="K231" t="s">
         <v>1053</v>
@@ -12961,7 +13015,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="K232" t="s">
         <v>1053</v>
@@ -12996,7 +13050,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="K233" t="s">
         <v>1053</v>
@@ -13031,7 +13085,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="K234" t="s">
         <v>1053</v>
@@ -13136,7 +13190,7 @@
         <v>10</v>
       </c>
       <c r="J237">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="K237" t="s">
         <v>1081</v>
@@ -13276,7 +13330,7 @@
         <v>10</v>
       </c>
       <c r="J241">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="K241" t="s">
         <v>1081</v>
@@ -13311,7 +13365,7 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="K242" t="s">
         <v>1103</v>
@@ -13346,7 +13400,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="K243" t="s">
         <v>1081</v>
@@ -13381,7 +13435,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K244" t="s">
         <v>1103</v>
@@ -13416,7 +13470,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="K245" t="s">
         <v>1103</v>
@@ -13521,7 +13575,7 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K248" t="s">
         <v>1081</v>
@@ -13556,7 +13610,7 @@
         <v>10</v>
       </c>
       <c r="J249">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K249" t="s">
         <v>1081</v>
@@ -13591,7 +13645,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>147</v>
+        <v>237</v>
       </c>
       <c r="K250" t="s">
         <v>1081</v>
@@ -13626,7 +13680,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="K251" t="s">
         <v>1103</v>
@@ -13661,7 +13715,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="K252" t="s">
         <v>1081</v>
@@ -13696,7 +13750,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="K253" t="s">
         <v>1081</v>
@@ -13731,7 +13785,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K254" t="s">
         <v>1152</v>
@@ -13766,7 +13820,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K255" t="s">
         <v>1152</v>
@@ -13801,7 +13855,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="K256" t="s">
         <v>1152</v>
@@ -13836,7 +13890,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="K257" t="s">
         <v>1166</v>
@@ -13871,7 +13925,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>141</v>
+        <v>84</v>
       </c>
       <c r="K258" t="s">
         <v>1166</v>
@@ -13906,7 +13960,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K259" t="s">
         <v>1166</v>
@@ -13941,7 +13995,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="K260" t="s">
         <v>1166</v>
@@ -13976,7 +14030,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="K261" t="s">
         <v>1166</v>
@@ -14046,7 +14100,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K263" t="s">
         <v>1166</v>
@@ -14081,7 +14135,7 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="K264" t="s">
         <v>1166</v>
@@ -14116,7 +14170,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K265" t="s">
         <v>1166</v>
@@ -14221,7 +14275,7 @@
         <v>10</v>
       </c>
       <c r="J268">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K268" t="s">
         <v>1201</v>
@@ -14291,7 +14345,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="K270" t="s">
         <v>1201</v>
@@ -14326,7 +14380,7 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="K271" t="s">
         <v>1223</v>
@@ -14361,7 +14415,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="K272" t="s">
         <v>1223</v>
@@ -14396,7 +14450,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K273" t="s">
         <v>1223</v>
@@ -14431,7 +14485,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K274" t="s">
         <v>1223</v>
@@ -14466,7 +14520,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="K275" t="s">
         <v>1223</v>
@@ -14501,7 +14555,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K276" t="s">
         <v>1223</v>
@@ -14571,7 +14625,7 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="K278" t="s">
         <v>1249</v>
@@ -14606,7 +14660,7 @@
         <v>10</v>
       </c>
       <c r="J279">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="K279" t="s">
         <v>1249</v>
@@ -14641,7 +14695,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>217</v>
+        <v>1410</v>
       </c>
       <c r="K280" t="s">
         <v>1263</v>
@@ -14676,7 +14730,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>158</v>
+        <v>253</v>
       </c>
       <c r="K281" t="s">
         <v>1263</v>
@@ -14711,7 +14765,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="K282" t="s">
         <v>1263</v>
@@ -14734,7 +14788,7 @@
         <v>1274</v>
       </c>
       <c r="F283" s="4" t="s">
-        <v>1271</v>
+        <v>1275</v>
       </c>
       <c r="G283" t="s">
         <v>24</v>
@@ -14746,7 +14800,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>145</v>
+        <v>235</v>
       </c>
       <c r="K283" t="s">
         <v>1263</v>
@@ -14757,19 +14811,19 @@
         <v>17</v>
       </c>
       <c r="B284" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="E284" s="4" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="F284" s="4" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="G284" t="s">
         <v>24</v>
@@ -14781,10 +14835,10 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="K284" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -14792,19 +14846,19 @@
         <v>17</v>
       </c>
       <c r="B285" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="E285" s="4" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="F285" s="4" t="s">
-        <v>1278</v>
+        <v>1285</v>
       </c>
       <c r="G285" t="s">
         <v>24</v>
@@ -14816,10 +14870,10 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="K285" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -14827,22 +14881,22 @@
         <v>17</v>
       </c>
       <c r="B286" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>1282</v>
+        <v>1286</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>1283</v>
+        <v>1287</v>
       </c>
       <c r="E286" s="4" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="F286" s="4" t="s">
-        <v>1262</v>
+        <v>1289</v>
       </c>
       <c r="G286" t="s">
-        <v>1285</v>
+        <v>24</v>
       </c>
       <c r="H286">
         <v>1</v>
@@ -14851,10 +14905,10 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="K286" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -14862,16 +14916,16 @@
         <v>17</v>
       </c>
       <c r="B287" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>1286</v>
+        <v>1290</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>1287</v>
+        <v>1291</v>
       </c>
       <c r="E287" s="4" t="s">
-        <v>1288</v>
+        <v>1292</v>
       </c>
       <c r="F287" s="4" t="s">
         <v>1289</v>
@@ -14886,10 +14940,10 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>543</v>
+        <v>145</v>
       </c>
       <c r="K287" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -14897,19 +14951,19 @@
         <v>17</v>
       </c>
       <c r="B288" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="E288" s="4" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>1262</v>
+        <v>1296</v>
       </c>
       <c r="G288" t="s">
         <v>24</v>
@@ -14921,10 +14975,10 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>306</v>
+        <v>173</v>
       </c>
       <c r="K288" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -14932,22 +14986,22 @@
         <v>17</v>
       </c>
       <c r="B289" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="E289" s="4" t="s">
-        <v>1295</v>
+        <v>1299</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>1262</v>
+        <v>1296</v>
       </c>
       <c r="G289" t="s">
-        <v>1296</v>
+        <v>24</v>
       </c>
       <c r="H289">
         <v>1</v>
@@ -14956,10 +15010,10 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="K289" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -14967,22 +15021,22 @@
         <v>17</v>
       </c>
       <c r="B290" t="s">
-        <v>1258</v>
+        <v>1276</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="E290" s="4" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>1262</v>
+        <v>1280</v>
       </c>
       <c r="G290" t="s">
-        <v>24</v>
+        <v>1303</v>
       </c>
       <c r="H290">
         <v>1</v>
@@ -14991,30 +15045,30 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="K290" t="s">
-        <v>1263</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B291" t="s">
-        <v>1300</v>
+        <v>1276</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="E291" s="4" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="F291" s="4" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="G291" t="s">
         <v>24</v>
@@ -15026,33 +15080,33 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>0</v>
+        <v>569</v>
       </c>
       <c r="K291" t="s">
-        <v>1305</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B292" t="s">
-        <v>1306</v>
+        <v>1276</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E292" s="4" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>1310</v>
+        <v>1280</v>
       </c>
       <c r="G292" t="s">
-        <v>626</v>
+        <v>24</v>
       </c>
       <c r="H292">
         <v>1</v>
@@ -15061,34 +15115,34 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>16</v>
+        <v>219</v>
       </c>
       <c r="K292" t="s">
-        <v>1311</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B293" t="s">
-        <v>1306</v>
+        <v>1276</v>
       </c>
       <c r="C293" s="4" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D293" s="4" t="s">
         <v>1312</v>
       </c>
-      <c r="D293" s="4" t="s">
+      <c r="E293" s="4" t="s">
         <v>1313</v>
       </c>
-      <c r="E293" s="4" t="s">
+      <c r="F293" s="4" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G293" t="s">
         <v>1314</v>
       </c>
-      <c r="F293" s="4" t="s">
-        <v>1315</v>
-      </c>
-      <c r="G293" t="s">
-        <v>1316</v>
-      </c>
       <c r="H293">
         <v>1</v>
       </c>
@@ -15096,33 +15150,33 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>52</v>
+        <v>189</v>
       </c>
       <c r="K293" t="s">
-        <v>1311</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B294" t="s">
-        <v>1306</v>
+        <v>1276</v>
       </c>
       <c r="C294" s="4" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D294" s="4" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E294" s="4" t="s">
         <v>1317</v>
       </c>
-      <c r="D294" s="4" t="s">
-        <v>1318</v>
-      </c>
-      <c r="E294" s="4" t="s">
-        <v>1319</v>
-      </c>
       <c r="F294" s="4" t="s">
-        <v>1320</v>
+        <v>1280</v>
       </c>
       <c r="G294" t="s">
-        <v>212</v>
+        <v>24</v>
       </c>
       <c r="H294">
         <v>1</v>
@@ -15131,10 +15185,10 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="K294" t="s">
-        <v>1311</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -15142,19 +15196,19 @@
         <v>18</v>
       </c>
       <c r="B295" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C295" s="4" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E295" s="4" t="s">
         <v>1321</v>
       </c>
-      <c r="C295" s="4" t="s">
+      <c r="F295" s="4" t="s">
         <v>1322</v>
-      </c>
-      <c r="D295" s="4" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E295" s="4" t="s">
-        <v>1324</v>
-      </c>
-      <c r="F295" s="4" t="s">
-        <v>1325</v>
       </c>
       <c r="G295" t="s">
         <v>24</v>
@@ -15166,10 +15220,10 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="K295" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -15177,34 +15231,34 @@
         <v>18</v>
       </c>
       <c r="B296" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="C296" s="4" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D296" s="4" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E296" s="4" t="s">
         <v>1327</v>
       </c>
-      <c r="D296" s="4" t="s">
+      <c r="F296" s="4" t="s">
         <v>1328</v>
       </c>
-      <c r="E296" s="4" t="s">
+      <c r="G296" t="s">
+        <v>626</v>
+      </c>
+      <c r="H296">
+        <v>1</v>
+      </c>
+      <c r="I296" t="s">
+        <v>10</v>
+      </c>
+      <c r="J296">
+        <v>1</v>
+      </c>
+      <c r="K296" t="s">
         <v>1329</v>
-      </c>
-      <c r="F296" s="4" t="s">
-        <v>1330</v>
-      </c>
-      <c r="G296" t="s">
-        <v>24</v>
-      </c>
-      <c r="H296">
-        <v>1</v>
-      </c>
-      <c r="I296" t="s">
-        <v>10</v>
-      </c>
-      <c r="J296">
-        <v>3</v>
-      </c>
-      <c r="K296" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -15212,23 +15266,23 @@
         <v>18</v>
       </c>
       <c r="B297" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="C297" s="4" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D297" s="4" t="s">
         <v>1331</v>
       </c>
-      <c r="D297" s="4" t="s">
+      <c r="E297" s="4" t="s">
         <v>1332</v>
       </c>
-      <c r="E297" s="4" t="s">
+      <c r="F297" s="4" t="s">
         <v>1333</v>
       </c>
-      <c r="F297" s="4" t="s">
+      <c r="G297" t="s">
         <v>1334</v>
       </c>
-      <c r="G297" t="s">
-        <v>24</v>
-      </c>
       <c r="H297">
         <v>1</v>
       </c>
@@ -15236,10 +15290,10 @@
         <v>10</v>
       </c>
       <c r="J297">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K297" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -15247,7 +15301,7 @@
         <v>18</v>
       </c>
       <c r="B298" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>1335</v>
@@ -15262,7 +15316,7 @@
         <v>1338</v>
       </c>
       <c r="G298" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="H298">
         <v>1</v>
@@ -15271,10 +15325,10 @@
         <v>10</v>
       </c>
       <c r="J298">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K298" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -15282,19 +15336,19 @@
         <v>18</v>
       </c>
       <c r="B299" t="s">
-        <v>1321</v>
+        <v>1339</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E299" s="4" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="F299" s="4" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="G299" t="s">
         <v>24</v>
@@ -15306,10 +15360,10 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K299" t="s">
-        <v>1326</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -15317,34 +15371,34 @@
         <v>18</v>
       </c>
       <c r="B300" t="s">
-        <v>1321</v>
+        <v>1339</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="D300" s="4" t="s">
+        <v>1346</v>
+      </c>
+      <c r="E300" s="4" t="s">
+        <v>1347</v>
+      </c>
+      <c r="F300" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="G300" t="s">
+        <v>24</v>
+      </c>
+      <c r="H300">
+        <v>1</v>
+      </c>
+      <c r="I300" t="s">
+        <v>10</v>
+      </c>
+      <c r="J300">
+        <v>2</v>
+      </c>
+      <c r="K300" t="s">
         <v>1344</v>
-      </c>
-      <c r="E300" s="4" t="s">
-        <v>1345</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>1346</v>
-      </c>
-      <c r="G300" t="s">
-        <v>194</v>
-      </c>
-      <c r="H300">
-        <v>1</v>
-      </c>
-      <c r="I300" t="s">
-        <v>10</v>
-      </c>
-      <c r="J300">
-        <v>1</v>
-      </c>
-      <c r="K300" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -15352,19 +15406,19 @@
         <v>18</v>
       </c>
       <c r="B301" t="s">
-        <v>1321</v>
+        <v>1339</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="E301" s="4" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="G301" t="s">
         <v>24</v>
@@ -15376,10 +15430,10 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K301" t="s">
-        <v>1326</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -15387,22 +15441,22 @@
         <v>18</v>
       </c>
       <c r="B302" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="E302" s="4" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="G302" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H302">
         <v>1</v>
@@ -15411,10 +15465,10 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K302" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -15422,7 +15476,7 @@
         <v>18</v>
       </c>
       <c r="B303" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>1357</v>
@@ -15437,7 +15491,7 @@
         <v>1360</v>
       </c>
       <c r="G303" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="H303">
         <v>1</v>
@@ -15446,10 +15500,10 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K303" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -15457,7 +15511,7 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>1361</v>
@@ -15472,7 +15526,7 @@
         <v>1364</v>
       </c>
       <c r="G304" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="H304">
         <v>1</v>
@@ -15481,10 +15535,10 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K304" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -15492,7 +15546,7 @@
         <v>18</v>
       </c>
       <c r="B305" t="s">
-        <v>1351</v>
+        <v>1339</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>1365</v>
@@ -15507,7 +15561,7 @@
         <v>1368</v>
       </c>
       <c r="G305" t="s">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="H305">
         <v>1</v>
@@ -15516,10 +15570,10 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K305" t="s">
-        <v>1356</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -15527,22 +15581,22 @@
         <v>18</v>
       </c>
       <c r="B306" t="s">
-        <v>1351</v>
+        <v>1369</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="E306" s="4" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="G306" t="s">
-        <v>866</v>
+        <v>120</v>
       </c>
       <c r="H306">
         <v>1</v>
@@ -15551,10 +15605,10 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K306" t="s">
-        <v>1356</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -15562,34 +15616,34 @@
         <v>18</v>
       </c>
       <c r="B307" t="s">
-        <v>1351</v>
+        <v>1369</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D307" s="4" t="s">
+        <v>1376</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G307" t="s">
+        <v>141</v>
+      </c>
+      <c r="H307">
+        <v>1</v>
+      </c>
+      <c r="I307" t="s">
+        <v>10</v>
+      </c>
+      <c r="J307">
+        <v>7</v>
+      </c>
+      <c r="K307" t="s">
         <v>1374</v>
-      </c>
-      <c r="E307" s="4" t="s">
-        <v>1375</v>
-      </c>
-      <c r="F307" s="4" t="s">
-        <v>1376</v>
-      </c>
-      <c r="G307" t="s">
-        <v>398</v>
-      </c>
-      <c r="H307">
-        <v>1</v>
-      </c>
-      <c r="I307" t="s">
-        <v>10</v>
-      </c>
-      <c r="J307">
-        <v>3</v>
-      </c>
-      <c r="K307" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
@@ -15597,22 +15651,22 @@
         <v>18</v>
       </c>
       <c r="B308" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="E308" s="4" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="G308" t="s">
-        <v>1382</v>
+        <v>180</v>
       </c>
       <c r="H308">
         <v>1</v>
@@ -15621,10 +15675,10 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K308" t="s">
-        <v>1383</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -15632,22 +15686,22 @@
         <v>18</v>
       </c>
       <c r="B309" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="C309" s="4" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D309" s="4" t="s">
         <v>1384</v>
       </c>
-      <c r="D309" s="4" t="s">
+      <c r="E309" s="4" t="s">
         <v>1385</v>
       </c>
-      <c r="E309" s="4" t="s">
+      <c r="F309" s="4" t="s">
         <v>1386</v>
       </c>
-      <c r="F309" s="4" t="s">
-        <v>1387</v>
-      </c>
       <c r="G309" t="s">
-        <v>424</v>
+        <v>180</v>
       </c>
       <c r="H309">
         <v>1</v>
@@ -15656,10 +15710,10 @@
         <v>10</v>
       </c>
       <c r="J309">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="K309" t="s">
-        <v>1383</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
@@ -15667,22 +15721,22 @@
         <v>18</v>
       </c>
       <c r="B310" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="C310" s="4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D310" s="4" t="s">
         <v>1388</v>
       </c>
-      <c r="D310" s="4" t="s">
+      <c r="E310" s="4" t="s">
         <v>1389</v>
       </c>
-      <c r="E310" s="4" t="s">
+      <c r="F310" s="4" t="s">
         <v>1390</v>
       </c>
-      <c r="F310" s="4" t="s">
-        <v>1391</v>
-      </c>
       <c r="G310" t="s">
-        <v>1392</v>
+        <v>866</v>
       </c>
       <c r="H310">
         <v>1</v>
@@ -15691,10 +15745,10 @@
         <v>10</v>
       </c>
       <c r="J310">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K310" t="s">
-        <v>1383</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
@@ -15702,34 +15756,174 @@
         <v>18</v>
       </c>
       <c r="B311" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="C311" s="4" t="s">
+        <v>1391</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E311" s="4" t="s">
         <v>1393</v>
       </c>
-      <c r="D311" s="4" t="s">
+      <c r="F311" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="E311" s="4" t="s">
+      <c r="G311" t="s">
+        <v>398</v>
+      </c>
+      <c r="H311">
+        <v>1</v>
+      </c>
+      <c r="I311" t="s">
+        <v>10</v>
+      </c>
+      <c r="J311">
+        <v>3</v>
+      </c>
+      <c r="K311" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>18</v>
+      </c>
+      <c r="B312" t="s">
         <v>1395</v>
       </c>
-      <c r="F311" s="4" t="s">
+      <c r="C312" s="4" t="s">
         <v>1396</v>
       </c>
-      <c r="G311" t="s">
+      <c r="D312" s="4" t="s">
         <v>1397</v>
       </c>
-      <c r="H311">
-        <v>1</v>
-      </c>
-      <c r="I311" t="s">
-        <v>10</v>
-      </c>
-      <c r="J311">
-        <v>137</v>
-      </c>
-      <c r="K311" t="s">
-        <v>1383</v>
+      <c r="E312" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G312" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H312">
+        <v>1</v>
+      </c>
+      <c r="I312" t="s">
+        <v>10</v>
+      </c>
+      <c r="J312">
+        <v>7</v>
+      </c>
+      <c r="K312" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>18</v>
+      </c>
+      <c r="B313" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E313" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="G313" t="s">
+        <v>424</v>
+      </c>
+      <c r="H313">
+        <v>1</v>
+      </c>
+      <c r="I313" t="s">
+        <v>10</v>
+      </c>
+      <c r="J313">
+        <v>71</v>
+      </c>
+      <c r="K313" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>18</v>
+      </c>
+      <c r="B314" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="E314" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G314" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H314">
+        <v>1</v>
+      </c>
+      <c r="I314" t="s">
+        <v>10</v>
+      </c>
+      <c r="J314">
+        <v>25</v>
+      </c>
+      <c r="K314" t="s">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>18</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>1414</v>
+      </c>
+      <c r="G315" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H315">
+        <v>1</v>
+      </c>
+      <c r="I315" t="s">
+        <v>10</v>
+      </c>
+      <c r="J315">
+        <v>140</v>
+      </c>
+      <c r="K315" t="s">
+        <v>1401</v>
       </c>
     </row>
   </sheetData>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 05:32</t>
+    <t>2026-09-15 05:43</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_05_31_50.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_05_43_14.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -7555,7 +7555,7 @@
         <v>10</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="s">
         <v>300</v>
@@ -8815,7 +8815,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -8920,7 +8920,7 @@
         <v>10</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115" t="s">
         <v>504</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="J128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="s">
         <v>558</v>
@@ -10075,7 +10075,7 @@
         <v>10</v>
       </c>
       <c r="J148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" t="s">
         <v>656</v>
@@ -11020,7 +11020,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -12245,7 +12245,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>723</v>
+        <v>764</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12455,7 +12455,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12490,7 +12490,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12525,7 +12525,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12560,7 +12560,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>788</v>
+        <v>630</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12595,7 +12595,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1010</v>
+        <v>906</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12630,7 +12630,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12665,7 +12665,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12700,7 +12700,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1695</v>
+        <v>1197</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12735,7 +12735,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12770,7 +12770,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12805,7 +12805,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12840,7 +12840,7 @@
         <v>10</v>
       </c>
       <c r="J227">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K227" t="s">
         <v>1004</v>
@@ -12910,7 +12910,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -12980,7 +12980,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>341</v>
+        <v>183</v>
       </c>
       <c r="K231" t="s">
         <v>1053</v>
@@ -13015,7 +13015,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="K232" t="s">
         <v>1053</v>
@@ -13050,7 +13050,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="K233" t="s">
         <v>1053</v>
@@ -13085,7 +13085,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="K234" t="s">
         <v>1053</v>
@@ -13120,7 +13120,7 @@
         <v>10</v>
       </c>
       <c r="J235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="s">
         <v>1071</v>
@@ -13190,7 +13190,7 @@
         <v>10</v>
       </c>
       <c r="J237">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="K237" t="s">
         <v>1081</v>
@@ -13295,7 +13295,7 @@
         <v>10</v>
       </c>
       <c r="J240">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K240" t="s">
         <v>1081</v>
@@ -13330,7 +13330,7 @@
         <v>10</v>
       </c>
       <c r="J241">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="K241" t="s">
         <v>1081</v>
@@ -13365,7 +13365,7 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="K242" t="s">
         <v>1103</v>
@@ -13400,7 +13400,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K243" t="s">
         <v>1081</v>
@@ -13435,7 +13435,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K244" t="s">
         <v>1103</v>
@@ -13470,7 +13470,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K245" t="s">
         <v>1103</v>
@@ -13575,7 +13575,7 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="K248" t="s">
         <v>1081</v>
@@ -13610,7 +13610,7 @@
         <v>10</v>
       </c>
       <c r="J249">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="K249" t="s">
         <v>1081</v>
@@ -13645,7 +13645,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="K250" t="s">
         <v>1081</v>
@@ -13680,7 +13680,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="K251" t="s">
         <v>1103</v>
@@ -13715,7 +13715,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K252" t="s">
         <v>1081</v>
@@ -13750,7 +13750,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="K253" t="s">
         <v>1081</v>
@@ -13785,7 +13785,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K254" t="s">
         <v>1152</v>
@@ -13820,7 +13820,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="K255" t="s">
         <v>1152</v>
@@ -13855,7 +13855,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K256" t="s">
         <v>1152</v>
@@ -13890,7 +13890,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K257" t="s">
         <v>1166</v>
@@ -13925,7 +13925,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K258" t="s">
         <v>1166</v>
@@ -13960,7 +13960,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="K259" t="s">
         <v>1166</v>
@@ -13995,7 +13995,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K260" t="s">
         <v>1166</v>
@@ -14030,7 +14030,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K261" t="s">
         <v>1166</v>
@@ -14065,7 +14065,7 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K262" t="s">
         <v>1166</v>
@@ -14100,7 +14100,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K263" t="s">
         <v>1166</v>
@@ -14135,7 +14135,7 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>118</v>
+        <v>78</v>
       </c>
       <c r="K264" t="s">
         <v>1166</v>
@@ -14170,7 +14170,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K265" t="s">
         <v>1166</v>
@@ -14275,7 +14275,7 @@
         <v>10</v>
       </c>
       <c r="J268">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="K268" t="s">
         <v>1201</v>
@@ -14310,7 +14310,7 @@
         <v>10</v>
       </c>
       <c r="J269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K269" t="s">
         <v>1201</v>
@@ -14345,7 +14345,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="K270" t="s">
         <v>1201</v>
@@ -14380,7 +14380,7 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="K271" t="s">
         <v>1223</v>
@@ -14415,7 +14415,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="K272" t="s">
         <v>1223</v>
@@ -14450,7 +14450,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K273" t="s">
         <v>1223</v>
@@ -14485,7 +14485,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K274" t="s">
         <v>1223</v>
@@ -14520,7 +14520,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K275" t="s">
         <v>1223</v>
@@ -14555,7 +14555,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K276" t="s">
         <v>1223</v>
@@ -14625,7 +14625,7 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K278" t="s">
         <v>1249</v>
@@ -14660,7 +14660,7 @@
         <v>10</v>
       </c>
       <c r="J279">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K279" t="s">
         <v>1249</v>
@@ -14695,7 +14695,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>1410</v>
+        <v>1270</v>
       </c>
       <c r="K280" t="s">
         <v>1263</v>
@@ -14730,7 +14730,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K281" t="s">
         <v>1263</v>
@@ -14765,7 +14765,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K282" t="s">
         <v>1263</v>
@@ -14800,7 +14800,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K283" t="s">
         <v>1263</v>
@@ -14835,7 +14835,7 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K284" t="s">
         <v>1281</v>
@@ -14870,7 +14870,7 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="K285" t="s">
         <v>1281</v>
@@ -14905,7 +14905,7 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="K286" t="s">
         <v>1281</v>
@@ -14940,7 +14940,7 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K287" t="s">
         <v>1281</v>
@@ -14975,7 +14975,7 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="K288" t="s">
         <v>1281</v>
@@ -15010,7 +15010,7 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="K289" t="s">
         <v>1281</v>
@@ -15045,7 +15045,7 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="K290" t="s">
         <v>1281</v>
@@ -15080,7 +15080,7 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>569</v>
+        <v>411</v>
       </c>
       <c r="K291" t="s">
         <v>1281</v>
@@ -15115,7 +15115,7 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="K292" t="s">
         <v>1281</v>
@@ -15150,7 +15150,7 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="K293" t="s">
         <v>1281</v>
@@ -15185,7 +15185,7 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K294" t="s">
         <v>1281</v>
@@ -15290,7 +15290,7 @@
         <v>10</v>
       </c>
       <c r="J297">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="K297" t="s">
         <v>1329</v>
@@ -15395,7 +15395,7 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K300" t="s">
         <v>1344</v>
@@ -15430,7 +15430,7 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K301" t="s">
         <v>1344</v>
@@ -15605,7 +15605,7 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K306" t="s">
         <v>1374</v>
@@ -15640,7 +15640,7 @@
         <v>10</v>
       </c>
       <c r="J307">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K307" t="s">
         <v>1374</v>
@@ -15675,7 +15675,7 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K308" t="s">
         <v>1374</v>
@@ -15710,7 +15710,7 @@
         <v>10</v>
       </c>
       <c r="J309">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K309" t="s">
         <v>1374</v>
@@ -15815,7 +15815,7 @@
         <v>10</v>
       </c>
       <c r="J312">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K312" t="s">
         <v>1401</v>
@@ -15850,7 +15850,7 @@
         <v>10</v>
       </c>
       <c r="J313">
-        <v>71</v>
+        <v>12</v>
       </c>
       <c r="K313" t="s">
         <v>1401</v>
@@ -15885,7 +15885,7 @@
         <v>10</v>
       </c>
       <c r="J314">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K314" t="s">
         <v>1401</v>
@@ -15920,7 +15920,7 @@
         <v>10</v>
       </c>
       <c r="J315">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="K315" t="s">
         <v>1401</v>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 05:43</t>
+    <t>2026-09-15 08:51</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_05_43_14.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_08_51_26.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -6680,7 +6680,7 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="s">
         <v>256</v>
@@ -6855,7 +6855,7 @@
         <v>10</v>
       </c>
       <c r="J56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="s">
         <v>277</v>
@@ -7205,7 +7205,7 @@
         <v>10</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66" t="s">
         <v>300</v>
@@ -7345,7 +7345,7 @@
         <v>10</v>
       </c>
       <c r="J70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="s">
         <v>300</v>
@@ -7485,7 +7485,7 @@
         <v>10</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K74" t="s">
         <v>300</v>
@@ -7555,7 +7555,7 @@
         <v>10</v>
       </c>
       <c r="J76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="s">
         <v>300</v>
@@ -7695,7 +7695,7 @@
         <v>10</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="s">
         <v>393</v>
@@ -8220,7 +8220,7 @@
         <v>10</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" t="s">
         <v>443</v>
@@ -8500,7 +8500,7 @@
         <v>10</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" t="s">
         <v>443</v>
@@ -8535,7 +8535,7 @@
         <v>10</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="s">
         <v>443</v>
@@ -8815,7 +8815,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -8920,7 +8920,7 @@
         <v>10</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115" t="s">
         <v>504</v>
@@ -9375,7 +9375,7 @@
         <v>10</v>
       </c>
       <c r="J128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="s">
         <v>558</v>
@@ -11510,7 +11510,7 @@
         <v>10</v>
       </c>
       <c r="J189">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K189" t="s">
         <v>844</v>
@@ -11965,7 +11965,7 @@
         <v>10</v>
       </c>
       <c r="J202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K202" t="s">
         <v>844</v>
@@ -12245,7 +12245,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>764</v>
+        <v>849</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12455,7 +12455,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12490,7 +12490,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12525,7 +12525,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12560,7 +12560,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>630</v>
+        <v>714</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12595,7 +12595,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>906</v>
+        <v>1718</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12630,7 +12630,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12665,7 +12665,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>256</v>
+        <v>372</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12700,7 +12700,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1197</v>
+        <v>1930</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12735,7 +12735,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>122</v>
+        <v>187</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12805,7 +12805,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12840,7 +12840,7 @@
         <v>10</v>
       </c>
       <c r="J227">
-        <v>160</v>
+        <v>337</v>
       </c>
       <c r="K227" t="s">
         <v>1004</v>
@@ -12875,7 +12875,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12910,7 +12910,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -12945,7 +12945,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -12980,7 +12980,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="K231" t="s">
         <v>1053</v>
@@ -13015,7 +13015,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="K232" t="s">
         <v>1053</v>
@@ -13050,7 +13050,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="K233" t="s">
         <v>1053</v>
@@ -13085,7 +13085,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K234" t="s">
         <v>1053</v>
@@ -13190,7 +13190,7 @@
         <v>10</v>
       </c>
       <c r="J237">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="K237" t="s">
         <v>1081</v>
@@ -13295,7 +13295,7 @@
         <v>10</v>
       </c>
       <c r="J240">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="K240" t="s">
         <v>1081</v>
@@ -13330,7 +13330,7 @@
         <v>10</v>
       </c>
       <c r="J241">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="K241" t="s">
         <v>1081</v>
@@ -13400,7 +13400,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="K243" t="s">
         <v>1081</v>
@@ -13435,7 +13435,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K244" t="s">
         <v>1103</v>
@@ -13470,7 +13470,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K245" t="s">
         <v>1103</v>
@@ -13505,7 +13505,7 @@
         <v>10</v>
       </c>
       <c r="J246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" t="s">
         <v>1071</v>
@@ -13575,7 +13575,7 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="K248" t="s">
         <v>1081</v>
@@ -13610,7 +13610,7 @@
         <v>10</v>
       </c>
       <c r="J249">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="K249" t="s">
         <v>1081</v>
@@ -13645,7 +13645,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="K250" t="s">
         <v>1081</v>
@@ -13680,7 +13680,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="K251" t="s">
         <v>1103</v>
@@ -13715,7 +13715,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K252" t="s">
         <v>1081</v>
@@ -13750,7 +13750,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="K253" t="s">
         <v>1081</v>
@@ -13785,7 +13785,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="K254" t="s">
         <v>1152</v>
@@ -13820,7 +13820,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>138</v>
+        <v>377</v>
       </c>
       <c r="K255" t="s">
         <v>1152</v>
@@ -13855,7 +13855,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K256" t="s">
         <v>1152</v>
@@ -13890,7 +13890,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="K257" t="s">
         <v>1166</v>
@@ -13925,7 +13925,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="K258" t="s">
         <v>1166</v>
@@ -13960,7 +13960,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>139</v>
+        <v>101</v>
       </c>
       <c r="K259" t="s">
         <v>1166</v>
@@ -13995,7 +13995,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="K260" t="s">
         <v>1166</v>
@@ -14030,7 +14030,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="K261" t="s">
         <v>1166</v>
@@ -14065,7 +14065,7 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="K262" t="s">
         <v>1166</v>
@@ -14100,7 +14100,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="K263" t="s">
         <v>1166</v>
@@ -14135,7 +14135,7 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="K264" t="s">
         <v>1166</v>
@@ -14170,7 +14170,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="K265" t="s">
         <v>1166</v>
@@ -14205,7 +14205,7 @@
         <v>10</v>
       </c>
       <c r="J266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K266" t="s">
         <v>1201</v>
@@ -14275,7 +14275,7 @@
         <v>10</v>
       </c>
       <c r="J268">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="K268" t="s">
         <v>1201</v>
@@ -14345,7 +14345,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="K270" t="s">
         <v>1201</v>
@@ -14380,7 +14380,7 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="K271" t="s">
         <v>1223</v>
@@ -14415,7 +14415,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K272" t="s">
         <v>1223</v>
@@ -14450,7 +14450,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="K273" t="s">
         <v>1223</v>
@@ -14485,7 +14485,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="K274" t="s">
         <v>1223</v>
@@ -14520,7 +14520,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="K275" t="s">
         <v>1223</v>
@@ -14555,7 +14555,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="K276" t="s">
         <v>1223</v>
@@ -14625,7 +14625,7 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K278" t="s">
         <v>1249</v>
@@ -14660,7 +14660,7 @@
         <v>10</v>
       </c>
       <c r="J279">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K279" t="s">
         <v>1249</v>
@@ -14695,7 +14695,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>1270</v>
+        <v>2606</v>
       </c>
       <c r="K280" t="s">
         <v>1263</v>
@@ -14730,7 +14730,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>255</v>
+        <v>903</v>
       </c>
       <c r="K281" t="s">
         <v>1263</v>
@@ -14765,7 +14765,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>253</v>
+        <v>1280</v>
       </c>
       <c r="K282" t="s">
         <v>1263</v>
@@ -14800,7 +14800,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>237</v>
+        <v>1100</v>
       </c>
       <c r="K283" t="s">
         <v>1263</v>
@@ -14835,7 +14835,7 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="K284" t="s">
         <v>1281</v>
@@ -14870,7 +14870,7 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>187</v>
+        <v>223</v>
       </c>
       <c r="K285" t="s">
         <v>1281</v>
@@ -14905,7 +14905,7 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="K286" t="s">
         <v>1281</v>
@@ -14940,7 +14940,7 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="K287" t="s">
         <v>1281</v>
@@ -14975,7 +14975,7 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="K288" t="s">
         <v>1281</v>
@@ -15010,7 +15010,7 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>168</v>
+        <v>211</v>
       </c>
       <c r="K289" t="s">
         <v>1281</v>
@@ -15045,7 +15045,7 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>226</v>
+        <v>296</v>
       </c>
       <c r="K290" t="s">
         <v>1281</v>
@@ -15080,7 +15080,7 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>411</v>
+        <v>610</v>
       </c>
       <c r="K291" t="s">
         <v>1281</v>
@@ -15115,7 +15115,7 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>226</v>
+        <v>276</v>
       </c>
       <c r="K292" t="s">
         <v>1281</v>
@@ -15150,7 +15150,7 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>186</v>
+        <v>235</v>
       </c>
       <c r="K293" t="s">
         <v>1281</v>
@@ -15185,7 +15185,7 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="K294" t="s">
         <v>1281</v>
@@ -15255,7 +15255,7 @@
         <v>10</v>
       </c>
       <c r="J296">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K296" t="s">
         <v>1329</v>
@@ -15290,7 +15290,7 @@
         <v>10</v>
       </c>
       <c r="J297">
-        <v>7</v>
+        <v>569</v>
       </c>
       <c r="K297" t="s">
         <v>1329</v>
@@ -15325,7 +15325,7 @@
         <v>10</v>
       </c>
       <c r="J298">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K298" t="s">
         <v>1329</v>
@@ -15360,7 +15360,7 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>11</v>
+        <v>776</v>
       </c>
       <c r="K299" t="s">
         <v>1344</v>
@@ -15395,7 +15395,7 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="K300" t="s">
         <v>1344</v>
@@ -15430,7 +15430,7 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>7</v>
+        <v>762</v>
       </c>
       <c r="K301" t="s">
         <v>1344</v>
@@ -15465,7 +15465,7 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>8</v>
+        <v>707</v>
       </c>
       <c r="K302" t="s">
         <v>1344</v>
@@ -15500,7 +15500,7 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>8</v>
+        <v>635</v>
       </c>
       <c r="K303" t="s">
         <v>1344</v>
@@ -15535,7 +15535,7 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="K304" t="s">
         <v>1344</v>
@@ -15570,7 +15570,7 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>9</v>
+        <v>1055</v>
       </c>
       <c r="K305" t="s">
         <v>1344</v>
@@ -15605,7 +15605,7 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K306" t="s">
         <v>1374</v>
@@ -15640,7 +15640,7 @@
         <v>10</v>
       </c>
       <c r="J307">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K307" t="s">
         <v>1374</v>
@@ -15675,7 +15675,7 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K308" t="s">
         <v>1374</v>
@@ -15710,7 +15710,7 @@
         <v>10</v>
       </c>
       <c r="J309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K309" t="s">
         <v>1374</v>
@@ -15745,7 +15745,7 @@
         <v>10</v>
       </c>
       <c r="J310">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K310" t="s">
         <v>1374</v>
@@ -15780,7 +15780,7 @@
         <v>10</v>
       </c>
       <c r="J311">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="K311" t="s">
         <v>1374</v>
@@ -15815,7 +15815,7 @@
         <v>10</v>
       </c>
       <c r="J312">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="K312" t="s">
         <v>1401</v>
@@ -15850,7 +15850,7 @@
         <v>10</v>
       </c>
       <c r="J313">
-        <v>12</v>
+        <v>933</v>
       </c>
       <c r="K313" t="s">
         <v>1401</v>
@@ -15885,7 +15885,7 @@
         <v>10</v>
       </c>
       <c r="J314">
-        <v>16</v>
+        <v>747</v>
       </c>
       <c r="K314" t="s">
         <v>1401</v>
@@ -15920,7 +15920,7 @@
         <v>10</v>
       </c>
       <c r="J315">
-        <v>12</v>
+        <v>740</v>
       </c>
       <c r="K315" t="s">
         <v>1401</v>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2865" uniqueCount="1416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1420">
   <si>
     <t>검진 예약·접수 관리 프로그램 — 단위시험 목록</t>
   </si>
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 08:51</t>
+    <t>2026-09-15 09:15</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_08_51_26.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_09_15_19.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -3081,6 +3081,18 @@
   </si>
   <si>
     <t>Shell 핸들이 만들어지고, 그룹 없는 Page 를 누르면 선택된 Page 가 바뀌지 않으며, 그렇게 열리지 않는 문은 「휴무일 관리」 하나뿐이다.</t>
+  </si>
+  <si>
+    <t>리본 버튼은 전부 아이콘을 갖는다</t>
+  </si>
+  <si>
+    <t>MainForm (WF-00) — Ribbon 버튼 전부의 아이콘</t>
+  </si>
+  <si>
+    <t>2026-09-15 사용자 요청으로 버튼에 아이콘을 넣었다. 아이콘은 리소스 이름으로 찾아 붙이므로 이름이 한 글자 틀리면 그 버튼만 조용히 글자만 남는다 — Designer 가 직렬화하는 값이 아니라 코드가 붙이는 값이라, 화면을 열어 보기 전에는 아무도 모른다. 버튼을 새로 더하면서 아이콘을 빼먹는 것도 같은 모양으로 지나간다.</t>
+  </si>
+  <si>
+    <t>Ribbon 의 모든 BarButtonItem 이 SvgImage 를 갖는다. 훑은 버튼이 0개이면 아무것도 재지 않은 green 이므로 그것도 실패로 센다.</t>
   </si>
   <si>
     <t>모든 화면이 디자이너용 생성자를 갖는다</t>
@@ -4773,13 +4785,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D11">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4833,13 +4845,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C14" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D14" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -4888,7 +4900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K315"/>
+  <dimension ref="A1:K316"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -5805,7 +5817,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
         <v>115</v>
@@ -6190,7 +6202,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="s">
         <v>189</v>
@@ -7205,7 +7217,7 @@
         <v>10</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="s">
         <v>300</v>
@@ -7485,7 +7497,7 @@
         <v>10</v>
       </c>
       <c r="J74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K74" t="s">
         <v>300</v>
@@ -8500,7 +8512,7 @@
         <v>10</v>
       </c>
       <c r="J103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103" t="s">
         <v>443</v>
@@ -8815,7 +8827,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -10005,7 +10017,7 @@
         <v>10</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="s">
         <v>656</v>
@@ -10075,7 +10087,7 @@
         <v>10</v>
       </c>
       <c r="J148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" t="s">
         <v>656</v>
@@ -10180,7 +10192,7 @@
         <v>10</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" t="s">
         <v>656</v>
@@ -11020,7 +11032,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -12245,7 +12257,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12455,7 +12467,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12490,7 +12502,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12525,7 +12537,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12560,7 +12572,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>714</v>
+        <v>752</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12595,7 +12607,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1718</v>
+        <v>1295</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12630,7 +12642,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12665,7 +12677,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>372</v>
+        <v>303</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12700,7 +12712,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1930</v>
+        <v>1639</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12735,7 +12747,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>187</v>
+        <v>136</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12770,7 +12782,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12796,7 +12808,7 @@
         <v>1030</v>
       </c>
       <c r="G226" t="s">
-        <v>1031</v>
+        <v>24</v>
       </c>
       <c r="H226">
         <v>1</v>
@@ -12805,7 +12817,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12819,20 +12831,20 @@
         <v>999</v>
       </c>
       <c r="C227" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D227" s="4" t="s">
         <v>1032</v>
       </c>
-      <c r="D227" s="4" t="s">
+      <c r="E227" s="4" t="s">
         <v>1033</v>
       </c>
-      <c r="E227" s="4" t="s">
+      <c r="F227" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="F227" s="4" t="s">
+      <c r="G227" t="s">
         <v>1035</v>
       </c>
-      <c r="G227" t="s">
-        <v>24</v>
-      </c>
       <c r="H227">
         <v>1</v>
       </c>
@@ -12840,7 +12852,7 @@
         <v>10</v>
       </c>
       <c r="J227">
-        <v>337</v>
+        <v>110</v>
       </c>
       <c r="K227" t="s">
         <v>1004</v>
@@ -12875,7 +12887,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12901,7 +12913,7 @@
         <v>1043</v>
       </c>
       <c r="G229" t="s">
-        <v>875</v>
+        <v>24</v>
       </c>
       <c r="H229">
         <v>1</v>
@@ -12910,7 +12922,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -12936,7 +12948,7 @@
         <v>1047</v>
       </c>
       <c r="G230" t="s">
-        <v>580</v>
+        <v>875</v>
       </c>
       <c r="H230">
         <v>1</v>
@@ -12945,7 +12957,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -12956,22 +12968,22 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
+        <v>999</v>
+      </c>
+      <c r="C231" s="4" t="s">
         <v>1048</v>
       </c>
-      <c r="C231" s="4" t="s">
+      <c r="D231" s="4" t="s">
         <v>1049</v>
       </c>
-      <c r="D231" s="4" t="s">
+      <c r="E231" s="4" t="s">
         <v>1050</v>
       </c>
-      <c r="E231" s="4" t="s">
+      <c r="F231" s="4" t="s">
         <v>1051</v>
       </c>
-      <c r="F231" s="4" t="s">
-        <v>1052</v>
-      </c>
       <c r="G231" t="s">
-        <v>24</v>
+        <v>580</v>
       </c>
       <c r="H231">
         <v>1</v>
@@ -12980,10 +12992,10 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="K231" t="s">
-        <v>1053</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -12991,19 +13003,19 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C232" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D232" s="4" t="s">
         <v>1054</v>
       </c>
-      <c r="D232" s="4" t="s">
+      <c r="E232" s="4" t="s">
         <v>1055</v>
       </c>
-      <c r="E232" s="4" t="s">
+      <c r="F232" s="4" t="s">
         <v>1056</v>
-      </c>
-      <c r="F232" s="4" t="s">
-        <v>1057</v>
       </c>
       <c r="G232" t="s">
         <v>24</v>
@@ -13015,10 +13027,10 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>158</v>
+        <v>186</v>
       </c>
       <c r="K232" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -13026,7 +13038,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C233" s="4" t="s">
         <v>1058</v>
@@ -13050,10 +13062,10 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="K233" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -13061,7 +13073,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>1062</v>
@@ -13076,7 +13088,7 @@
         <v>1065</v>
       </c>
       <c r="G234" t="s">
-        <v>473</v>
+        <v>24</v>
       </c>
       <c r="H234">
         <v>1</v>
@@ -13085,10 +13097,10 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="K234" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -13096,22 +13108,22 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C235" s="4" t="s">
         <v>1066</v>
       </c>
-      <c r="C235" s="4" t="s">
+      <c r="D235" s="4" t="s">
         <v>1067</v>
       </c>
-      <c r="D235" s="4" t="s">
+      <c r="E235" s="4" t="s">
         <v>1068</v>
       </c>
-      <c r="E235" s="4" t="s">
+      <c r="F235" s="4" t="s">
         <v>1069</v>
       </c>
-      <c r="F235" s="4" t="s">
-        <v>1070</v>
-      </c>
       <c r="G235" t="s">
-        <v>580</v>
+        <v>473</v>
       </c>
       <c r="H235">
         <v>1</v>
@@ -13120,10 +13132,10 @@
         <v>10</v>
       </c>
       <c r="J235">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="K235" t="s">
-        <v>1071</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -13131,34 +13143,34 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C236" s="4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D236" s="4" t="s">
         <v>1072</v>
       </c>
-      <c r="D236" s="4" t="s">
+      <c r="E236" s="4" t="s">
         <v>1073</v>
       </c>
-      <c r="E236" s="4" t="s">
+      <c r="F236" s="4" t="s">
         <v>1074</v>
       </c>
-      <c r="F236" s="4" t="s">
+      <c r="G236" t="s">
+        <v>580</v>
+      </c>
+      <c r="H236">
+        <v>1</v>
+      </c>
+      <c r="I236" t="s">
+        <v>10</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236" t="s">
         <v>1075</v>
-      </c>
-      <c r="G236" t="s">
-        <v>24</v>
-      </c>
-      <c r="H236">
-        <v>1</v>
-      </c>
-      <c r="I236" t="s">
-        <v>10</v>
-      </c>
-      <c r="J236">
-        <v>0</v>
-      </c>
-      <c r="K236" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -13166,7 +13178,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C237" s="4" t="s">
         <v>1076</v>
@@ -13181,7 +13193,7 @@
         <v>1079</v>
       </c>
       <c r="G237" t="s">
-        <v>1080</v>
+        <v>24</v>
       </c>
       <c r="H237">
         <v>1</v>
@@ -13190,10 +13202,10 @@
         <v>10</v>
       </c>
       <c r="J237">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="K237" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -13201,34 +13213,34 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C238" s="4" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E238" s="4" t="s">
         <v>1082</v>
       </c>
-      <c r="D238" s="4" t="s">
+      <c r="F238" s="4" t="s">
         <v>1083</v>
       </c>
-      <c r="E238" s="4" t="s">
+      <c r="G238" t="s">
         <v>1084</v>
       </c>
-      <c r="F238" s="4" t="s">
+      <c r="H238">
+        <v>1</v>
+      </c>
+      <c r="I238" t="s">
+        <v>10</v>
+      </c>
+      <c r="J238">
+        <v>159</v>
+      </c>
+      <c r="K238" t="s">
         <v>1085</v>
-      </c>
-      <c r="G238" t="s">
-        <v>24</v>
-      </c>
-      <c r="H238">
-        <v>1</v>
-      </c>
-      <c r="I238" t="s">
-        <v>10</v>
-      </c>
-      <c r="J238">
-        <v>0</v>
-      </c>
-      <c r="K238" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -13236,7 +13248,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C239" s="4" t="s">
         <v>1086</v>
@@ -13263,7 +13275,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
@@ -13271,7 +13283,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>1090</v>
@@ -13295,10 +13307,10 @@
         <v>10</v>
       </c>
       <c r="J240">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -13306,7 +13318,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>1094</v>
@@ -13321,7 +13333,7 @@
         <v>1097</v>
       </c>
       <c r="G241" t="s">
-        <v>604</v>
+        <v>24</v>
       </c>
       <c r="H241">
         <v>1</v>
@@ -13330,10 +13342,10 @@
         <v>10</v>
       </c>
       <c r="J241">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="K241" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -13341,7 +13353,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>1098</v>
@@ -13356,7 +13368,7 @@
         <v>1101</v>
       </c>
       <c r="G242" t="s">
-        <v>1102</v>
+        <v>604</v>
       </c>
       <c r="H242">
         <v>1</v>
@@ -13365,10 +13377,10 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>59</v>
+        <v>184</v>
       </c>
       <c r="K242" t="s">
-        <v>1103</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -13376,34 +13388,34 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C243" s="4" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E243" s="4" t="s">
         <v>1104</v>
       </c>
-      <c r="D243" s="4" t="s">
+      <c r="F243" s="4" t="s">
         <v>1105</v>
       </c>
-      <c r="E243" s="4" t="s">
+      <c r="G243" t="s">
         <v>1106</v>
       </c>
-      <c r="F243" s="4" t="s">
+      <c r="H243">
+        <v>1</v>
+      </c>
+      <c r="I243" t="s">
+        <v>10</v>
+      </c>
+      <c r="J243">
+        <v>62</v>
+      </c>
+      <c r="K243" t="s">
         <v>1107</v>
-      </c>
-      <c r="G243" t="s">
-        <v>626</v>
-      </c>
-      <c r="H243">
-        <v>1</v>
-      </c>
-      <c r="I243" t="s">
-        <v>10</v>
-      </c>
-      <c r="J243">
-        <v>100</v>
-      </c>
-      <c r="K243" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -13411,7 +13423,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>1108</v>
@@ -13435,10 +13447,10 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>56</v>
+        <v>233</v>
       </c>
       <c r="K244" t="s">
-        <v>1103</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -13446,7 +13458,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>1112</v>
@@ -13461,7 +13473,7 @@
         <v>1115</v>
       </c>
       <c r="G245" t="s">
-        <v>24</v>
+        <v>626</v>
       </c>
       <c r="H245">
         <v>1</v>
@@ -13470,10 +13482,10 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K245" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -13481,7 +13493,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>1116</v>
@@ -13505,10 +13517,10 @@
         <v>10</v>
       </c>
       <c r="J246">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="K246" t="s">
-        <v>1071</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -13516,7 +13528,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>1120</v>
@@ -13540,10 +13552,10 @@
         <v>10</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K247" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -13551,7 +13563,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>1124</v>
@@ -13575,10 +13587,10 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="K248" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -13586,7 +13598,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>1128</v>
@@ -13601,7 +13613,7 @@
         <v>1131</v>
       </c>
       <c r="G249" t="s">
-        <v>604</v>
+        <v>24</v>
       </c>
       <c r="H249">
         <v>1</v>
@@ -13610,10 +13622,10 @@
         <v>10</v>
       </c>
       <c r="J249">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="K249" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -13621,7 +13633,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>1132</v>
@@ -13636,7 +13648,7 @@
         <v>1135</v>
       </c>
       <c r="G250" t="s">
-        <v>24</v>
+        <v>604</v>
       </c>
       <c r="H250">
         <v>1</v>
@@ -13645,10 +13657,10 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>239</v>
+        <v>100</v>
       </c>
       <c r="K250" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -13656,7 +13668,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>1136</v>
@@ -13680,10 +13692,10 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="K251" t="s">
-        <v>1103</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -13691,7 +13703,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>1140</v>
@@ -13706,7 +13718,7 @@
         <v>1143</v>
       </c>
       <c r="G252" t="s">
-        <v>1080</v>
+        <v>24</v>
       </c>
       <c r="H252">
         <v>1</v>
@@ -13715,10 +13727,10 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="K252" t="s">
-        <v>1081</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -13726,7 +13738,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>1144</v>
@@ -13741,7 +13753,7 @@
         <v>1147</v>
       </c>
       <c r="G253" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="H253">
         <v>1</v>
@@ -13750,10 +13762,10 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="K253" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -13761,7 +13773,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>213</v>
+        <v>1070</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>1148</v>
@@ -13776,7 +13788,7 @@
         <v>1151</v>
       </c>
       <c r="G254" t="s">
-        <v>733</v>
+        <v>1084</v>
       </c>
       <c r="H254">
         <v>1</v>
@@ -13785,10 +13797,10 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="K254" t="s">
-        <v>1152</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -13799,31 +13811,31 @@
         <v>213</v>
       </c>
       <c r="C255" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D255" s="4" t="s">
         <v>1153</v>
       </c>
-      <c r="D255" s="4" t="s">
+      <c r="E255" s="4" t="s">
         <v>1154</v>
       </c>
-      <c r="E255" s="4" t="s">
+      <c r="F255" s="4" t="s">
         <v>1155</v>
       </c>
-      <c r="F255" s="4" t="s">
+      <c r="G255" t="s">
+        <v>733</v>
+      </c>
+      <c r="H255">
+        <v>1</v>
+      </c>
+      <c r="I255" t="s">
+        <v>10</v>
+      </c>
+      <c r="J255">
+        <v>132</v>
+      </c>
+      <c r="K255" t="s">
         <v>1156</v>
-      </c>
-      <c r="G255" t="s">
-        <v>24</v>
-      </c>
-      <c r="H255">
-        <v>1</v>
-      </c>
-      <c r="I255" t="s">
-        <v>10</v>
-      </c>
-      <c r="J255">
-        <v>377</v>
-      </c>
-      <c r="K255" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -13855,10 +13867,10 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K256" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -13866,22 +13878,22 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
+        <v>213</v>
+      </c>
+      <c r="C257" s="4" t="s">
         <v>1161</v>
       </c>
-      <c r="C257" s="4" t="s">
+      <c r="D257" s="4" t="s">
         <v>1162</v>
       </c>
-      <c r="D257" s="4" t="s">
+      <c r="E257" s="4" t="s">
         <v>1163</v>
       </c>
-      <c r="E257" s="4" t="s">
+      <c r="F257" s="4" t="s">
         <v>1164</v>
       </c>
-      <c r="F257" s="4" t="s">
-        <v>1165</v>
-      </c>
       <c r="G257" t="s">
-        <v>917</v>
+        <v>24</v>
       </c>
       <c r="H257">
         <v>1</v>
@@ -13890,10 +13902,10 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>96</v>
+        <v>151</v>
       </c>
       <c r="K257" t="s">
-        <v>1166</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -13901,34 +13913,34 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C258" s="4" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D258" s="4" t="s">
         <v>1167</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="E258" s="4" t="s">
         <v>1168</v>
       </c>
-      <c r="E258" s="4" t="s">
+      <c r="F258" s="4" t="s">
         <v>1169</v>
       </c>
-      <c r="F258" s="4" t="s">
+      <c r="G258" t="s">
+        <v>917</v>
+      </c>
+      <c r="H258">
+        <v>1</v>
+      </c>
+      <c r="I258" t="s">
+        <v>10</v>
+      </c>
+      <c r="J258">
+        <v>106</v>
+      </c>
+      <c r="K258" t="s">
         <v>1170</v>
-      </c>
-      <c r="G258" t="s">
-        <v>24</v>
-      </c>
-      <c r="H258">
-        <v>1</v>
-      </c>
-      <c r="I258" t="s">
-        <v>10</v>
-      </c>
-      <c r="J258">
-        <v>107</v>
-      </c>
-      <c r="K258" t="s">
-        <v>1166</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -13936,19 +13948,19 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>1090</v>
+        <v>1171</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="E259" s="4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="F259" s="4" t="s">
-        <v>1093</v>
+        <v>1174</v>
       </c>
       <c r="G259" t="s">
         <v>24</v>
@@ -13960,10 +13972,10 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="K259" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -13971,19 +13983,19 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>1173</v>
+        <v>1094</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>1176</v>
+        <v>1097</v>
       </c>
       <c r="G260" t="s">
         <v>24</v>
@@ -13995,10 +14007,10 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>107</v>
+        <v>155</v>
       </c>
       <c r="K260" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -14006,7 +14018,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C261" s="4" t="s">
         <v>1177</v>
@@ -14030,10 +14042,10 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K261" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -14041,7 +14053,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>1181</v>
@@ -14065,10 +14077,10 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="K262" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -14076,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>1185</v>
@@ -14091,7 +14103,7 @@
         <v>1188</v>
       </c>
       <c r="G263" t="s">
-        <v>884</v>
+        <v>24</v>
       </c>
       <c r="H263">
         <v>1</v>
@@ -14100,10 +14112,10 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K263" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -14111,7 +14123,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>1189</v>
@@ -14126,7 +14138,7 @@
         <v>1192</v>
       </c>
       <c r="G264" t="s">
-        <v>24</v>
+        <v>884</v>
       </c>
       <c r="H264">
         <v>1</v>
@@ -14135,10 +14147,10 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K264" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -14146,22 +14158,22 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>1140</v>
+        <v>1193</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E265" s="4" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F265" s="4" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G265" t="s">
-        <v>1080</v>
+        <v>24</v>
       </c>
       <c r="H265">
         <v>1</v>
@@ -14170,10 +14182,10 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>153</v>
+        <v>81</v>
       </c>
       <c r="K265" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -14181,22 +14193,22 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>1196</v>
+        <v>1165</v>
       </c>
       <c r="C266" s="4" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D266" s="4" t="s">
         <v>1197</v>
       </c>
-      <c r="D266" s="4" t="s">
+      <c r="E266" s="4" t="s">
         <v>1198</v>
       </c>
-      <c r="E266" s="4" t="s">
+      <c r="F266" s="4" t="s">
         <v>1199</v>
       </c>
-      <c r="F266" s="4" t="s">
-        <v>1200</v>
-      </c>
       <c r="G266" t="s">
-        <v>24</v>
+        <v>1084</v>
       </c>
       <c r="H266">
         <v>1</v>
@@ -14205,10 +14217,10 @@
         <v>10</v>
       </c>
       <c r="J266">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="K266" t="s">
-        <v>1201</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -14216,19 +14228,19 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C267" s="4" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D267" s="4" t="s">
         <v>1202</v>
       </c>
-      <c r="D267" s="4" t="s">
+      <c r="E267" s="4" t="s">
         <v>1203</v>
       </c>
-      <c r="E267" s="4" t="s">
+      <c r="F267" s="4" t="s">
         <v>1204</v>
-      </c>
-      <c r="F267" s="4" t="s">
-        <v>1205</v>
       </c>
       <c r="G267" t="s">
         <v>24</v>
@@ -14240,10 +14252,10 @@
         <v>10</v>
       </c>
       <c r="J267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -14251,7 +14263,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C268" s="4" t="s">
         <v>1206</v>
@@ -14275,10 +14287,10 @@
         <v>10</v>
       </c>
       <c r="J268">
-        <v>86</v>
+        <v>1</v>
       </c>
       <c r="K268" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -14286,7 +14298,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>1210</v>
@@ -14310,10 +14322,10 @@
         <v>10</v>
       </c>
       <c r="J269">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="K269" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -14321,7 +14333,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>1196</v>
+        <v>1200</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>1214</v>
@@ -14345,10 +14357,10 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>83</v>
+        <v>2</v>
       </c>
       <c r="K270" t="s">
-        <v>1201</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -14356,22 +14368,22 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C271" s="4" t="s">
         <v>1218</v>
       </c>
-      <c r="C271" s="4" t="s">
+      <c r="D271" s="4" t="s">
         <v>1219</v>
       </c>
-      <c r="D271" s="4" t="s">
+      <c r="E271" s="4" t="s">
         <v>1220</v>
       </c>
-      <c r="E271" s="4" t="s">
+      <c r="F271" s="4" t="s">
         <v>1221</v>
       </c>
-      <c r="F271" s="4" t="s">
-        <v>1222</v>
-      </c>
       <c r="G271" t="s">
-        <v>843</v>
+        <v>24</v>
       </c>
       <c r="H271">
         <v>1</v>
@@ -14380,10 +14392,10 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K271" t="s">
-        <v>1223</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -14391,34 +14403,34 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C272" s="4" t="s">
+        <v>1223</v>
+      </c>
+      <c r="D272" s="4" t="s">
         <v>1224</v>
       </c>
-      <c r="D272" s="4" t="s">
+      <c r="E272" s="4" t="s">
         <v>1225</v>
       </c>
-      <c r="E272" s="4" t="s">
+      <c r="F272" s="4" t="s">
         <v>1226</v>
       </c>
-      <c r="F272" s="4" t="s">
+      <c r="G272" t="s">
+        <v>843</v>
+      </c>
+      <c r="H272">
+        <v>1</v>
+      </c>
+      <c r="I272" t="s">
+        <v>10</v>
+      </c>
+      <c r="J272">
+        <v>64</v>
+      </c>
+      <c r="K272" t="s">
         <v>1227</v>
-      </c>
-      <c r="G272" t="s">
-        <v>24</v>
-      </c>
-      <c r="H272">
-        <v>1</v>
-      </c>
-      <c r="I272" t="s">
-        <v>10</v>
-      </c>
-      <c r="J272">
-        <v>70</v>
-      </c>
-      <c r="K272" t="s">
-        <v>1223</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
@@ -14426,7 +14438,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C273" s="4" t="s">
         <v>1228</v>
@@ -14441,7 +14453,7 @@
         <v>1231</v>
       </c>
       <c r="G273" t="s">
-        <v>604</v>
+        <v>24</v>
       </c>
       <c r="H273">
         <v>1</v>
@@ -14450,10 +14462,10 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="K273" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
@@ -14461,7 +14473,7 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>1232</v>
@@ -14476,7 +14488,7 @@
         <v>1235</v>
       </c>
       <c r="G274" t="s">
-        <v>861</v>
+        <v>604</v>
       </c>
       <c r="H274">
         <v>1</v>
@@ -14485,10 +14497,10 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="K274" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
@@ -14496,7 +14508,7 @@
         <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>1236</v>
@@ -14511,7 +14523,7 @@
         <v>1239</v>
       </c>
       <c r="G275" t="s">
-        <v>24</v>
+        <v>861</v>
       </c>
       <c r="H275">
         <v>1</v>
@@ -14520,10 +14532,10 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="K275" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -14531,7 +14543,7 @@
         <v>16</v>
       </c>
       <c r="B276" t="s">
-        <v>1218</v>
+        <v>1222</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>1240</v>
@@ -14555,10 +14567,10 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="K276" t="s">
-        <v>1223</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -14566,19 +14578,19 @@
         <v>16</v>
       </c>
       <c r="B277" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C277" s="4" t="s">
         <v>1244</v>
       </c>
-      <c r="C277" s="4" t="s">
+      <c r="D277" s="4" t="s">
         <v>1245</v>
       </c>
-      <c r="D277" s="4" t="s">
+      <c r="E277" s="4" t="s">
         <v>1246</v>
       </c>
-      <c r="E277" s="4" t="s">
+      <c r="F277" s="4" t="s">
         <v>1247</v>
-      </c>
-      <c r="F277" s="4" t="s">
-        <v>1248</v>
       </c>
       <c r="G277" t="s">
         <v>24</v>
@@ -14590,10 +14602,10 @@
         <v>10</v>
       </c>
       <c r="J277">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="K277" t="s">
-        <v>1249</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -14601,19 +14613,19 @@
         <v>16</v>
       </c>
       <c r="B278" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="C278" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D278" s="4" t="s">
         <v>1250</v>
       </c>
-      <c r="D278" s="4" t="s">
+      <c r="E278" s="4" t="s">
         <v>1251</v>
       </c>
-      <c r="E278" s="4" t="s">
+      <c r="F278" s="4" t="s">
         <v>1252</v>
-      </c>
-      <c r="F278" s="4" t="s">
-        <v>1253</v>
       </c>
       <c r="G278" t="s">
         <v>24</v>
@@ -14625,10 +14637,10 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="K278" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -14636,7 +14648,7 @@
         <v>16</v>
       </c>
       <c r="B279" t="s">
-        <v>1244</v>
+        <v>1248</v>
       </c>
       <c r="C279" s="4" t="s">
         <v>1254</v>
@@ -14660,30 +14672,30 @@
         <v>10</v>
       </c>
       <c r="J279">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K279" t="s">
-        <v>1249</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B280" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C280" s="4" t="s">
         <v>1258</v>
       </c>
-      <c r="C280" s="4" t="s">
+      <c r="D280" s="4" t="s">
         <v>1259</v>
       </c>
-      <c r="D280" s="4" t="s">
+      <c r="E280" s="4" t="s">
         <v>1260</v>
       </c>
-      <c r="E280" s="4" t="s">
+      <c r="F280" s="4" t="s">
         <v>1261</v>
-      </c>
-      <c r="F280" s="4" t="s">
-        <v>1262</v>
       </c>
       <c r="G280" t="s">
         <v>24</v>
@@ -14695,10 +14707,10 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>2606</v>
+        <v>54</v>
       </c>
       <c r="K280" t="s">
-        <v>1263</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -14706,19 +14718,19 @@
         <v>17</v>
       </c>
       <c r="B281" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="C281" s="4" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D281" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="D281" s="4" t="s">
+      <c r="E281" s="4" t="s">
         <v>1265</v>
       </c>
-      <c r="E281" s="4" t="s">
+      <c r="F281" s="4" t="s">
         <v>1266</v>
-      </c>
-      <c r="F281" s="4" t="s">
-        <v>1267</v>
       </c>
       <c r="G281" t="s">
         <v>24</v>
@@ -14730,10 +14742,10 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>903</v>
+        <v>2317</v>
       </c>
       <c r="K281" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -14741,7 +14753,7 @@
         <v>17</v>
       </c>
       <c r="B282" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="C282" s="4" t="s">
         <v>1268</v>
@@ -14765,10 +14777,10 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>1280</v>
+        <v>971</v>
       </c>
       <c r="K282" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -14776,7 +14788,7 @@
         <v>17</v>
       </c>
       <c r="B283" t="s">
-        <v>1258</v>
+        <v>1262</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>1272</v>
@@ -14800,10 +14812,10 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>1100</v>
+        <v>1068</v>
       </c>
       <c r="K283" t="s">
-        <v>1263</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -14811,19 +14823,19 @@
         <v>17</v>
       </c>
       <c r="B284" t="s">
+        <v>1262</v>
+      </c>
+      <c r="C284" s="4" t="s">
         <v>1276</v>
       </c>
-      <c r="C284" s="4" t="s">
+      <c r="D284" s="4" t="s">
         <v>1277</v>
       </c>
-      <c r="D284" s="4" t="s">
+      <c r="E284" s="4" t="s">
         <v>1278</v>
       </c>
-      <c r="E284" s="4" t="s">
+      <c r="F284" s="4" t="s">
         <v>1279</v>
-      </c>
-      <c r="F284" s="4" t="s">
-        <v>1280</v>
       </c>
       <c r="G284" t="s">
         <v>24</v>
@@ -14835,10 +14847,10 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>238</v>
+        <v>1050</v>
       </c>
       <c r="K284" t="s">
-        <v>1281</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -14846,19 +14858,19 @@
         <v>17</v>
       </c>
       <c r="B285" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C285" s="4" t="s">
+        <v>1281</v>
+      </c>
+      <c r="D285" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="D285" s="4" t="s">
+      <c r="E285" s="4" t="s">
         <v>1283</v>
       </c>
-      <c r="E285" s="4" t="s">
+      <c r="F285" s="4" t="s">
         <v>1284</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>1285</v>
       </c>
       <c r="G285" t="s">
         <v>24</v>
@@ -14870,10 +14882,10 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="K285" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -14881,7 +14893,7 @@
         <v>17</v>
       </c>
       <c r="B286" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>1286</v>
@@ -14905,10 +14917,10 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="K286" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -14916,7 +14928,7 @@
         <v>17</v>
       </c>
       <c r="B287" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>1290</v>
@@ -14928,7 +14940,7 @@
         <v>1292</v>
       </c>
       <c r="F287" s="4" t="s">
-        <v>1289</v>
+        <v>1293</v>
       </c>
       <c r="G287" t="s">
         <v>24</v>
@@ -14940,10 +14952,10 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="K287" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -14951,19 +14963,19 @@
         <v>17</v>
       </c>
       <c r="B288" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C288" s="4" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D288" s="4" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E288" s="4" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F288" s="4" t="s">
         <v>1293</v>
-      </c>
-      <c r="D288" s="4" t="s">
-        <v>1294</v>
-      </c>
-      <c r="E288" s="4" t="s">
-        <v>1295</v>
-      </c>
-      <c r="F288" s="4" t="s">
-        <v>1296</v>
       </c>
       <c r="G288" t="s">
         <v>24</v>
@@ -14975,10 +14987,10 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="K288" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -14986,7 +14998,7 @@
         <v>17</v>
       </c>
       <c r="B289" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>1297</v>
@@ -14998,7 +15010,7 @@
         <v>1299</v>
       </c>
       <c r="F289" s="4" t="s">
-        <v>1296</v>
+        <v>1300</v>
       </c>
       <c r="G289" t="s">
         <v>24</v>
@@ -15010,10 +15022,10 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="K289" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -15021,22 +15033,22 @@
         <v>17</v>
       </c>
       <c r="B290" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C290" s="4" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D290" s="4" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E290" s="4" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F290" s="4" t="s">
         <v>1300</v>
       </c>
-      <c r="D290" s="4" t="s">
-        <v>1301</v>
-      </c>
-      <c r="E290" s="4" t="s">
-        <v>1302</v>
-      </c>
-      <c r="F290" s="4" t="s">
-        <v>1280</v>
-      </c>
       <c r="G290" t="s">
-        <v>1303</v>
+        <v>24</v>
       </c>
       <c r="H290">
         <v>1</v>
@@ -15045,10 +15057,10 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>296</v>
+        <v>192</v>
       </c>
       <c r="K290" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -15056,7 +15068,7 @@
         <v>17</v>
       </c>
       <c r="B291" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>1304</v>
@@ -15068,11 +15080,11 @@
         <v>1306</v>
       </c>
       <c r="F291" s="4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G291" t="s">
         <v>1307</v>
       </c>
-      <c r="G291" t="s">
-        <v>24</v>
-      </c>
       <c r="H291">
         <v>1</v>
       </c>
@@ -15080,10 +15092,10 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>610</v>
+        <v>343</v>
       </c>
       <c r="K291" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -15091,7 +15103,7 @@
         <v>17</v>
       </c>
       <c r="B292" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>1308</v>
@@ -15103,7 +15115,7 @@
         <v>1310</v>
       </c>
       <c r="F292" s="4" t="s">
-        <v>1280</v>
+        <v>1311</v>
       </c>
       <c r="G292" t="s">
         <v>24</v>
@@ -15115,10 +15127,10 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>276</v>
+        <v>512</v>
       </c>
       <c r="K292" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -15126,22 +15138,22 @@
         <v>17</v>
       </c>
       <c r="B293" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="E293" s="4" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="G293" t="s">
-        <v>1314</v>
+        <v>24</v>
       </c>
       <c r="H293">
         <v>1</v>
@@ -15150,10 +15162,10 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="K293" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -15161,7 +15173,7 @@
         <v>17</v>
       </c>
       <c r="B294" t="s">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C294" s="4" t="s">
         <v>1315</v>
@@ -15173,10 +15185,10 @@
         <v>1317</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="G294" t="s">
-        <v>24</v>
+        <v>1318</v>
       </c>
       <c r="H294">
         <v>1</v>
@@ -15185,18 +15197,18 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>273</v>
+        <v>216</v>
       </c>
       <c r="K294" t="s">
-        <v>1281</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B295" t="s">
-        <v>1318</v>
+        <v>1280</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>1319</v>
@@ -15208,7 +15220,7 @@
         <v>1321</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>1322</v>
+        <v>1284</v>
       </c>
       <c r="G295" t="s">
         <v>24</v>
@@ -15220,10 +15232,10 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="K295" t="s">
-        <v>1323</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -15231,34 +15243,34 @@
         <v>18</v>
       </c>
       <c r="B296" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C296" s="4" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D296" s="4" t="s">
         <v>1324</v>
       </c>
-      <c r="C296" s="4" t="s">
+      <c r="E296" s="4" t="s">
         <v>1325</v>
       </c>
-      <c r="D296" s="4" t="s">
+      <c r="F296" s="4" t="s">
         <v>1326</v>
       </c>
-      <c r="E296" s="4" t="s">
+      <c r="G296" t="s">
+        <v>24</v>
+      </c>
+      <c r="H296">
+        <v>1</v>
+      </c>
+      <c r="I296" t="s">
+        <v>10</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296" t="s">
         <v>1327</v>
-      </c>
-      <c r="F296" s="4" t="s">
-        <v>1328</v>
-      </c>
-      <c r="G296" t="s">
-        <v>626</v>
-      </c>
-      <c r="H296">
-        <v>1</v>
-      </c>
-      <c r="I296" t="s">
-        <v>10</v>
-      </c>
-      <c r="J296">
-        <v>18</v>
-      </c>
-      <c r="K296" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -15266,34 +15278,34 @@
         <v>18</v>
       </c>
       <c r="B297" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="C297" s="4" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D297" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="D297" s="4" t="s">
+      <c r="E297" s="4" t="s">
         <v>1331</v>
       </c>
-      <c r="E297" s="4" t="s">
+      <c r="F297" s="4" t="s">
         <v>1332</v>
       </c>
-      <c r="F297" s="4" t="s">
+      <c r="G297" t="s">
+        <v>626</v>
+      </c>
+      <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297" t="s">
+        <v>10</v>
+      </c>
+      <c r="J297">
+        <v>22</v>
+      </c>
+      <c r="K297" t="s">
         <v>1333</v>
-      </c>
-      <c r="G297" t="s">
-        <v>1334</v>
-      </c>
-      <c r="H297">
-        <v>1</v>
-      </c>
-      <c r="I297" t="s">
-        <v>10</v>
-      </c>
-      <c r="J297">
-        <v>569</v>
-      </c>
-      <c r="K297" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -15301,23 +15313,23 @@
         <v>18</v>
       </c>
       <c r="B298" t="s">
-        <v>1324</v>
+        <v>1328</v>
       </c>
       <c r="C298" s="4" t="s">
+        <v>1334</v>
+      </c>
+      <c r="D298" s="4" t="s">
         <v>1335</v>
       </c>
-      <c r="D298" s="4" t="s">
+      <c r="E298" s="4" t="s">
         <v>1336</v>
       </c>
-      <c r="E298" s="4" t="s">
+      <c r="F298" s="4" t="s">
         <v>1337</v>
       </c>
-      <c r="F298" s="4" t="s">
+      <c r="G298" t="s">
         <v>1338</v>
       </c>
-      <c r="G298" t="s">
-        <v>212</v>
-      </c>
       <c r="H298">
         <v>1</v>
       </c>
@@ -15325,10 +15337,10 @@
         <v>10</v>
       </c>
       <c r="J298">
-        <v>6</v>
+        <v>119</v>
       </c>
       <c r="K298" t="s">
-        <v>1329</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -15336,22 +15348,22 @@
         <v>18</v>
       </c>
       <c r="B299" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C299" s="4" t="s">
         <v>1339</v>
       </c>
-      <c r="C299" s="4" t="s">
+      <c r="D299" s="4" t="s">
         <v>1340</v>
       </c>
-      <c r="D299" s="4" t="s">
+      <c r="E299" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="E299" s="4" t="s">
+      <c r="F299" s="4" t="s">
         <v>1342</v>
       </c>
-      <c r="F299" s="4" t="s">
-        <v>1343</v>
-      </c>
       <c r="G299" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="H299">
         <v>1</v>
@@ -15360,10 +15372,10 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>776</v>
+        <v>18</v>
       </c>
       <c r="K299" t="s">
-        <v>1344</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -15371,19 +15383,19 @@
         <v>18</v>
       </c>
       <c r="B300" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C300" s="4" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D300" s="4" t="s">
         <v>1345</v>
       </c>
-      <c r="D300" s="4" t="s">
+      <c r="E300" s="4" t="s">
         <v>1346</v>
       </c>
-      <c r="E300" s="4" t="s">
+      <c r="F300" s="4" t="s">
         <v>1347</v>
-      </c>
-      <c r="F300" s="4" t="s">
-        <v>1348</v>
       </c>
       <c r="G300" t="s">
         <v>24</v>
@@ -15395,10 +15407,10 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>40</v>
+        <v>548</v>
       </c>
       <c r="K300" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -15406,7 +15418,7 @@
         <v>18</v>
       </c>
       <c r="B301" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>1349</v>
@@ -15430,10 +15442,10 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>762</v>
+        <v>24</v>
       </c>
       <c r="K301" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -15441,7 +15453,7 @@
         <v>18</v>
       </c>
       <c r="B302" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>1353</v>
@@ -15465,10 +15477,10 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>707</v>
+        <v>573</v>
       </c>
       <c r="K302" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -15476,7 +15488,7 @@
         <v>18</v>
       </c>
       <c r="B303" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>1357</v>
@@ -15500,10 +15512,10 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>635</v>
+        <v>586</v>
       </c>
       <c r="K303" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -15511,7 +15523,7 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>1361</v>
@@ -15526,7 +15538,7 @@
         <v>1364</v>
       </c>
       <c r="G304" t="s">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="H304">
         <v>1</v>
@@ -15535,10 +15547,10 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>36</v>
+        <v>785</v>
       </c>
       <c r="K304" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -15546,7 +15558,7 @@
         <v>18</v>
       </c>
       <c r="B305" t="s">
-        <v>1339</v>
+        <v>1343</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>1365</v>
@@ -15561,7 +15573,7 @@
         <v>1368</v>
       </c>
       <c r="G305" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="H305">
         <v>1</v>
@@ -15570,10 +15582,10 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>1055</v>
+        <v>27</v>
       </c>
       <c r="K305" t="s">
-        <v>1344</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -15581,22 +15593,22 @@
         <v>18</v>
       </c>
       <c r="B306" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C306" s="4" t="s">
         <v>1369</v>
       </c>
-      <c r="C306" s="4" t="s">
+      <c r="D306" s="4" t="s">
         <v>1370</v>
       </c>
-      <c r="D306" s="4" t="s">
+      <c r="E306" s="4" t="s">
         <v>1371</v>
       </c>
-      <c r="E306" s="4" t="s">
+      <c r="F306" s="4" t="s">
         <v>1372</v>
       </c>
-      <c r="F306" s="4" t="s">
-        <v>1373</v>
-      </c>
       <c r="G306" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H306">
         <v>1</v>
@@ -15605,10 +15617,10 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>6</v>
+        <v>892</v>
       </c>
       <c r="K306" t="s">
-        <v>1374</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -15616,34 +15628,34 @@
         <v>18</v>
       </c>
       <c r="B307" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="C307" s="4" t="s">
+        <v>1374</v>
+      </c>
+      <c r="D307" s="4" t="s">
         <v>1375</v>
       </c>
-      <c r="D307" s="4" t="s">
+      <c r="E307" s="4" t="s">
         <v>1376</v>
       </c>
-      <c r="E307" s="4" t="s">
+      <c r="F307" s="4" t="s">
         <v>1377</v>
       </c>
-      <c r="F307" s="4" t="s">
+      <c r="G307" t="s">
+        <v>120</v>
+      </c>
+      <c r="H307">
+        <v>1</v>
+      </c>
+      <c r="I307" t="s">
+        <v>10</v>
+      </c>
+      <c r="J307">
+        <v>7</v>
+      </c>
+      <c r="K307" t="s">
         <v>1378</v>
-      </c>
-      <c r="G307" t="s">
-        <v>141</v>
-      </c>
-      <c r="H307">
-        <v>1</v>
-      </c>
-      <c r="I307" t="s">
-        <v>10</v>
-      </c>
-      <c r="J307">
-        <v>8</v>
-      </c>
-      <c r="K307" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
@@ -15651,7 +15663,7 @@
         <v>18</v>
       </c>
       <c r="B308" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="C308" s="4" t="s">
         <v>1379</v>
@@ -15666,7 +15678,7 @@
         <v>1382</v>
       </c>
       <c r="G308" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="H308">
         <v>1</v>
@@ -15675,10 +15687,10 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K308" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -15686,7 +15698,7 @@
         <v>18</v>
       </c>
       <c r="B309" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>1383</v>
@@ -15710,10 +15722,10 @@
         <v>10</v>
       </c>
       <c r="J309">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="K309" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
@@ -15721,7 +15733,7 @@
         <v>18</v>
       </c>
       <c r="B310" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>1387</v>
@@ -15736,7 +15748,7 @@
         <v>1390</v>
       </c>
       <c r="G310" t="s">
-        <v>866</v>
+        <v>180</v>
       </c>
       <c r="H310">
         <v>1</v>
@@ -15745,10 +15757,10 @@
         <v>10</v>
       </c>
       <c r="J310">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K310" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
@@ -15756,7 +15768,7 @@
         <v>18</v>
       </c>
       <c r="B311" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>1391</v>
@@ -15771,7 +15783,7 @@
         <v>1394</v>
       </c>
       <c r="G311" t="s">
-        <v>398</v>
+        <v>866</v>
       </c>
       <c r="H311">
         <v>1</v>
@@ -15780,10 +15792,10 @@
         <v>10</v>
       </c>
       <c r="J311">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="K311" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
@@ -15791,22 +15803,22 @@
         <v>18</v>
       </c>
       <c r="B312" t="s">
+        <v>1373</v>
+      </c>
+      <c r="C312" s="4" t="s">
         <v>1395</v>
       </c>
-      <c r="C312" s="4" t="s">
+      <c r="D312" s="4" t="s">
         <v>1396</v>
       </c>
-      <c r="D312" s="4" t="s">
+      <c r="E312" s="4" t="s">
         <v>1397</v>
       </c>
-      <c r="E312" s="4" t="s">
+      <c r="F312" s="4" t="s">
         <v>1398</v>
       </c>
-      <c r="F312" s="4" t="s">
-        <v>1399</v>
-      </c>
       <c r="G312" t="s">
-        <v>1400</v>
+        <v>398</v>
       </c>
       <c r="H312">
         <v>1</v>
@@ -15815,10 +15827,10 @@
         <v>10</v>
       </c>
       <c r="J312">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K312" t="s">
-        <v>1401</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
@@ -15826,34 +15838,34 @@
         <v>18</v>
       </c>
       <c r="B313" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="C313" s="4" t="s">
+        <v>1400</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>1401</v>
+      </c>
+      <c r="E313" s="4" t="s">
         <v>1402</v>
       </c>
-      <c r="D313" s="4" t="s">
+      <c r="F313" s="4" t="s">
         <v>1403</v>
       </c>
-      <c r="E313" s="4" t="s">
+      <c r="G313" t="s">
         <v>1404</v>
       </c>
-      <c r="F313" s="4" t="s">
+      <c r="H313">
+        <v>1</v>
+      </c>
+      <c r="I313" t="s">
+        <v>10</v>
+      </c>
+      <c r="J313">
+        <v>17</v>
+      </c>
+      <c r="K313" t="s">
         <v>1405</v>
-      </c>
-      <c r="G313" t="s">
-        <v>424</v>
-      </c>
-      <c r="H313">
-        <v>1</v>
-      </c>
-      <c r="I313" t="s">
-        <v>10</v>
-      </c>
-      <c r="J313">
-        <v>933</v>
-      </c>
-      <c r="K313" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
@@ -15861,7 +15873,7 @@
         <v>18</v>
       </c>
       <c r="B314" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>1406</v>
@@ -15876,7 +15888,7 @@
         <v>1409</v>
       </c>
       <c r="G314" t="s">
-        <v>1410</v>
+        <v>424</v>
       </c>
       <c r="H314">
         <v>1</v>
@@ -15885,10 +15897,10 @@
         <v>10</v>
       </c>
       <c r="J314">
-        <v>747</v>
+        <v>828</v>
       </c>
       <c r="K314" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
@@ -15896,34 +15908,69 @@
         <v>18</v>
       </c>
       <c r="B315" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="C315" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D315" s="4" t="s">
         <v>1411</v>
       </c>
-      <c r="D315" s="4" t="s">
+      <c r="E315" s="4" t="s">
         <v>1412</v>
       </c>
-      <c r="E315" s="4" t="s">
+      <c r="F315" s="4" t="s">
         <v>1413</v>
       </c>
-      <c r="F315" s="4" t="s">
+      <c r="G315" t="s">
         <v>1414</v>
       </c>
-      <c r="G315" t="s">
+      <c r="H315">
+        <v>1</v>
+      </c>
+      <c r="I315" t="s">
+        <v>10</v>
+      </c>
+      <c r="J315">
+        <v>1276</v>
+      </c>
+      <c r="K315" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>18</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C316" s="4" t="s">
         <v>1415</v>
       </c>
-      <c r="H315">
-        <v>1</v>
-      </c>
-      <c r="I315" t="s">
-        <v>10</v>
-      </c>
-      <c r="J315">
-        <v>740</v>
-      </c>
-      <c r="K315" t="s">
-        <v>1401</v>
+      <c r="D316" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G316" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H316">
+        <v>1</v>
+      </c>
+      <c r="I316" t="s">
+        <v>10</v>
+      </c>
+      <c r="J316">
+        <v>977</v>
+      </c>
+      <c r="K316" t="s">
+        <v>1405</v>
       </c>
     </row>
   </sheetData>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1437">
   <si>
     <t>검진 예약·접수 관리 프로그램 — 단위시험 목록</t>
   </si>
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 09:15</t>
+    <t>2026-09-15 09:34</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_09_15_19.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_09_34_11.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -4259,6 +4259,18 @@
     <t>05 §9.4 · 05 §9.11</t>
   </si>
   <si>
+    <t>SP RSV 02 는 WALKIN 으로도 오늘 예약을 세운다</t>
+  </si>
+  <si>
+    <t>실물 DB — 예약구분 WALKIN 으로 예약가능정보 조회(SP-RSV-01)와 예약 등록(SP-RSV-02)</t>
+  </si>
+  <si>
+    <t>01 「프로세스 간 통합 검증」 §3 이 현장 당일예약을 P02-01 의 WalkIn 재사용으로 정했고 02 기능정의 No 26 이 같은 자리다. 그런데 WALKIN 은 Presenter 단위시험 (fake)에만 있고 실물 DB 로는 한 번도 가 본 적이 없었다 — 예약구분은 어느 마감을 보는지를 가르는 값이라(NORMAL 은 예약마감, WALKIN 은 접수마감) fake 가 잘못 읽었으면 창구에서 당일예약만 조용히 막힌다.</t>
+  </si>
+  <si>
+    <t>WALKIN 으로 오늘을 물으면 결과코드 0 에 시간대가 서고, 그 자리로 등록하면 결과코드 0 · 상태코드 RSV 다 — WalkIn 도 예약을 세우고 접수는 그 다음이다.</t>
+  </si>
+  <si>
     <t>SP RSV 03 은 AEX 를 바꾸면 새 행버전을 내고 같은 값에는 1 이다</t>
   </si>
   <si>
@@ -4272,6 +4284,45 @@
   </si>
   <si>
     <t>05 §11.2 · 05 §16.3</t>
+  </si>
+  <si>
+    <t>SP RSV 03 은 시간대만 바꾸면 그 칸만 바뀐다</t>
+  </si>
+  <si>
+    <t>실물 DB — 예약 변경(SP-RSV-03)의 시간대만 변경 경로</t>
+  </si>
+  <si>
+    <t>02 No 20 과 05 §11.2 가 「시간대만 변경이면 TGT/NEX/AEX 를 재평가하지 않고 검사구성을 재조립하지 않는다」로 정했다. 재조립해 버리면 예약 당시의 검사구성이 조용히 달라지고, 수검자는 같은 날 다른 검사를 받게 된다. 조회 SP 의 SLOT 범위는 쟀지만 저장 경로는 실물로 밟은 적이 없다.</t>
+  </si>
+  <si>
+    <t>같은 날 반대 시간대로 바꾸면 결과코드 0 · 행버전이 바뀌고, 상세의 시간대코드가 그 칸이며 예약일은 그대로다.</t>
+  </si>
+  <si>
+    <t>SP RSV 03 은 예약일을 옮기고 상세가 그날로 바뀐다</t>
+  </si>
+  <si>
+    <t>실물 DB — 예약 변경(SP-RSV-03)의 예약일 변경 경로</t>
+  </si>
+  <si>
+    <t>01 §4 가 「예약일 변경 → 일정검증 → TGT 재판정 → NEX 재구성 → AEX 재검증 → 유효한 경우만 저장」으로 정했고 02 No 19 가 같은 자리다. 셋 중 이 갈래가 가장 많은 것을 다시 계산하는데(05 §11.2 변경 Matrix 의 첫 줄) 실물로는 한 번도 밟지 않았다 — 지금까지 실물로 돈 것은 AEX 만 바꾸는 갈래뿐이다.</t>
+  </si>
+  <si>
+    <t>앞으로 열려 있는 업무일로 옮기면 결과코드 0 · 상태 RSV · 행버전이 바뀌고, 상세 조회의 예약일이 실제로 그 날짜다 (요청만 받고 안 옮기면 화면이 거짓말을 한다).</t>
+  </si>
+  <si>
+    <t>01 §4 · 05 §11.2</t>
+  </si>
+  <si>
+    <t>운영시간 밖에서는 쓰기가 309 로 막힌다</t>
+  </si>
+  <si>
+    <t>실물 DB — 운영시간 밖에서 쓰기 SP 를 부른다 (F-COM-007)</t>
+  </si>
+  <si>
+    <t>02 No 36 이 「P01~P03 모든 업무 Action 은 DB 현재일이 업무 가능일이고 운영시간 안일 때만 수행된다」로 정했다. 그런데 이 폴더의 시험은 창을 열어 그 판정을 피해 왔다 — 피하는 것과 재는 것은 다르다. 창이 실제로 막는지 한 번은 봐야, 나머지 시험이 창 덕분에 도는 것인지 우연히 도는 것인지 갈린다.</t>
+  </si>
+  <si>
+    <t>창을 비운 채 예약을 등록하면 결과코드 309(운영시간 밖)로 막히고 RS1 이 없다. 창은 finally 로 되돌아오며, 그 뒤 같은 요청이 결과코드 0 으로 선다.</t>
   </si>
 </sst>
 </file>
@@ -4825,13 +4876,13 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4845,13 +4896,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C14" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D14" s="2">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -4900,7 +4951,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K316"/>
+  <dimension ref="A1:K320"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -5817,7 +5868,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="s">
         <v>115</v>
@@ -6202,7 +6253,7 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" t="s">
         <v>189</v>
@@ -6657,7 +6708,7 @@
         <v>10</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K50" t="s">
         <v>256</v>
@@ -6692,7 +6743,7 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="s">
         <v>256</v>
@@ -7007,7 +7058,7 @@
         <v>10</v>
       </c>
       <c r="J60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" t="s">
         <v>300</v>
@@ -7357,7 +7408,7 @@
         <v>10</v>
       </c>
       <c r="J70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="s">
         <v>300</v>
@@ -7567,7 +7618,7 @@
         <v>10</v>
       </c>
       <c r="J76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="s">
         <v>300</v>
@@ -7707,7 +7758,7 @@
         <v>10</v>
       </c>
       <c r="J80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="s">
         <v>393</v>
@@ -8232,7 +8283,7 @@
         <v>10</v>
       </c>
       <c r="J95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K95" t="s">
         <v>443</v>
@@ -8547,7 +8598,7 @@
         <v>10</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="s">
         <v>443</v>
@@ -8827,7 +8878,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -8932,7 +8983,7 @@
         <v>10</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115" t="s">
         <v>504</v>
@@ -10017,7 +10068,7 @@
         <v>10</v>
       </c>
       <c r="J146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="s">
         <v>656</v>
@@ -10087,7 +10138,7 @@
         <v>10</v>
       </c>
       <c r="J148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" t="s">
         <v>656</v>
@@ -10192,7 +10243,7 @@
         <v>10</v>
       </c>
       <c r="J151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K151" t="s">
         <v>656</v>
@@ -11032,7 +11083,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -11522,7 +11573,7 @@
         <v>10</v>
       </c>
       <c r="J189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K189" t="s">
         <v>844</v>
@@ -11977,7 +12028,7 @@
         <v>10</v>
       </c>
       <c r="J202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K202" t="s">
         <v>844</v>
@@ -12257,7 +12308,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>861</v>
+        <v>829</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12467,7 +12518,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12502,7 +12553,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12537,7 +12588,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12572,7 +12623,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>752</v>
+        <v>685</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12607,7 +12658,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1295</v>
+        <v>1010</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12677,7 +12728,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12712,7 +12763,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1639</v>
+        <v>1369</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12747,7 +12798,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12782,7 +12833,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12852,7 +12903,7 @@
         <v>10</v>
       </c>
       <c r="J227">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="K227" t="s">
         <v>1004</v>
@@ -12887,7 +12938,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12922,7 +12973,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -12957,7 +13008,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -12992,7 +13043,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="K231" t="s">
         <v>1004</v>
@@ -13027,7 +13078,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="K232" t="s">
         <v>1057</v>
@@ -13062,7 +13113,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="K233" t="s">
         <v>1057</v>
@@ -13097,7 +13148,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="K234" t="s">
         <v>1057</v>
@@ -13132,7 +13183,7 @@
         <v>10</v>
       </c>
       <c r="J235">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="K235" t="s">
         <v>1057</v>
@@ -13237,7 +13288,7 @@
         <v>10</v>
       </c>
       <c r="J238">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="K238" t="s">
         <v>1085</v>
@@ -13342,7 +13393,7 @@
         <v>10</v>
       </c>
       <c r="J241">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="K241" t="s">
         <v>1085</v>
@@ -13377,7 +13428,7 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="K242" t="s">
         <v>1085</v>
@@ -13412,7 +13463,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="K243" t="s">
         <v>1107</v>
@@ -13447,7 +13498,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="K244" t="s">
         <v>1085</v>
@@ -13482,7 +13533,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K245" t="s">
         <v>1107</v>
@@ -13517,7 +13568,7 @@
         <v>10</v>
       </c>
       <c r="J246">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="K246" t="s">
         <v>1107</v>
@@ -13552,7 +13603,7 @@
         <v>10</v>
       </c>
       <c r="J247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" t="s">
         <v>1075</v>
@@ -13622,7 +13673,7 @@
         <v>10</v>
       </c>
       <c r="J249">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="K249" t="s">
         <v>1085</v>
@@ -13657,7 +13708,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="K250" t="s">
         <v>1085</v>
@@ -13692,7 +13743,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="K251" t="s">
         <v>1085</v>
@@ -13727,7 +13778,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="K252" t="s">
         <v>1107</v>
@@ -13762,7 +13813,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K253" t="s">
         <v>1085</v>
@@ -13797,7 +13848,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="K254" t="s">
         <v>1085</v>
@@ -13832,7 +13883,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K255" t="s">
         <v>1156</v>
@@ -13867,7 +13918,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="K256" t="s">
         <v>1156</v>
@@ -13902,7 +13953,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="K257" t="s">
         <v>1156</v>
@@ -13937,7 +13988,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="K258" t="s">
         <v>1170</v>
@@ -13972,7 +14023,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="K259" t="s">
         <v>1170</v>
@@ -14007,7 +14058,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>155</v>
+        <v>101</v>
       </c>
       <c r="K260" t="s">
         <v>1170</v>
@@ -14042,7 +14093,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K261" t="s">
         <v>1170</v>
@@ -14077,7 +14128,7 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="K262" t="s">
         <v>1170</v>
@@ -14112,7 +14163,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="K263" t="s">
         <v>1170</v>
@@ -14147,7 +14198,7 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="K264" t="s">
         <v>1170</v>
@@ -14182,7 +14233,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="K265" t="s">
         <v>1170</v>
@@ -14217,7 +14268,7 @@
         <v>10</v>
       </c>
       <c r="J266">
-        <v>102</v>
+        <v>143</v>
       </c>
       <c r="K266" t="s">
         <v>1170</v>
@@ -14322,7 +14373,7 @@
         <v>10</v>
       </c>
       <c r="J269">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="K269" t="s">
         <v>1205</v>
@@ -14357,7 +14408,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K270" t="s">
         <v>1205</v>
@@ -14392,7 +14443,7 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K271" t="s">
         <v>1205</v>
@@ -14427,7 +14478,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K272" t="s">
         <v>1227</v>
@@ -14462,7 +14513,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K273" t="s">
         <v>1227</v>
@@ -14497,7 +14548,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="K274" t="s">
         <v>1227</v>
@@ -14532,7 +14583,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="K275" t="s">
         <v>1227</v>
@@ -14567,7 +14618,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="K276" t="s">
         <v>1227</v>
@@ -14602,7 +14653,7 @@
         <v>10</v>
       </c>
       <c r="J277">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="K277" t="s">
         <v>1227</v>
@@ -14672,7 +14723,7 @@
         <v>10</v>
       </c>
       <c r="J279">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K279" t="s">
         <v>1253</v>
@@ -14707,7 +14758,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="K280" t="s">
         <v>1253</v>
@@ -14742,7 +14793,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>2317</v>
+        <v>1902</v>
       </c>
       <c r="K281" t="s">
         <v>1267</v>
@@ -14777,7 +14828,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>971</v>
+        <v>282</v>
       </c>
       <c r="K282" t="s">
         <v>1267</v>
@@ -14812,7 +14863,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>1068</v>
+        <v>274</v>
       </c>
       <c r="K283" t="s">
         <v>1267</v>
@@ -14847,7 +14898,7 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>1050</v>
+        <v>251</v>
       </c>
       <c r="K284" t="s">
         <v>1267</v>
@@ -14882,7 +14933,7 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="K285" t="s">
         <v>1285</v>
@@ -14917,7 +14968,7 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="K286" t="s">
         <v>1285</v>
@@ -14987,7 +15038,7 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="K288" t="s">
         <v>1285</v>
@@ -15022,7 +15073,7 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K289" t="s">
         <v>1285</v>
@@ -15057,7 +15108,7 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="K290" t="s">
         <v>1285</v>
@@ -15092,7 +15143,7 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>343</v>
+        <v>248</v>
       </c>
       <c r="K291" t="s">
         <v>1285</v>
@@ -15127,7 +15178,7 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="K292" t="s">
         <v>1285</v>
@@ -15162,7 +15213,7 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="K293" t="s">
         <v>1285</v>
@@ -15197,7 +15248,7 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="K294" t="s">
         <v>1285</v>
@@ -15232,7 +15283,7 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="K295" t="s">
         <v>1285</v>
@@ -15302,7 +15353,7 @@
         <v>10</v>
       </c>
       <c r="J297">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="K297" t="s">
         <v>1333</v>
@@ -15337,7 +15388,7 @@
         <v>10</v>
       </c>
       <c r="J298">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="K298" t="s">
         <v>1333</v>
@@ -15372,7 +15423,7 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="K299" t="s">
         <v>1333</v>
@@ -15407,7 +15458,7 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>548</v>
+        <v>11</v>
       </c>
       <c r="K300" t="s">
         <v>1348</v>
@@ -15442,7 +15493,7 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="K301" t="s">
         <v>1348</v>
@@ -15477,7 +15528,7 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>573</v>
+        <v>6</v>
       </c>
       <c r="K302" t="s">
         <v>1348</v>
@@ -15512,7 +15563,7 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>586</v>
+        <v>8</v>
       </c>
       <c r="K303" t="s">
         <v>1348</v>
@@ -15547,7 +15598,7 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>785</v>
+        <v>8</v>
       </c>
       <c r="K304" t="s">
         <v>1348</v>
@@ -15582,7 +15633,7 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="K305" t="s">
         <v>1348</v>
@@ -15617,7 +15668,7 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>892</v>
+        <v>9</v>
       </c>
       <c r="K306" t="s">
         <v>1348</v>
@@ -15652,7 +15703,7 @@
         <v>10</v>
       </c>
       <c r="J307">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K307" t="s">
         <v>1378</v>
@@ -15687,7 +15738,7 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K308" t="s">
         <v>1378</v>
@@ -15722,7 +15773,7 @@
         <v>10</v>
       </c>
       <c r="J309">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K309" t="s">
         <v>1378</v>
@@ -15827,7 +15878,7 @@
         <v>10</v>
       </c>
       <c r="J312">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="K312" t="s">
         <v>1378</v>
@@ -15862,7 +15913,7 @@
         <v>10</v>
       </c>
       <c r="J313">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K313" t="s">
         <v>1405</v>
@@ -15897,7 +15948,7 @@
         <v>10</v>
       </c>
       <c r="J314">
-        <v>828</v>
+        <v>77</v>
       </c>
       <c r="K314" t="s">
         <v>1405</v>
@@ -15932,7 +15983,7 @@
         <v>10</v>
       </c>
       <c r="J315">
-        <v>1276</v>
+        <v>30</v>
       </c>
       <c r="K315" t="s">
         <v>1405</v>
@@ -15958,18 +16009,158 @@
         <v>1418</v>
       </c>
       <c r="G316" t="s">
+        <v>24</v>
+      </c>
+      <c r="H316">
+        <v>1</v>
+      </c>
+      <c r="I316" t="s">
+        <v>10</v>
+      </c>
+      <c r="J316">
+        <v>6</v>
+      </c>
+      <c r="K316" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>18</v>
+      </c>
+      <c r="B317" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C317" s="4" t="s">
         <v>1419</v>
       </c>
-      <c r="H316">
-        <v>1</v>
-      </c>
-      <c r="I316" t="s">
-        <v>10</v>
-      </c>
-      <c r="J316">
-        <v>977</v>
-      </c>
-      <c r="K316" t="s">
+      <c r="D317" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G317" t="s">
+        <v>1423</v>
+      </c>
+      <c r="H317">
+        <v>1</v>
+      </c>
+      <c r="I317" t="s">
+        <v>10</v>
+      </c>
+      <c r="J317">
+        <v>151</v>
+      </c>
+      <c r="K317" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>18</v>
+      </c>
+      <c r="B318" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="G318" t="s">
+        <v>703</v>
+      </c>
+      <c r="H318">
+        <v>1</v>
+      </c>
+      <c r="I318" t="s">
+        <v>10</v>
+      </c>
+      <c r="J318">
+        <v>10</v>
+      </c>
+      <c r="K318" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>18</v>
+      </c>
+      <c r="B319" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="G319" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H319">
+        <v>1</v>
+      </c>
+      <c r="I319" t="s">
+        <v>10</v>
+      </c>
+      <c r="J319">
+        <v>36</v>
+      </c>
+      <c r="K319" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>18</v>
+      </c>
+      <c r="B320" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="G320" t="s">
+        <v>24</v>
+      </c>
+      <c r="H320">
+        <v>1</v>
+      </c>
+      <c r="I320" t="s">
+        <v>10</v>
+      </c>
+      <c r="J320">
+        <v>9</v>
+      </c>
+      <c r="K320" t="s">
         <v>1405</v>
       </c>
     </row>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2910" uniqueCount="1437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="1441">
   <si>
     <t>검진 예약·접수 관리 프로그램 — 단위시험 목록</t>
   </si>
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 09:34</t>
+    <t>2026-09-15 09:48</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_09_34_11.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_09_48_23.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -3081,6 +3081,18 @@
   </si>
   <si>
     <t>Shell 핸들이 만들어지고, 그룹 없는 Page 를 누르면 선택된 Page 가 바뀌지 않으며, 그렇게 열리지 않는 문은 「휴무일 관리」 하나뿐이다.</t>
+  </si>
+  <si>
+    <t>대화상자 버튼도 아이콘을 갖는다</t>
+  </si>
+  <si>
+    <t>DLG-HOL-01 (FrmHoliday) — 대화상자 버튼의 아이콘</t>
+  </si>
+  <si>
+    <t>2026-09-15 사용자가 물어서 드러난 자리다. 리본에만 아이콘을 넣어 두어 대화상자는 글자만 남아 있었고, 창구에서는 절반만 바뀐 화면으로 보인다. 휴무일 관리는 버튼이 다섯으로 가장 많아 하나를 빠뜨리기도 가장 쉽다.</t>
+  </si>
+  <si>
+    <t>폼 안의 SimpleButton 전부가 SvgImage 를 갖는다. 훑은 버튼이 0개이면 아무것도 재지 않은 green 이므로 그것도 실패로 센다.</t>
   </si>
   <si>
     <t>리본 버튼은 전부 아이콘을 갖는다</t>
@@ -4836,13 +4848,13 @@
         <v>16</v>
       </c>
       <c r="B11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D11">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4896,13 +4908,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C14" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D14" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -4951,7 +4963,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K320"/>
+  <dimension ref="A1:K321"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -5868,7 +5880,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="s">
         <v>115</v>
@@ -6708,7 +6720,7 @@
         <v>10</v>
       </c>
       <c r="J50">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K50" t="s">
         <v>256</v>
@@ -6743,7 +6755,7 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="s">
         <v>256</v>
@@ -7058,7 +7070,7 @@
         <v>10</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" t="s">
         <v>300</v>
@@ -7548,7 +7560,7 @@
         <v>10</v>
       </c>
       <c r="J74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K74" t="s">
         <v>300</v>
@@ -7758,7 +7770,7 @@
         <v>10</v>
       </c>
       <c r="J80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="s">
         <v>393</v>
@@ -8283,7 +8295,7 @@
         <v>10</v>
       </c>
       <c r="J95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K95" t="s">
         <v>443</v>
@@ -8598,7 +8610,7 @@
         <v>10</v>
       </c>
       <c r="J104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="s">
         <v>443</v>
@@ -8878,7 +8890,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -9858,7 +9870,7 @@
         <v>10</v>
       </c>
       <c r="J140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" t="s">
         <v>656</v>
@@ -10068,7 +10080,7 @@
         <v>10</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="s">
         <v>656</v>
@@ -10243,7 +10255,7 @@
         <v>10</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" t="s">
         <v>656</v>
@@ -10873,7 +10885,7 @@
         <v>10</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K169" t="s">
         <v>656</v>
@@ -11083,7 +11095,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -12028,7 +12040,7 @@
         <v>10</v>
       </c>
       <c r="J202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K202" t="s">
         <v>844</v>
@@ -12308,7 +12320,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12518,7 +12530,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12553,7 +12565,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12588,7 +12600,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12623,7 +12635,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>685</v>
+        <v>844</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12658,7 +12670,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1010</v>
+        <v>1233</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12693,7 +12705,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12728,7 +12740,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12763,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1369</v>
+        <v>1641</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12798,7 +12810,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12833,7 +12845,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12868,7 +12880,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12894,7 +12906,7 @@
         <v>1034</v>
       </c>
       <c r="G227" t="s">
-        <v>1035</v>
+        <v>24</v>
       </c>
       <c r="H227">
         <v>1</v>
@@ -12903,7 +12915,7 @@
         <v>10</v>
       </c>
       <c r="J227">
-        <v>101</v>
+        <v>2</v>
       </c>
       <c r="K227" t="s">
         <v>1004</v>
@@ -12917,20 +12929,20 @@
         <v>999</v>
       </c>
       <c r="C228" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D228" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="D228" s="4" t="s">
+      <c r="E228" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="E228" s="4" t="s">
+      <c r="F228" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="F228" s="4" t="s">
+      <c r="G228" t="s">
         <v>1039</v>
       </c>
-      <c r="G228" t="s">
-        <v>24</v>
-      </c>
       <c r="H228">
         <v>1</v>
       </c>
@@ -12938,7 +12950,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>149</v>
+        <v>113</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12973,7 +12985,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -12999,7 +13011,7 @@
         <v>1047</v>
       </c>
       <c r="G230" t="s">
-        <v>875</v>
+        <v>24</v>
       </c>
       <c r="H230">
         <v>1</v>
@@ -13008,7 +13020,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -13034,7 +13046,7 @@
         <v>1051</v>
       </c>
       <c r="G231" t="s">
-        <v>580</v>
+        <v>875</v>
       </c>
       <c r="H231">
         <v>1</v>
@@ -13043,7 +13055,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="K231" t="s">
         <v>1004</v>
@@ -13054,22 +13066,22 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
+        <v>999</v>
+      </c>
+      <c r="C232" s="4" t="s">
         <v>1052</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="D232" s="4" t="s">
         <v>1053</v>
       </c>
-      <c r="D232" s="4" t="s">
+      <c r="E232" s="4" t="s">
         <v>1054</v>
       </c>
-      <c r="E232" s="4" t="s">
+      <c r="F232" s="4" t="s">
         <v>1055</v>
       </c>
-      <c r="F232" s="4" t="s">
-        <v>1056</v>
-      </c>
       <c r="G232" t="s">
-        <v>24</v>
+        <v>580</v>
       </c>
       <c r="H232">
         <v>1</v>
@@ -13078,10 +13090,10 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>172</v>
+        <v>103</v>
       </c>
       <c r="K232" t="s">
-        <v>1057</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -13089,19 +13101,19 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C233" s="4" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D233" s="4" t="s">
         <v>1058</v>
       </c>
-      <c r="D233" s="4" t="s">
+      <c r="E233" s="4" t="s">
         <v>1059</v>
       </c>
-      <c r="E233" s="4" t="s">
+      <c r="F233" s="4" t="s">
         <v>1060</v>
-      </c>
-      <c r="F233" s="4" t="s">
-        <v>1061</v>
       </c>
       <c r="G233" t="s">
         <v>24</v>
@@ -13113,10 +13125,10 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="K233" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -13124,7 +13136,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C234" s="4" t="s">
         <v>1062</v>
@@ -13148,10 +13160,10 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="K234" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -13159,7 +13171,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C235" s="4" t="s">
         <v>1066</v>
@@ -13174,7 +13186,7 @@
         <v>1069</v>
       </c>
       <c r="G235" t="s">
-        <v>473</v>
+        <v>24</v>
       </c>
       <c r="H235">
         <v>1</v>
@@ -13183,10 +13195,10 @@
         <v>10</v>
       </c>
       <c r="J235">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="K235" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -13194,22 +13206,22 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C236" s="4" t="s">
         <v>1070</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="D236" s="4" t="s">
         <v>1071</v>
       </c>
-      <c r="D236" s="4" t="s">
+      <c r="E236" s="4" t="s">
         <v>1072</v>
       </c>
-      <c r="E236" s="4" t="s">
+      <c r="F236" s="4" t="s">
         <v>1073</v>
       </c>
-      <c r="F236" s="4" t="s">
-        <v>1074</v>
-      </c>
       <c r="G236" t="s">
-        <v>580</v>
+        <v>473</v>
       </c>
       <c r="H236">
         <v>1</v>
@@ -13218,10 +13230,10 @@
         <v>10</v>
       </c>
       <c r="J236">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="K236" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -13229,34 +13241,34 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C237" s="4" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D237" s="4" t="s">
         <v>1076</v>
       </c>
-      <c r="D237" s="4" t="s">
+      <c r="E237" s="4" t="s">
         <v>1077</v>
       </c>
-      <c r="E237" s="4" t="s">
+      <c r="F237" s="4" t="s">
         <v>1078</v>
       </c>
-      <c r="F237" s="4" t="s">
+      <c r="G237" t="s">
+        <v>580</v>
+      </c>
+      <c r="H237">
+        <v>1</v>
+      </c>
+      <c r="I237" t="s">
+        <v>10</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237" t="s">
         <v>1079</v>
-      </c>
-      <c r="G237" t="s">
-        <v>24</v>
-      </c>
-      <c r="H237">
-        <v>1</v>
-      </c>
-      <c r="I237" t="s">
-        <v>10</v>
-      </c>
-      <c r="J237">
-        <v>0</v>
-      </c>
-      <c r="K237" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -13264,7 +13276,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C238" s="4" t="s">
         <v>1080</v>
@@ -13279,7 +13291,7 @@
         <v>1083</v>
       </c>
       <c r="G238" t="s">
-        <v>1084</v>
+        <v>24</v>
       </c>
       <c r="H238">
         <v>1</v>
@@ -13288,10 +13300,10 @@
         <v>10</v>
       </c>
       <c r="J238">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K238" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -13299,34 +13311,34 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C239" s="4" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D239" s="4" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E239" s="4" t="s">
         <v>1086</v>
       </c>
-      <c r="D239" s="4" t="s">
+      <c r="F239" s="4" t="s">
         <v>1087</v>
       </c>
-      <c r="E239" s="4" t="s">
+      <c r="G239" t="s">
         <v>1088</v>
       </c>
-      <c r="F239" s="4" t="s">
+      <c r="H239">
+        <v>1</v>
+      </c>
+      <c r="I239" t="s">
+        <v>10</v>
+      </c>
+      <c r="J239">
+        <v>176</v>
+      </c>
+      <c r="K239" t="s">
         <v>1089</v>
-      </c>
-      <c r="G239" t="s">
-        <v>24</v>
-      </c>
-      <c r="H239">
-        <v>1</v>
-      </c>
-      <c r="I239" t="s">
-        <v>10</v>
-      </c>
-      <c r="J239">
-        <v>0</v>
-      </c>
-      <c r="K239" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
@@ -13334,7 +13346,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C240" s="4" t="s">
         <v>1090</v>
@@ -13361,7 +13373,7 @@
         <v>0</v>
       </c>
       <c r="K240" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -13369,7 +13381,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C241" s="4" t="s">
         <v>1094</v>
@@ -13393,10 +13405,10 @@
         <v>10</v>
       </c>
       <c r="J241">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="K241" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -13404,7 +13416,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C242" s="4" t="s">
         <v>1098</v>
@@ -13419,7 +13431,7 @@
         <v>1101</v>
       </c>
       <c r="G242" t="s">
-        <v>604</v>
+        <v>24</v>
       </c>
       <c r="H242">
         <v>1</v>
@@ -13428,10 +13440,10 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K242" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -13439,7 +13451,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C243" s="4" t="s">
         <v>1102</v>
@@ -13454,7 +13466,7 @@
         <v>1105</v>
       </c>
       <c r="G243" t="s">
-        <v>1106</v>
+        <v>604</v>
       </c>
       <c r="H243">
         <v>1</v>
@@ -13463,10 +13475,10 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="K243" t="s">
-        <v>1107</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -13474,34 +13486,34 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C244" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E244" s="4" t="s">
         <v>1108</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="F244" s="4" t="s">
         <v>1109</v>
       </c>
-      <c r="E244" s="4" t="s">
+      <c r="G244" t="s">
         <v>1110</v>
       </c>
-      <c r="F244" s="4" t="s">
+      <c r="H244">
+        <v>1</v>
+      </c>
+      <c r="I244" t="s">
+        <v>10</v>
+      </c>
+      <c r="J244">
+        <v>63</v>
+      </c>
+      <c r="K244" t="s">
         <v>1111</v>
-      </c>
-      <c r="G244" t="s">
-        <v>626</v>
-      </c>
-      <c r="H244">
-        <v>1</v>
-      </c>
-      <c r="I244" t="s">
-        <v>10</v>
-      </c>
-      <c r="J244">
-        <v>90</v>
-      </c>
-      <c r="K244" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -13509,7 +13521,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>1112</v>
@@ -13533,10 +13545,10 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="K245" t="s">
-        <v>1107</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -13544,7 +13556,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>1116</v>
@@ -13559,7 +13571,7 @@
         <v>1119</v>
       </c>
       <c r="G246" t="s">
-        <v>24</v>
+        <v>626</v>
       </c>
       <c r="H246">
         <v>1</v>
@@ -13568,10 +13580,10 @@
         <v>10</v>
       </c>
       <c r="J246">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K246" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -13579,7 +13591,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>1120</v>
@@ -13603,10 +13615,10 @@
         <v>10</v>
       </c>
       <c r="J247">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="K247" t="s">
-        <v>1075</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -13614,7 +13626,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C248" s="4" t="s">
         <v>1124</v>
@@ -13638,10 +13650,10 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K248" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -13649,7 +13661,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C249" s="4" t="s">
         <v>1128</v>
@@ -13673,10 +13685,10 @@
         <v>10</v>
       </c>
       <c r="J249">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="K249" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -13684,7 +13696,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>1132</v>
@@ -13699,7 +13711,7 @@
         <v>1135</v>
       </c>
       <c r="G250" t="s">
-        <v>604</v>
+        <v>24</v>
       </c>
       <c r="H250">
         <v>1</v>
@@ -13708,10 +13720,10 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="K250" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -13719,7 +13731,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>1136</v>
@@ -13734,7 +13746,7 @@
         <v>1139</v>
       </c>
       <c r="G251" t="s">
-        <v>24</v>
+        <v>604</v>
       </c>
       <c r="H251">
         <v>1</v>
@@ -13743,10 +13755,10 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K251" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -13754,7 +13766,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>1140</v>
@@ -13778,10 +13790,10 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>73</v>
+        <v>241</v>
       </c>
       <c r="K252" t="s">
-        <v>1107</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -13789,7 +13801,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>1144</v>
@@ -13804,7 +13816,7 @@
         <v>1147</v>
       </c>
       <c r="G253" t="s">
-        <v>1084</v>
+        <v>24</v>
       </c>
       <c r="H253">
         <v>1</v>
@@ -13813,10 +13825,10 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="K253" t="s">
-        <v>1085</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -13824,7 +13836,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>1148</v>
@@ -13839,7 +13851,7 @@
         <v>1151</v>
       </c>
       <c r="G254" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="H254">
         <v>1</v>
@@ -13848,10 +13860,10 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>83</v>
+        <v>156</v>
       </c>
       <c r="K254" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -13859,7 +13871,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>213</v>
+        <v>1074</v>
       </c>
       <c r="C255" s="4" t="s">
         <v>1152</v>
@@ -13874,7 +13886,7 @@
         <v>1155</v>
       </c>
       <c r="G255" t="s">
-        <v>733</v>
+        <v>1088</v>
       </c>
       <c r="H255">
         <v>1</v>
@@ -13883,10 +13895,10 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K255" t="s">
-        <v>1156</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -13897,31 +13909,31 @@
         <v>213</v>
       </c>
       <c r="C256" s="4" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D256" s="4" t="s">
         <v>1157</v>
       </c>
-      <c r="D256" s="4" t="s">
+      <c r="E256" s="4" t="s">
         <v>1158</v>
       </c>
-      <c r="E256" s="4" t="s">
+      <c r="F256" s="4" t="s">
         <v>1159</v>
       </c>
-      <c r="F256" s="4" t="s">
+      <c r="G256" t="s">
+        <v>733</v>
+      </c>
+      <c r="H256">
+        <v>1</v>
+      </c>
+      <c r="I256" t="s">
+        <v>10</v>
+      </c>
+      <c r="J256">
+        <v>172</v>
+      </c>
+      <c r="K256" t="s">
         <v>1160</v>
-      </c>
-      <c r="G256" t="s">
-        <v>24</v>
-      </c>
-      <c r="H256">
-        <v>1</v>
-      </c>
-      <c r="I256" t="s">
-        <v>10</v>
-      </c>
-      <c r="J256">
-        <v>146</v>
-      </c>
-      <c r="K256" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -13953,10 +13965,10 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>133</v>
+        <v>282</v>
       </c>
       <c r="K257" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -13964,22 +13976,22 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
+        <v>213</v>
+      </c>
+      <c r="C258" s="4" t="s">
         <v>1165</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="D258" s="4" t="s">
         <v>1166</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="E258" s="4" t="s">
         <v>1167</v>
       </c>
-      <c r="E258" s="4" t="s">
+      <c r="F258" s="4" t="s">
         <v>1168</v>
       </c>
-      <c r="F258" s="4" t="s">
-        <v>1169</v>
-      </c>
       <c r="G258" t="s">
-        <v>917</v>
+        <v>24</v>
       </c>
       <c r="H258">
         <v>1</v>
@@ -13988,10 +14000,10 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>81</v>
+        <v>232</v>
       </c>
       <c r="K258" t="s">
-        <v>1170</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -13999,34 +14011,34 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C259" s="4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="D259" s="4" t="s">
         <v>1171</v>
       </c>
-      <c r="D259" s="4" t="s">
+      <c r="E259" s="4" t="s">
         <v>1172</v>
       </c>
-      <c r="E259" s="4" t="s">
+      <c r="F259" s="4" t="s">
         <v>1173</v>
       </c>
-      <c r="F259" s="4" t="s">
+      <c r="G259" t="s">
+        <v>917</v>
+      </c>
+      <c r="H259">
+        <v>1</v>
+      </c>
+      <c r="I259" t="s">
+        <v>10</v>
+      </c>
+      <c r="J259">
+        <v>103</v>
+      </c>
+      <c r="K259" t="s">
         <v>1174</v>
-      </c>
-      <c r="G259" t="s">
-        <v>24</v>
-      </c>
-      <c r="H259">
-        <v>1</v>
-      </c>
-      <c r="I259" t="s">
-        <v>10</v>
-      </c>
-      <c r="J259">
-        <v>107</v>
-      </c>
-      <c r="K259" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -14034,19 +14046,19 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>1094</v>
+        <v>1175</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="E260" s="4" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F260" s="4" t="s">
-        <v>1097</v>
+        <v>1178</v>
       </c>
       <c r="G260" t="s">
         <v>24</v>
@@ -14058,10 +14070,10 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="K260" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -14069,19 +14081,19 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>1177</v>
+        <v>1098</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E261" s="4" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F261" s="4" t="s">
-        <v>1180</v>
+        <v>1101</v>
       </c>
       <c r="G261" t="s">
         <v>24</v>
@@ -14093,10 +14105,10 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="K261" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -14104,7 +14116,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C262" s="4" t="s">
         <v>1181</v>
@@ -14128,10 +14140,10 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="K262" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -14139,7 +14151,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C263" s="4" t="s">
         <v>1185</v>
@@ -14163,10 +14175,10 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="K263" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -14174,7 +14186,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C264" s="4" t="s">
         <v>1189</v>
@@ -14189,7 +14201,7 @@
         <v>1192</v>
       </c>
       <c r="G264" t="s">
-        <v>884</v>
+        <v>24</v>
       </c>
       <c r="H264">
         <v>1</v>
@@ -14198,10 +14210,10 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>83</v>
+        <v>172</v>
       </c>
       <c r="K264" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -14209,7 +14221,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C265" s="4" t="s">
         <v>1193</v>
@@ -14224,7 +14236,7 @@
         <v>1196</v>
       </c>
       <c r="G265" t="s">
-        <v>24</v>
+        <v>884</v>
       </c>
       <c r="H265">
         <v>1</v>
@@ -14233,10 +14245,10 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>89</v>
+        <v>140</v>
       </c>
       <c r="K265" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -14244,22 +14256,22 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>1144</v>
+        <v>1197</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E266" s="4" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F266" s="4" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="G266" t="s">
-        <v>1084</v>
+        <v>24</v>
       </c>
       <c r="H266">
         <v>1</v>
@@ -14268,10 +14280,10 @@
         <v>10</v>
       </c>
       <c r="J266">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="K266" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -14279,22 +14291,22 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>1200</v>
+        <v>1169</v>
       </c>
       <c r="C267" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D267" s="4" t="s">
         <v>1201</v>
       </c>
-      <c r="D267" s="4" t="s">
+      <c r="E267" s="4" t="s">
         <v>1202</v>
       </c>
-      <c r="E267" s="4" t="s">
+      <c r="F267" s="4" t="s">
         <v>1203</v>
       </c>
-      <c r="F267" s="4" t="s">
-        <v>1204</v>
-      </c>
       <c r="G267" t="s">
-        <v>24</v>
+        <v>1088</v>
       </c>
       <c r="H267">
         <v>1</v>
@@ -14303,10 +14315,10 @@
         <v>10</v>
       </c>
       <c r="J267">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="K267" t="s">
-        <v>1205</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -14314,19 +14326,19 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="C268" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D268" s="4" t="s">
         <v>1206</v>
       </c>
-      <c r="D268" s="4" t="s">
+      <c r="E268" s="4" t="s">
         <v>1207</v>
       </c>
-      <c r="E268" s="4" t="s">
+      <c r="F268" s="4" t="s">
         <v>1208</v>
-      </c>
-      <c r="F268" s="4" t="s">
-        <v>1209</v>
       </c>
       <c r="G268" t="s">
         <v>24</v>
@@ -14338,10 +14350,10 @@
         <v>10</v>
       </c>
       <c r="J268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K268" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -14349,7 +14361,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="C269" s="4" t="s">
         <v>1210</v>
@@ -14373,10 +14385,10 @@
         <v>10</v>
       </c>
       <c r="J269">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="K269" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -14384,7 +14396,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="C270" s="4" t="s">
         <v>1214</v>
@@ -14408,10 +14420,10 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>3</v>
+        <v>87</v>
       </c>
       <c r="K270" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -14419,7 +14431,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>1200</v>
+        <v>1204</v>
       </c>
       <c r="C271" s="4" t="s">
         <v>1218</v>
@@ -14443,10 +14455,10 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="K271" t="s">
-        <v>1205</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
@@ -14454,22 +14466,22 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C272" s="4" t="s">
         <v>1222</v>
       </c>
-      <c r="C272" s="4" t="s">
+      <c r="D272" s="4" t="s">
         <v>1223</v>
       </c>
-      <c r="D272" s="4" t="s">
+      <c r="E272" s="4" t="s">
         <v>1224</v>
       </c>
-      <c r="E272" s="4" t="s">
+      <c r="F272" s="4" t="s">
         <v>1225</v>
       </c>
-      <c r="F272" s="4" t="s">
-        <v>1226</v>
-      </c>
       <c r="G272" t="s">
-        <v>843</v>
+        <v>24</v>
       </c>
       <c r="H272">
         <v>1</v>
@@ -14478,10 +14490,10 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="K272" t="s">
-        <v>1227</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="273" spans="1:11" x14ac:dyDescent="0.25">
@@ -14489,34 +14501,34 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C273" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D273" s="4" t="s">
         <v>1228</v>
       </c>
-      <c r="D273" s="4" t="s">
+      <c r="E273" s="4" t="s">
         <v>1229</v>
       </c>
-      <c r="E273" s="4" t="s">
+      <c r="F273" s="4" t="s">
         <v>1230</v>
       </c>
-      <c r="F273" s="4" t="s">
+      <c r="G273" t="s">
+        <v>843</v>
+      </c>
+      <c r="H273">
+        <v>1</v>
+      </c>
+      <c r="I273" t="s">
+        <v>10</v>
+      </c>
+      <c r="J273">
+        <v>73</v>
+      </c>
+      <c r="K273" t="s">
         <v>1231</v>
-      </c>
-      <c r="G273" t="s">
-        <v>24</v>
-      </c>
-      <c r="H273">
-        <v>1</v>
-      </c>
-      <c r="I273" t="s">
-        <v>10</v>
-      </c>
-      <c r="J273">
-        <v>66</v>
-      </c>
-      <c r="K273" t="s">
-        <v>1227</v>
       </c>
     </row>
     <row r="274" spans="1:11" x14ac:dyDescent="0.25">
@@ -14524,7 +14536,7 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C274" s="4" t="s">
         <v>1232</v>
@@ -14539,7 +14551,7 @@
         <v>1235</v>
       </c>
       <c r="G274" t="s">
-        <v>604</v>
+        <v>24</v>
       </c>
       <c r="H274">
         <v>1</v>
@@ -14548,10 +14560,10 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K274" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="275" spans="1:11" x14ac:dyDescent="0.25">
@@ -14559,7 +14571,7 @@
         <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C275" s="4" t="s">
         <v>1236</v>
@@ -14574,7 +14586,7 @@
         <v>1239</v>
       </c>
       <c r="G275" t="s">
-        <v>861</v>
+        <v>604</v>
       </c>
       <c r="H275">
         <v>1</v>
@@ -14583,10 +14595,10 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="K275" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -14594,7 +14606,7 @@
         <v>16</v>
       </c>
       <c r="B276" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C276" s="4" t="s">
         <v>1240</v>
@@ -14609,7 +14621,7 @@
         <v>1243</v>
       </c>
       <c r="G276" t="s">
-        <v>24</v>
+        <v>861</v>
       </c>
       <c r="H276">
         <v>1</v>
@@ -14618,10 +14630,10 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="K276" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -14629,7 +14641,7 @@
         <v>16</v>
       </c>
       <c r="B277" t="s">
-        <v>1222</v>
+        <v>1226</v>
       </c>
       <c r="C277" s="4" t="s">
         <v>1244</v>
@@ -14653,10 +14665,10 @@
         <v>10</v>
       </c>
       <c r="J277">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K277" t="s">
-        <v>1227</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -14664,19 +14676,19 @@
         <v>16</v>
       </c>
       <c r="B278" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C278" s="4" t="s">
         <v>1248</v>
       </c>
-      <c r="C278" s="4" t="s">
+      <c r="D278" s="4" t="s">
         <v>1249</v>
       </c>
-      <c r="D278" s="4" t="s">
+      <c r="E278" s="4" t="s">
         <v>1250</v>
       </c>
-      <c r="E278" s="4" t="s">
+      <c r="F278" s="4" t="s">
         <v>1251</v>
-      </c>
-      <c r="F278" s="4" t="s">
-        <v>1252</v>
       </c>
       <c r="G278" t="s">
         <v>24</v>
@@ -14688,10 +14700,10 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="K278" t="s">
-        <v>1253</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -14699,19 +14711,19 @@
         <v>16</v>
       </c>
       <c r="B279" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="C279" s="4" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D279" s="4" t="s">
         <v>1254</v>
       </c>
-      <c r="D279" s="4" t="s">
+      <c r="E279" s="4" t="s">
         <v>1255</v>
       </c>
-      <c r="E279" s="4" t="s">
+      <c r="F279" s="4" t="s">
         <v>1256</v>
-      </c>
-      <c r="F279" s="4" t="s">
-        <v>1257</v>
       </c>
       <c r="G279" t="s">
         <v>24</v>
@@ -14723,10 +14735,10 @@
         <v>10</v>
       </c>
       <c r="J279">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="K279" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -14734,7 +14746,7 @@
         <v>16</v>
       </c>
       <c r="B280" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="C280" s="4" t="s">
         <v>1258</v>
@@ -14758,30 +14770,30 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="K280" t="s">
-        <v>1253</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B281" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C281" s="4" t="s">
         <v>1262</v>
       </c>
-      <c r="C281" s="4" t="s">
+      <c r="D281" s="4" t="s">
         <v>1263</v>
       </c>
-      <c r="D281" s="4" t="s">
+      <c r="E281" s="4" t="s">
         <v>1264</v>
       </c>
-      <c r="E281" s="4" t="s">
+      <c r="F281" s="4" t="s">
         <v>1265</v>
-      </c>
-      <c r="F281" s="4" t="s">
-        <v>1266</v>
       </c>
       <c r="G281" t="s">
         <v>24</v>
@@ -14793,10 +14805,10 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>1902</v>
+        <v>62</v>
       </c>
       <c r="K281" t="s">
-        <v>1267</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -14804,19 +14816,19 @@
         <v>17</v>
       </c>
       <c r="B282" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C282" s="4" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D282" s="4" t="s">
         <v>1268</v>
       </c>
-      <c r="D282" s="4" t="s">
+      <c r="E282" s="4" t="s">
         <v>1269</v>
       </c>
-      <c r="E282" s="4" t="s">
+      <c r="F282" s="4" t="s">
         <v>1270</v>
-      </c>
-      <c r="F282" s="4" t="s">
-        <v>1271</v>
       </c>
       <c r="G282" t="s">
         <v>24</v>
@@ -14828,10 +14840,10 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>282</v>
+        <v>2273</v>
       </c>
       <c r="K282" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -14839,7 +14851,7 @@
         <v>17</v>
       </c>
       <c r="B283" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>1272</v>
@@ -14863,10 +14875,10 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>274</v>
+        <v>1219</v>
       </c>
       <c r="K283" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -14874,7 +14886,7 @@
         <v>17</v>
       </c>
       <c r="B284" t="s">
-        <v>1262</v>
+        <v>1266</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>1276</v>
@@ -14898,10 +14910,10 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>251</v>
+        <v>993</v>
       </c>
       <c r="K284" t="s">
-        <v>1267</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -14909,19 +14921,19 @@
         <v>17</v>
       </c>
       <c r="B285" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C285" s="4" t="s">
         <v>1280</v>
       </c>
-      <c r="C285" s="4" t="s">
+      <c r="D285" s="4" t="s">
         <v>1281</v>
       </c>
-      <c r="D285" s="4" t="s">
+      <c r="E285" s="4" t="s">
         <v>1282</v>
       </c>
-      <c r="E285" s="4" t="s">
+      <c r="F285" s="4" t="s">
         <v>1283</v>
-      </c>
-      <c r="F285" s="4" t="s">
-        <v>1284</v>
       </c>
       <c r="G285" t="s">
         <v>24</v>
@@ -14933,10 +14945,10 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>227</v>
+        <v>1152</v>
       </c>
       <c r="K285" t="s">
-        <v>1285</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -14944,19 +14956,19 @@
         <v>17</v>
       </c>
       <c r="B286" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C286" s="4" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D286" s="4" t="s">
         <v>1286</v>
       </c>
-      <c r="D286" s="4" t="s">
+      <c r="E286" s="4" t="s">
         <v>1287</v>
       </c>
-      <c r="E286" s="4" t="s">
+      <c r="F286" s="4" t="s">
         <v>1288</v>
-      </c>
-      <c r="F286" s="4" t="s">
-        <v>1289</v>
       </c>
       <c r="G286" t="s">
         <v>24</v>
@@ -14968,10 +14980,10 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>198</v>
+        <v>350</v>
       </c>
       <c r="K286" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -14979,7 +14991,7 @@
         <v>17</v>
       </c>
       <c r="B287" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>1290</v>
@@ -15003,10 +15015,10 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>201</v>
+        <v>308</v>
       </c>
       <c r="K287" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -15014,7 +15026,7 @@
         <v>17</v>
       </c>
       <c r="B288" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>1294</v>
@@ -15026,7 +15038,7 @@
         <v>1296</v>
       </c>
       <c r="F288" s="4" t="s">
-        <v>1293</v>
+        <v>1297</v>
       </c>
       <c r="G288" t="s">
         <v>24</v>
@@ -15038,10 +15050,10 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>176</v>
+        <v>286</v>
       </c>
       <c r="K288" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -15049,19 +15061,19 @@
         <v>17</v>
       </c>
       <c r="B289" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C289" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D289" s="4" t="s">
+        <v>1299</v>
+      </c>
+      <c r="E289" s="4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="F289" s="4" t="s">
         <v>1297</v>
-      </c>
-      <c r="D289" s="4" t="s">
-        <v>1298</v>
-      </c>
-      <c r="E289" s="4" t="s">
-        <v>1299</v>
-      </c>
-      <c r="F289" s="4" t="s">
-        <v>1300</v>
       </c>
       <c r="G289" t="s">
         <v>24</v>
@@ -15073,10 +15085,10 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="K289" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -15084,7 +15096,7 @@
         <v>17</v>
       </c>
       <c r="B290" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>1301</v>
@@ -15096,7 +15108,7 @@
         <v>1303</v>
       </c>
       <c r="F290" s="4" t="s">
-        <v>1300</v>
+        <v>1304</v>
       </c>
       <c r="G290" t="s">
         <v>24</v>
@@ -15108,10 +15120,10 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="K290" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -15119,22 +15131,22 @@
         <v>17</v>
       </c>
       <c r="B291" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C291" s="4" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D291" s="4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E291" s="4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F291" s="4" t="s">
         <v>1304</v>
       </c>
-      <c r="D291" s="4" t="s">
-        <v>1305</v>
-      </c>
-      <c r="E291" s="4" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F291" s="4" t="s">
-        <v>1284</v>
-      </c>
       <c r="G291" t="s">
-        <v>1307</v>
+        <v>24</v>
       </c>
       <c r="H291">
         <v>1</v>
@@ -15143,10 +15155,10 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="K291" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -15154,7 +15166,7 @@
         <v>17</v>
       </c>
       <c r="B292" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>1308</v>
@@ -15166,11 +15178,11 @@
         <v>1310</v>
       </c>
       <c r="F292" s="4" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G292" t="s">
         <v>1311</v>
       </c>
-      <c r="G292" t="s">
-        <v>24</v>
-      </c>
       <c r="H292">
         <v>1</v>
       </c>
@@ -15178,10 +15190,10 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>487</v>
+        <v>428</v>
       </c>
       <c r="K292" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -15189,7 +15201,7 @@
         <v>17</v>
       </c>
       <c r="B293" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C293" s="4" t="s">
         <v>1312</v>
@@ -15201,7 +15213,7 @@
         <v>1314</v>
       </c>
       <c r="F293" s="4" t="s">
-        <v>1284</v>
+        <v>1315</v>
       </c>
       <c r="G293" t="s">
         <v>24</v>
@@ -15213,10 +15225,10 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>273</v>
+        <v>596</v>
       </c>
       <c r="K293" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -15224,22 +15236,22 @@
         <v>17</v>
       </c>
       <c r="B294" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="E294" s="4" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="F294" s="4" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="G294" t="s">
-        <v>1318</v>
+        <v>24</v>
       </c>
       <c r="H294">
         <v>1</v>
@@ -15248,10 +15260,10 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>201</v>
+        <v>353</v>
       </c>
       <c r="K294" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -15259,7 +15271,7 @@
         <v>17</v>
       </c>
       <c r="B295" t="s">
-        <v>1280</v>
+        <v>1284</v>
       </c>
       <c r="C295" s="4" t="s">
         <v>1319</v>
@@ -15271,10 +15283,10 @@
         <v>1321</v>
       </c>
       <c r="F295" s="4" t="s">
-        <v>1284</v>
+        <v>1288</v>
       </c>
       <c r="G295" t="s">
-        <v>24</v>
+        <v>1322</v>
       </c>
       <c r="H295">
         <v>1</v>
@@ -15283,18 +15295,18 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="K295" t="s">
-        <v>1285</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B296" t="s">
-        <v>1322</v>
+        <v>1284</v>
       </c>
       <c r="C296" s="4" t="s">
         <v>1323</v>
@@ -15306,7 +15318,7 @@
         <v>1325</v>
       </c>
       <c r="F296" s="4" t="s">
-        <v>1326</v>
+        <v>1288</v>
       </c>
       <c r="G296" t="s">
         <v>24</v>
@@ -15318,10 +15330,10 @@
         <v>10</v>
       </c>
       <c r="J296">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K296" t="s">
-        <v>1327</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -15329,34 +15341,34 @@
         <v>18</v>
       </c>
       <c r="B297" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C297" s="4" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D297" s="4" t="s">
         <v>1328</v>
       </c>
-      <c r="C297" s="4" t="s">
+      <c r="E297" s="4" t="s">
         <v>1329</v>
       </c>
-      <c r="D297" s="4" t="s">
+      <c r="F297" s="4" t="s">
         <v>1330</v>
       </c>
-      <c r="E297" s="4" t="s">
+      <c r="G297" t="s">
+        <v>24</v>
+      </c>
+      <c r="H297">
+        <v>1</v>
+      </c>
+      <c r="I297" t="s">
+        <v>10</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297" t="s">
         <v>1331</v>
-      </c>
-      <c r="F297" s="4" t="s">
-        <v>1332</v>
-      </c>
-      <c r="G297" t="s">
-        <v>626</v>
-      </c>
-      <c r="H297">
-        <v>1</v>
-      </c>
-      <c r="I297" t="s">
-        <v>10</v>
-      </c>
-      <c r="J297">
-        <v>2</v>
-      </c>
-      <c r="K297" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -15364,34 +15376,34 @@
         <v>18</v>
       </c>
       <c r="B298" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="C298" s="4" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D298" s="4" t="s">
         <v>1334</v>
       </c>
-      <c r="D298" s="4" t="s">
+      <c r="E298" s="4" t="s">
         <v>1335</v>
       </c>
-      <c r="E298" s="4" t="s">
+      <c r="F298" s="4" t="s">
         <v>1336</v>
       </c>
-      <c r="F298" s="4" t="s">
+      <c r="G298" t="s">
+        <v>626</v>
+      </c>
+      <c r="H298">
+        <v>1</v>
+      </c>
+      <c r="I298" t="s">
+        <v>10</v>
+      </c>
+      <c r="J298">
+        <v>17</v>
+      </c>
+      <c r="K298" t="s">
         <v>1337</v>
-      </c>
-      <c r="G298" t="s">
-        <v>1338</v>
-      </c>
-      <c r="H298">
-        <v>1</v>
-      </c>
-      <c r="I298" t="s">
-        <v>10</v>
-      </c>
-      <c r="J298">
-        <v>37</v>
-      </c>
-      <c r="K298" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -15399,23 +15411,23 @@
         <v>18</v>
       </c>
       <c r="B299" t="s">
-        <v>1328</v>
+        <v>1332</v>
       </c>
       <c r="C299" s="4" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D299" s="4" t="s">
         <v>1339</v>
       </c>
-      <c r="D299" s="4" t="s">
+      <c r="E299" s="4" t="s">
         <v>1340</v>
       </c>
-      <c r="E299" s="4" t="s">
+      <c r="F299" s="4" t="s">
         <v>1341</v>
       </c>
-      <c r="F299" s="4" t="s">
+      <c r="G299" t="s">
         <v>1342</v>
       </c>
-      <c r="G299" t="s">
-        <v>212</v>
-      </c>
       <c r="H299">
         <v>1</v>
       </c>
@@ -15423,10 +15435,10 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="K299" t="s">
-        <v>1333</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -15434,22 +15446,22 @@
         <v>18</v>
       </c>
       <c r="B300" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C300" s="4" t="s">
         <v>1343</v>
       </c>
-      <c r="C300" s="4" t="s">
+      <c r="D300" s="4" t="s">
         <v>1344</v>
       </c>
-      <c r="D300" s="4" t="s">
+      <c r="E300" s="4" t="s">
         <v>1345</v>
       </c>
-      <c r="E300" s="4" t="s">
+      <c r="F300" s="4" t="s">
         <v>1346</v>
       </c>
-      <c r="F300" s="4" t="s">
-        <v>1347</v>
-      </c>
       <c r="G300" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="H300">
         <v>1</v>
@@ -15458,10 +15470,10 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K300" t="s">
-        <v>1348</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -15469,19 +15481,19 @@
         <v>18</v>
       </c>
       <c r="B301" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C301" s="4" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D301" s="4" t="s">
         <v>1349</v>
       </c>
-      <c r="D301" s="4" t="s">
+      <c r="E301" s="4" t="s">
         <v>1350</v>
       </c>
-      <c r="E301" s="4" t="s">
+      <c r="F301" s="4" t="s">
         <v>1351</v>
-      </c>
-      <c r="F301" s="4" t="s">
-        <v>1352</v>
       </c>
       <c r="G301" t="s">
         <v>24</v>
@@ -15493,10 +15505,10 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>2</v>
+        <v>526</v>
       </c>
       <c r="K301" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -15504,7 +15516,7 @@
         <v>18</v>
       </c>
       <c r="B302" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C302" s="4" t="s">
         <v>1353</v>
@@ -15528,10 +15540,10 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="K302" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -15539,7 +15551,7 @@
         <v>18</v>
       </c>
       <c r="B303" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C303" s="4" t="s">
         <v>1357</v>
@@ -15563,10 +15575,10 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>8</v>
+        <v>607</v>
       </c>
       <c r="K303" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -15574,7 +15586,7 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C304" s="4" t="s">
         <v>1361</v>
@@ -15598,10 +15610,10 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>8</v>
+        <v>623</v>
       </c>
       <c r="K304" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -15609,7 +15621,7 @@
         <v>18</v>
       </c>
       <c r="B305" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C305" s="4" t="s">
         <v>1365</v>
@@ -15624,7 +15636,7 @@
         <v>1368</v>
       </c>
       <c r="G305" t="s">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="H305">
         <v>1</v>
@@ -15633,10 +15645,10 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>1</v>
+        <v>748</v>
       </c>
       <c r="K305" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -15644,7 +15656,7 @@
         <v>18</v>
       </c>
       <c r="B306" t="s">
-        <v>1343</v>
+        <v>1347</v>
       </c>
       <c r="C306" s="4" t="s">
         <v>1369</v>
@@ -15659,7 +15671,7 @@
         <v>1372</v>
       </c>
       <c r="G306" t="s">
-        <v>24</v>
+        <v>194</v>
       </c>
       <c r="H306">
         <v>1</v>
@@ -15668,10 +15680,10 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="K306" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -15679,22 +15691,22 @@
         <v>18</v>
       </c>
       <c r="B307" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C307" s="4" t="s">
         <v>1373</v>
       </c>
-      <c r="C307" s="4" t="s">
+      <c r="D307" s="4" t="s">
         <v>1374</v>
       </c>
-      <c r="D307" s="4" t="s">
+      <c r="E307" s="4" t="s">
         <v>1375</v>
       </c>
-      <c r="E307" s="4" t="s">
+      <c r="F307" s="4" t="s">
         <v>1376</v>
       </c>
-      <c r="F307" s="4" t="s">
-        <v>1377</v>
-      </c>
       <c r="G307" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H307">
         <v>1</v>
@@ -15703,10 +15715,10 @@
         <v>10</v>
       </c>
       <c r="J307">
-        <v>5</v>
+        <v>936</v>
       </c>
       <c r="K307" t="s">
-        <v>1378</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
@@ -15714,22 +15726,22 @@
         <v>18</v>
       </c>
       <c r="B308" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C308" s="4" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D308" s="4" t="s">
         <v>1379</v>
       </c>
-      <c r="D308" s="4" t="s">
+      <c r="E308" s="4" t="s">
         <v>1380</v>
       </c>
-      <c r="E308" s="4" t="s">
+      <c r="F308" s="4" t="s">
         <v>1381</v>
       </c>
-      <c r="F308" s="4" t="s">
-        <v>1382</v>
-      </c>
       <c r="G308" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="H308">
         <v>1</v>
@@ -15741,7 +15753,7 @@
         <v>7</v>
       </c>
       <c r="K308" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -15749,7 +15761,7 @@
         <v>18</v>
       </c>
       <c r="B309" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C309" s="4" t="s">
         <v>1383</v>
@@ -15764,7 +15776,7 @@
         <v>1386</v>
       </c>
       <c r="G309" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="H309">
         <v>1</v>
@@ -15773,10 +15785,10 @@
         <v>10</v>
       </c>
       <c r="J309">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K309" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
@@ -15784,7 +15796,7 @@
         <v>18</v>
       </c>
       <c r="B310" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C310" s="4" t="s">
         <v>1387</v>
@@ -15808,10 +15820,10 @@
         <v>10</v>
       </c>
       <c r="J310">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K310" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
@@ -15819,7 +15831,7 @@
         <v>18</v>
       </c>
       <c r="B311" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>1391</v>
@@ -15834,7 +15846,7 @@
         <v>1394</v>
       </c>
       <c r="G311" t="s">
-        <v>866</v>
+        <v>180</v>
       </c>
       <c r="H311">
         <v>1</v>
@@ -15846,7 +15858,7 @@
         <v>1</v>
       </c>
       <c r="K311" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
@@ -15854,7 +15866,7 @@
         <v>18</v>
       </c>
       <c r="B312" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>1395</v>
@@ -15869,7 +15881,7 @@
         <v>1398</v>
       </c>
       <c r="G312" t="s">
-        <v>398</v>
+        <v>866</v>
       </c>
       <c r="H312">
         <v>1</v>
@@ -15878,10 +15890,10 @@
         <v>10</v>
       </c>
       <c r="J312">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="K312" t="s">
-        <v>1378</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
@@ -15889,22 +15901,22 @@
         <v>18</v>
       </c>
       <c r="B313" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C313" s="4" t="s">
         <v>1399</v>
       </c>
-      <c r="C313" s="4" t="s">
+      <c r="D313" s="4" t="s">
         <v>1400</v>
       </c>
-      <c r="D313" s="4" t="s">
+      <c r="E313" s="4" t="s">
         <v>1401</v>
       </c>
-      <c r="E313" s="4" t="s">
+      <c r="F313" s="4" t="s">
         <v>1402</v>
       </c>
-      <c r="F313" s="4" t="s">
-        <v>1403</v>
-      </c>
       <c r="G313" t="s">
-        <v>1404</v>
+        <v>398</v>
       </c>
       <c r="H313">
         <v>1</v>
@@ -15913,10 +15925,10 @@
         <v>10</v>
       </c>
       <c r="J313">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="K313" t="s">
-        <v>1405</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
@@ -15924,34 +15936,34 @@
         <v>18</v>
       </c>
       <c r="B314" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C314" s="4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E314" s="4" t="s">
         <v>1406</v>
       </c>
-      <c r="D314" s="4" t="s">
+      <c r="F314" s="4" t="s">
         <v>1407</v>
       </c>
-      <c r="E314" s="4" t="s">
+      <c r="G314" t="s">
         <v>1408</v>
       </c>
-      <c r="F314" s="4" t="s">
+      <c r="H314">
+        <v>1</v>
+      </c>
+      <c r="I314" t="s">
+        <v>10</v>
+      </c>
+      <c r="J314">
+        <v>55</v>
+      </c>
+      <c r="K314" t="s">
         <v>1409</v>
-      </c>
-      <c r="G314" t="s">
-        <v>424</v>
-      </c>
-      <c r="H314">
-        <v>1</v>
-      </c>
-      <c r="I314" t="s">
-        <v>10</v>
-      </c>
-      <c r="J314">
-        <v>77</v>
-      </c>
-      <c r="K314" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
@@ -15959,7 +15971,7 @@
         <v>18</v>
       </c>
       <c r="B315" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>1410</v>
@@ -15974,7 +15986,7 @@
         <v>1413</v>
       </c>
       <c r="G315" t="s">
-        <v>1414</v>
+        <v>424</v>
       </c>
       <c r="H315">
         <v>1</v>
@@ -15983,10 +15995,10 @@
         <v>10</v>
       </c>
       <c r="J315">
-        <v>30</v>
+        <v>745</v>
       </c>
       <c r="K315" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
@@ -15994,23 +16006,23 @@
         <v>18</v>
       </c>
       <c r="B316" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C316" s="4" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D316" s="4" t="s">
         <v>1415</v>
       </c>
-      <c r="D316" s="4" t="s">
+      <c r="E316" s="4" t="s">
         <v>1416</v>
       </c>
-      <c r="E316" s="4" t="s">
+      <c r="F316" s="4" t="s">
         <v>1417</v>
       </c>
-      <c r="F316" s="4" t="s">
+      <c r="G316" t="s">
         <v>1418</v>
       </c>
-      <c r="G316" t="s">
-        <v>24</v>
-      </c>
       <c r="H316">
         <v>1</v>
       </c>
@@ -16018,10 +16030,10 @@
         <v>10</v>
       </c>
       <c r="J316">
-        <v>6</v>
+        <v>882</v>
       </c>
       <c r="K316" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
@@ -16029,7 +16041,7 @@
         <v>18</v>
       </c>
       <c r="B317" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>1419</v>
@@ -16044,7 +16056,7 @@
         <v>1422</v>
       </c>
       <c r="G317" t="s">
-        <v>1423</v>
+        <v>24</v>
       </c>
       <c r="H317">
         <v>1</v>
@@ -16053,10 +16065,10 @@
         <v>10</v>
       </c>
       <c r="J317">
-        <v>151</v>
+        <v>536</v>
       </c>
       <c r="K317" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
@@ -16064,23 +16076,23 @@
         <v>18</v>
       </c>
       <c r="B318" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C318" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D318" s="4" t="s">
         <v>1424</v>
       </c>
-      <c r="D318" s="4" t="s">
+      <c r="E318" s="4" t="s">
         <v>1425</v>
       </c>
-      <c r="E318" s="4" t="s">
+      <c r="F318" s="4" t="s">
         <v>1426</v>
       </c>
-      <c r="F318" s="4" t="s">
+      <c r="G318" t="s">
         <v>1427</v>
       </c>
-      <c r="G318" t="s">
-        <v>703</v>
-      </c>
       <c r="H318">
         <v>1</v>
       </c>
@@ -16088,10 +16100,10 @@
         <v>10</v>
       </c>
       <c r="J318">
-        <v>10</v>
+        <v>1374</v>
       </c>
       <c r="K318" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
@@ -16099,7 +16111,7 @@
         <v>18</v>
       </c>
       <c r="B319" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C319" s="4" t="s">
         <v>1428</v>
@@ -16114,7 +16126,7 @@
         <v>1431</v>
       </c>
       <c r="G319" t="s">
-        <v>1432</v>
+        <v>703</v>
       </c>
       <c r="H319">
         <v>1</v>
@@ -16123,10 +16135,10 @@
         <v>10</v>
       </c>
       <c r="J319">
-        <v>36</v>
+        <v>1013</v>
       </c>
       <c r="K319" t="s">
-        <v>1405</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
@@ -16134,34 +16146,69 @@
         <v>18</v>
       </c>
       <c r="B320" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="C320" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D320" s="4" t="s">
         <v>1433</v>
       </c>
-      <c r="D320" s="4" t="s">
+      <c r="E320" s="4" t="s">
         <v>1434</v>
       </c>
-      <c r="E320" s="4" t="s">
+      <c r="F320" s="4" t="s">
         <v>1435</v>
       </c>
-      <c r="F320" s="4" t="s">
+      <c r="G320" t="s">
         <v>1436</v>
       </c>
-      <c r="G320" t="s">
+      <c r="H320">
+        <v>1</v>
+      </c>
+      <c r="I320" t="s">
+        <v>10</v>
+      </c>
+      <c r="J320">
+        <v>1134</v>
+      </c>
+      <c r="K320" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>18</v>
+      </c>
+      <c r="B321" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E321" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G321" t="s">
         <v>24</v>
       </c>
-      <c r="H320">
-        <v>1</v>
-      </c>
-      <c r="I320" t="s">
-        <v>10</v>
-      </c>
-      <c r="J320">
-        <v>9</v>
-      </c>
-      <c r="K320" t="s">
-        <v>1405</v>
+      <c r="H321">
+        <v>1</v>
+      </c>
+      <c r="I321" t="s">
+        <v>10</v>
+      </c>
+      <c r="J321">
+        <v>668</v>
+      </c>
+      <c r="K321" t="s">
+        <v>1409</v>
       </c>
     </row>
   </sheetData>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 09:48</t>
+    <t>2026-09-15 10:09</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_09_48_23.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_10_09_42.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -5880,7 +5880,7 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="s">
         <v>115</v>
@@ -6755,7 +6755,7 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="s">
         <v>256</v>
@@ -7070,7 +7070,7 @@
         <v>10</v>
       </c>
       <c r="J60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K60" t="s">
         <v>300</v>
@@ -7560,7 +7560,7 @@
         <v>10</v>
       </c>
       <c r="J74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K74" t="s">
         <v>300</v>
@@ -7770,7 +7770,7 @@
         <v>10</v>
       </c>
       <c r="J80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="s">
         <v>393</v>
@@ -8610,7 +8610,7 @@
         <v>10</v>
       </c>
       <c r="J104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="s">
         <v>443</v>
@@ -8890,7 +8890,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -9870,7 +9870,7 @@
         <v>10</v>
       </c>
       <c r="J140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="s">
         <v>656</v>
@@ -10080,7 +10080,7 @@
         <v>10</v>
       </c>
       <c r="J146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="s">
         <v>656</v>
@@ -10255,7 +10255,7 @@
         <v>10</v>
       </c>
       <c r="J151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K151" t="s">
         <v>656</v>
@@ -10885,7 +10885,7 @@
         <v>10</v>
       </c>
       <c r="J169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K169" t="s">
         <v>656</v>
@@ -11095,7 +11095,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -12040,7 +12040,7 @@
         <v>10</v>
       </c>
       <c r="J202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K202" t="s">
         <v>844</v>
@@ -12320,7 +12320,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>843</v>
+        <v>812</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12530,7 +12530,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>133</v>
+        <v>90</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12565,7 +12565,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12600,7 +12600,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>278</v>
+        <v>219</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12635,7 +12635,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>844</v>
+        <v>672</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12670,7 +12670,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1233</v>
+        <v>1036</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12705,7 +12705,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12740,7 +12740,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12775,7 +12775,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1641</v>
+        <v>1531</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12810,7 +12810,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12845,7 +12845,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12880,7 +12880,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>91</v>
+        <v>265</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12950,7 +12950,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12985,7 +12985,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>190</v>
+        <v>379</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -13020,7 +13020,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -13055,7 +13055,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="K231" t="s">
         <v>1004</v>
@@ -13090,7 +13090,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K232" t="s">
         <v>1004</v>
@@ -13125,7 +13125,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="K233" t="s">
         <v>1061</v>
@@ -13160,7 +13160,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="K234" t="s">
         <v>1061</v>
@@ -13195,7 +13195,7 @@
         <v>10</v>
       </c>
       <c r="J235">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="K235" t="s">
         <v>1061</v>
@@ -13230,7 +13230,7 @@
         <v>10</v>
       </c>
       <c r="J236">
-        <v>239</v>
+        <v>179</v>
       </c>
       <c r="K236" t="s">
         <v>1061</v>
@@ -13335,7 +13335,7 @@
         <v>10</v>
       </c>
       <c r="J239">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="K239" t="s">
         <v>1089</v>
@@ -13440,7 +13440,7 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>181</v>
+        <v>95</v>
       </c>
       <c r="K242" t="s">
         <v>1089</v>
@@ -13475,7 +13475,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="K243" t="s">
         <v>1089</v>
@@ -13510,7 +13510,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="K244" t="s">
         <v>1111</v>
@@ -13545,7 +13545,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="K245" t="s">
         <v>1089</v>
@@ -13580,7 +13580,7 @@
         <v>10</v>
       </c>
       <c r="J246">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K246" t="s">
         <v>1111</v>
@@ -13615,7 +13615,7 @@
         <v>10</v>
       </c>
       <c r="J247">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="K247" t="s">
         <v>1111</v>
@@ -13650,7 +13650,7 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K248" t="s">
         <v>1079</v>
@@ -13720,7 +13720,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="K250" t="s">
         <v>1089</v>
@@ -13755,7 +13755,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="K251" t="s">
         <v>1089</v>
@@ -13790,7 +13790,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>241</v>
+        <v>116</v>
       </c>
       <c r="K252" t="s">
         <v>1089</v>
@@ -13825,7 +13825,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="K253" t="s">
         <v>1111</v>
@@ -13860,7 +13860,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="K254" t="s">
         <v>1089</v>
@@ -13895,7 +13895,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="K255" t="s">
         <v>1089</v>
@@ -13930,7 +13930,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>172</v>
+        <v>127</v>
       </c>
       <c r="K256" t="s">
         <v>1160</v>
@@ -13965,7 +13965,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>282</v>
+        <v>133</v>
       </c>
       <c r="K257" t="s">
         <v>1160</v>
@@ -14000,7 +14000,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>232</v>
+        <v>131</v>
       </c>
       <c r="K258" t="s">
         <v>1160</v>
@@ -14035,7 +14035,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="K259" t="s">
         <v>1174</v>
@@ -14070,7 +14070,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="K260" t="s">
         <v>1174</v>
@@ -14105,7 +14105,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K261" t="s">
         <v>1174</v>
@@ -14140,7 +14140,7 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="K262" t="s">
         <v>1174</v>
@@ -14175,7 +14175,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="K263" t="s">
         <v>1174</v>
@@ -14210,7 +14210,7 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="K264" t="s">
         <v>1174</v>
@@ -14245,7 +14245,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="K265" t="s">
         <v>1174</v>
@@ -14280,7 +14280,7 @@
         <v>10</v>
       </c>
       <c r="J266">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="K266" t="s">
         <v>1174</v>
@@ -14315,7 +14315,7 @@
         <v>10</v>
       </c>
       <c r="J267">
-        <v>192</v>
+        <v>89</v>
       </c>
       <c r="K267" t="s">
         <v>1174</v>
@@ -14385,7 +14385,7 @@
         <v>10</v>
       </c>
       <c r="J269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K269" t="s">
         <v>1209</v>
@@ -14420,7 +14420,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K270" t="s">
         <v>1209</v>
@@ -14455,7 +14455,7 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K271" t="s">
         <v>1209</v>
@@ -14490,7 +14490,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="K272" t="s">
         <v>1209</v>
@@ -14525,7 +14525,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="K273" t="s">
         <v>1231</v>
@@ -14560,7 +14560,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="K274" t="s">
         <v>1231</v>
@@ -14595,7 +14595,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="K275" t="s">
         <v>1231</v>
@@ -14630,7 +14630,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="K276" t="s">
         <v>1231</v>
@@ -14665,7 +14665,7 @@
         <v>10</v>
       </c>
       <c r="J277">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="K277" t="s">
         <v>1231</v>
@@ -14700,7 +14700,7 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="K278" t="s">
         <v>1231</v>
@@ -14770,7 +14770,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K280" t="s">
         <v>1257</v>
@@ -14805,7 +14805,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="K281" t="s">
         <v>1257</v>
@@ -14840,7 +14840,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>2273</v>
+        <v>1865</v>
       </c>
       <c r="K282" t="s">
         <v>1271</v>
@@ -14875,7 +14875,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>1219</v>
+        <v>248</v>
       </c>
       <c r="K283" t="s">
         <v>1271</v>
@@ -14910,7 +14910,7 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>993</v>
+        <v>254</v>
       </c>
       <c r="K284" t="s">
         <v>1271</v>
@@ -14945,7 +14945,7 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>1152</v>
+        <v>276</v>
       </c>
       <c r="K285" t="s">
         <v>1271</v>
@@ -14980,7 +14980,7 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>350</v>
+        <v>402</v>
       </c>
       <c r="K286" t="s">
         <v>1289</v>
@@ -15015,7 +15015,7 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>308</v>
+        <v>170</v>
       </c>
       <c r="K287" t="s">
         <v>1289</v>
@@ -15050,7 +15050,7 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>286</v>
+        <v>198</v>
       </c>
       <c r="K288" t="s">
         <v>1289</v>
@@ -15085,7 +15085,7 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>219</v>
+        <v>156</v>
       </c>
       <c r="K289" t="s">
         <v>1289</v>
@@ -15120,7 +15120,7 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K290" t="s">
         <v>1289</v>
@@ -15155,7 +15155,7 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="K291" t="s">
         <v>1289</v>
@@ -15190,7 +15190,7 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>428</v>
+        <v>238</v>
       </c>
       <c r="K292" t="s">
         <v>1289</v>
@@ -15225,7 +15225,7 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>596</v>
+        <v>456</v>
       </c>
       <c r="K293" t="s">
         <v>1289</v>
@@ -15260,7 +15260,7 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>353</v>
+        <v>234</v>
       </c>
       <c r="K294" t="s">
         <v>1289</v>
@@ -15295,7 +15295,7 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="K295" t="s">
         <v>1289</v>
@@ -15330,7 +15330,7 @@
         <v>10</v>
       </c>
       <c r="J296">
-        <v>374</v>
+        <v>232</v>
       </c>
       <c r="K296" t="s">
         <v>1289</v>
@@ -15400,7 +15400,7 @@
         <v>10</v>
       </c>
       <c r="J298">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="K298" t="s">
         <v>1337</v>
@@ -15435,7 +15435,7 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="K299" t="s">
         <v>1337</v>
@@ -15470,7 +15470,7 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K300" t="s">
         <v>1337</v>
@@ -15505,7 +15505,7 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>526</v>
+        <v>11</v>
       </c>
       <c r="K301" t="s">
         <v>1352</v>
@@ -15540,7 +15540,7 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K302" t="s">
         <v>1352</v>
@@ -15575,7 +15575,7 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>607</v>
+        <v>6</v>
       </c>
       <c r="K303" t="s">
         <v>1352</v>
@@ -15610,7 +15610,7 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>623</v>
+        <v>8</v>
       </c>
       <c r="K304" t="s">
         <v>1352</v>
@@ -15645,7 +15645,7 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>748</v>
+        <v>7</v>
       </c>
       <c r="K305" t="s">
         <v>1352</v>
@@ -15680,7 +15680,7 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="K306" t="s">
         <v>1352</v>
@@ -15715,7 +15715,7 @@
         <v>10</v>
       </c>
       <c r="J307">
-        <v>936</v>
+        <v>10</v>
       </c>
       <c r="K307" t="s">
         <v>1352</v>
@@ -15750,7 +15750,7 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K308" t="s">
         <v>1382</v>
@@ -15820,7 +15820,7 @@
         <v>10</v>
       </c>
       <c r="J310">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K310" t="s">
         <v>1382</v>
@@ -15890,7 +15890,7 @@
         <v>10</v>
       </c>
       <c r="J312">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K312" t="s">
         <v>1382</v>
@@ -15925,7 +15925,7 @@
         <v>10</v>
       </c>
       <c r="J313">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="K313" t="s">
         <v>1382</v>
@@ -15960,7 +15960,7 @@
         <v>10</v>
       </c>
       <c r="J314">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="K314" t="s">
         <v>1409</v>
@@ -15995,7 +15995,7 @@
         <v>10</v>
       </c>
       <c r="J315">
-        <v>745</v>
+        <v>73</v>
       </c>
       <c r="K315" t="s">
         <v>1409</v>
@@ -16030,7 +16030,7 @@
         <v>10</v>
       </c>
       <c r="J316">
-        <v>882</v>
+        <v>36</v>
       </c>
       <c r="K316" t="s">
         <v>1409</v>
@@ -16065,7 +16065,7 @@
         <v>10</v>
       </c>
       <c r="J317">
-        <v>536</v>
+        <v>9</v>
       </c>
       <c r="K317" t="s">
         <v>1409</v>
@@ -16100,7 +16100,7 @@
         <v>10</v>
       </c>
       <c r="J318">
-        <v>1374</v>
+        <v>168</v>
       </c>
       <c r="K318" t="s">
         <v>1409</v>
@@ -16135,7 +16135,7 @@
         <v>10</v>
       </c>
       <c r="J319">
-        <v>1013</v>
+        <v>10</v>
       </c>
       <c r="K319" t="s">
         <v>1409</v>
@@ -16170,7 +16170,7 @@
         <v>10</v>
       </c>
       <c r="J320">
-        <v>1134</v>
+        <v>36</v>
       </c>
       <c r="K320" t="s">
         <v>1409</v>
@@ -16205,7 +16205,7 @@
         <v>10</v>
       </c>
       <c r="J321">
-        <v>668</v>
+        <v>9</v>
       </c>
       <c r="K321" t="s">
         <v>1409</v>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2919" uniqueCount="1441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="1457">
   <si>
     <t>검진 예약·접수 관리 프로그램 — 단위시험 목록</t>
   </si>
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 10:09</t>
+    <t>2026-09-15 10:39</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_10_09_42.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_10_39_19.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -4008,6 +4008,54 @@
   </si>
   <si>
     <t>Integration/DbFixture.cs</t>
+  </si>
+  <si>
+    <t>ExamRuleDb</t>
+  </si>
+  <si>
+    <t>검진대상의 국가검사는 나이와 성별대로 구성된다</t>
+  </si>
+  <si>
+    <t>실물 DB — 검진대상자 여섯의 국가검사 구성 개수 (DataRow 6건)</t>
+  </si>
+  <si>
+    <t>00 §7.2 NEX-01~07 이 나이와 성별로 조건부 검사를 가른다. 그 규칙이 틀리면 수검자가 받아야 할 검사를 못 받거나 받지 않아도 될 검사를 받는다 — 화면은 DB 가 준 목록을 그대로 그리므로 스스로 눈치채지 못한다. 2026-09-14 에 한 번 실측해 문서에 적어 두었을 뿐 지키는 것이 없어서, 규칙이 바뀌어도 아무도 모른다.</t>
+  </si>
+  <si>
+    <t>기본 8종 위에 조건부가 얹혀 만40 남 10 · 만56 남 11(상한) · 만54 여 9 · 만60 여 10 · 만66 여 10 · 만45 여 8 이고, 여섯 모두 검진대상여부가 1 이다.</t>
+  </si>
+  <si>
+    <t>00 §7.2</t>
+  </si>
+  <si>
+    <t>Integration/ExamRuleDbTests.cs</t>
+  </si>
+  <si>
+    <t>비대상은 사유코드로 갈리고 검사구성이 서지 않는다</t>
+  </si>
+  <si>
+    <t>실물 DB — 검진 비대상 둘의 사유코드와 검사구성 (DataRow 2건)</t>
+  </si>
+  <si>
+    <t>00 TGT-01(만20세 미만)과 TGT-04(주기 미도래)는 막는 이유가 다르다. 둘을 같은 코드로 뭉치면 창구가 「내년에 오세요」와 「나이가 안 됐습니다」를 구분해 말하지 못한다. 그리고 비대상에게 검사구성이 서면 저장까지 갈 수 있다.</t>
+  </si>
+  <si>
+    <t>만19는 400, 2025 완료자는 401 이고, 둘 다 검진대상여부가 0 이며 RS4 국가검사가 0행이다. RS5 추가검사는 7행이 오되 고를 수 있는 것이 하나도 없다 (05 §9.10).</t>
+  </si>
+  <si>
+    <t>05 §9.10</t>
+  </si>
+  <si>
+    <t>추가검사는 성별로 고를 수 있는 것이 갈린다</t>
+  </si>
+  <si>
+    <t>실물 DB — 추가검사 7종의 성별 조건 (남 D0011 · 여 D0013)</t>
+  </si>
+  <si>
+    <t>00 AEX-01~05 가 성별로 고를 수 있는 것을 가른다. 이 판정이 무너지면 남성에게 여성 전용 검사가 열리고, 그것은 화면이 아니라 저장 SP 가 411 로 막아야 하는 자리다. 개수만 재면 남녀가 우연히 같은 수일 때 규칙이 죽어도 통과하므로, 막힌 집합이 서로 다른지까지 본다.</t>
+  </si>
+  <si>
+    <t>남녀 모두 7행 중 5종을 고를 수 있고, 막힌 두 집합이 서로 같지 않다. 막힌 항목에는 사유코드가 붙어 있다 (선택가능과 사유코드가 어긋나지 않는다).</t>
   </si>
   <si>
     <t>PatientRepositoryDb</t>
@@ -4888,13 +4936,13 @@
         <v>18</v>
       </c>
       <c r="B13">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D13">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4908,13 +4956,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C14" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D14" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="E14" s="2">
         <v>0</v>
@@ -4963,7 +5011,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K321"/>
+  <dimension ref="A1:K324"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -6755,7 +6803,7 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="s">
         <v>256</v>
@@ -7070,7 +7118,7 @@
         <v>10</v>
       </c>
       <c r="J60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K60" t="s">
         <v>300</v>
@@ -8890,7 +8938,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -8995,7 +9043,7 @@
         <v>10</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115" t="s">
         <v>504</v>
@@ -9310,7 +9358,7 @@
         <v>10</v>
       </c>
       <c r="J124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="s">
         <v>558</v>
@@ -10675,7 +10723,7 @@
         <v>10</v>
       </c>
       <c r="J163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163" t="s">
         <v>656</v>
@@ -11095,7 +11143,7 @@
         <v>10</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" t="s">
         <v>656</v>
@@ -12320,7 +12368,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>812</v>
+        <v>1019</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12530,7 +12578,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12565,7 +12613,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12600,7 +12648,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>219</v>
+        <v>291</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12635,7 +12683,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>672</v>
+        <v>968</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12670,7 +12718,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1036</v>
+        <v>1333</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12705,7 +12753,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12740,7 +12788,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12775,7 +12823,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1531</v>
+        <v>1574</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12810,7 +12858,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12845,7 +12893,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12880,7 +12928,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>265</v>
+        <v>99</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -12950,7 +12998,7 @@
         <v>10</v>
       </c>
       <c r="J228">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="K228" t="s">
         <v>1004</v>
@@ -12985,7 +13033,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>379</v>
+        <v>404</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -13020,7 +13068,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -13055,7 +13103,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="K231" t="s">
         <v>1004</v>
@@ -13090,7 +13138,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="K232" t="s">
         <v>1004</v>
@@ -13125,7 +13173,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="K233" t="s">
         <v>1061</v>
@@ -13160,7 +13208,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="K234" t="s">
         <v>1061</v>
@@ -13195,7 +13243,7 @@
         <v>10</v>
       </c>
       <c r="J235">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K235" t="s">
         <v>1061</v>
@@ -13230,7 +13278,7 @@
         <v>10</v>
       </c>
       <c r="J236">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="K236" t="s">
         <v>1061</v>
@@ -13265,7 +13313,7 @@
         <v>10</v>
       </c>
       <c r="J237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K237" t="s">
         <v>1079</v>
@@ -13335,7 +13383,7 @@
         <v>10</v>
       </c>
       <c r="J239">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="K239" t="s">
         <v>1089</v>
@@ -13440,7 +13488,7 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="K242" t="s">
         <v>1089</v>
@@ -13475,7 +13523,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="K243" t="s">
         <v>1089</v>
@@ -13510,7 +13558,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>55</v>
+        <v>88</v>
       </c>
       <c r="K244" t="s">
         <v>1111</v>
@@ -13545,7 +13593,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>85</v>
+        <v>127</v>
       </c>
       <c r="K245" t="s">
         <v>1089</v>
@@ -13580,7 +13628,7 @@
         <v>10</v>
       </c>
       <c r="J246">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K246" t="s">
         <v>1111</v>
@@ -13615,7 +13663,7 @@
         <v>10</v>
       </c>
       <c r="J247">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K247" t="s">
         <v>1111</v>
@@ -13650,7 +13698,7 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K248" t="s">
         <v>1079</v>
@@ -13720,7 +13768,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>106</v>
+        <v>169</v>
       </c>
       <c r="K250" t="s">
         <v>1089</v>
@@ -13755,7 +13803,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="K251" t="s">
         <v>1089</v>
@@ -13790,7 +13838,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="K252" t="s">
         <v>1089</v>
@@ -13825,7 +13873,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="K253" t="s">
         <v>1111</v>
@@ -13860,7 +13908,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K254" t="s">
         <v>1089</v>
@@ -13895,7 +13943,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="K255" t="s">
         <v>1089</v>
@@ -13930,7 +13978,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="K256" t="s">
         <v>1160</v>
@@ -13965,7 +14013,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>133</v>
+        <v>243</v>
       </c>
       <c r="K257" t="s">
         <v>1160</v>
@@ -14000,7 +14048,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K258" t="s">
         <v>1160</v>
@@ -14035,7 +14083,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="K259" t="s">
         <v>1174</v>
@@ -14070,7 +14118,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="K260" t="s">
         <v>1174</v>
@@ -14105,7 +14153,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="K261" t="s">
         <v>1174</v>
@@ -14140,7 +14188,7 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="K262" t="s">
         <v>1174</v>
@@ -14175,7 +14223,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="K263" t="s">
         <v>1174</v>
@@ -14210,7 +14258,7 @@
         <v>10</v>
       </c>
       <c r="J264">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="K264" t="s">
         <v>1174</v>
@@ -14245,7 +14293,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>127</v>
+        <v>106</v>
       </c>
       <c r="K265" t="s">
         <v>1174</v>
@@ -14280,7 +14328,7 @@
         <v>10</v>
       </c>
       <c r="J266">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="K266" t="s">
         <v>1174</v>
@@ -14315,7 +14363,7 @@
         <v>10</v>
       </c>
       <c r="J267">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="K267" t="s">
         <v>1174</v>
@@ -14420,7 +14468,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="K270" t="s">
         <v>1209</v>
@@ -14455,7 +14503,7 @@
         <v>10</v>
       </c>
       <c r="J271">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K271" t="s">
         <v>1209</v>
@@ -14490,7 +14538,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="K272" t="s">
         <v>1209</v>
@@ -14525,7 +14573,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K273" t="s">
         <v>1231</v>
@@ -14560,7 +14608,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="K274" t="s">
         <v>1231</v>
@@ -14595,7 +14643,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="K275" t="s">
         <v>1231</v>
@@ -14630,7 +14678,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="K276" t="s">
         <v>1231</v>
@@ -14665,7 +14713,7 @@
         <v>10</v>
       </c>
       <c r="J277">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="K277" t="s">
         <v>1231</v>
@@ -14700,7 +14748,7 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="K278" t="s">
         <v>1231</v>
@@ -14770,7 +14818,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K280" t="s">
         <v>1257</v>
@@ -14805,7 +14853,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="K281" t="s">
         <v>1257</v>
@@ -14840,7 +14888,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>1865</v>
+        <v>2142</v>
       </c>
       <c r="K282" t="s">
         <v>1271</v>
@@ -14875,7 +14923,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>248</v>
+        <v>314</v>
       </c>
       <c r="K283" t="s">
         <v>1271</v>
@@ -14910,7 +14958,7 @@
         <v>10</v>
       </c>
       <c r="J284">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="K284" t="s">
         <v>1271</v>
@@ -14945,7 +14993,7 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>276</v>
+        <v>313</v>
       </c>
       <c r="K285" t="s">
         <v>1271</v>
@@ -14980,7 +15028,7 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>402</v>
+        <v>277</v>
       </c>
       <c r="K286" t="s">
         <v>1289</v>
@@ -15015,7 +15063,7 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="K287" t="s">
         <v>1289</v>
@@ -15050,7 +15098,7 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="K288" t="s">
         <v>1289</v>
@@ -15085,7 +15133,7 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="K289" t="s">
         <v>1289</v>
@@ -15120,7 +15168,7 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>207</v>
+        <v>231</v>
       </c>
       <c r="K290" t="s">
         <v>1289</v>
@@ -15155,7 +15203,7 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>181</v>
+        <v>260</v>
       </c>
       <c r="K291" t="s">
         <v>1289</v>
@@ -15190,7 +15238,7 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>238</v>
+        <v>348</v>
       </c>
       <c r="K292" t="s">
         <v>1289</v>
@@ -15225,7 +15273,7 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>456</v>
+        <v>524</v>
       </c>
       <c r="K293" t="s">
         <v>1289</v>
@@ -15260,7 +15308,7 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>234</v>
+        <v>315</v>
       </c>
       <c r="K294" t="s">
         <v>1289</v>
@@ -15295,7 +15343,7 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>242</v>
+        <v>484</v>
       </c>
       <c r="K295" t="s">
         <v>1289</v>
@@ -15330,7 +15378,7 @@
         <v>10</v>
       </c>
       <c r="J296">
-        <v>232</v>
+        <v>290</v>
       </c>
       <c r="K296" t="s">
         <v>1289</v>
@@ -15391,19 +15439,19 @@
         <v>1336</v>
       </c>
       <c r="G298" t="s">
-        <v>626</v>
+        <v>1337</v>
       </c>
       <c r="H298">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I298" t="s">
         <v>10</v>
       </c>
       <c r="J298">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K298" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -15414,31 +15462,31 @@
         <v>1332</v>
       </c>
       <c r="C299" s="4" t="s">
+        <v>1339</v>
+      </c>
+      <c r="D299" s="4" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E299" s="4" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F299" s="4" t="s">
+        <v>1342</v>
+      </c>
+      <c r="G299" t="s">
+        <v>1343</v>
+      </c>
+      <c r="H299">
+        <v>2</v>
+      </c>
+      <c r="I299" t="s">
+        <v>10</v>
+      </c>
+      <c r="J299">
+        <v>5</v>
+      </c>
+      <c r="K299" t="s">
         <v>1338</v>
-      </c>
-      <c r="D299" s="4" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E299" s="4" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F299" s="4" t="s">
-        <v>1341</v>
-      </c>
-      <c r="G299" t="s">
-        <v>1342</v>
-      </c>
-      <c r="H299">
-        <v>1</v>
-      </c>
-      <c r="I299" t="s">
-        <v>10</v>
-      </c>
-      <c r="J299">
-        <v>39</v>
-      </c>
-      <c r="K299" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -15449,19 +15497,19 @@
         <v>1332</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="E300" s="4" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F300" s="4" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="G300" t="s">
-        <v>212</v>
+        <v>24</v>
       </c>
       <c r="H300">
         <v>1</v>
@@ -15470,10 +15518,10 @@
         <v>10</v>
       </c>
       <c r="J300">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K300" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -15481,22 +15529,22 @@
         <v>18</v>
       </c>
       <c r="B301" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="E301" s="4" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="F301" s="4" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="G301" t="s">
-        <v>24</v>
+        <v>626</v>
       </c>
       <c r="H301">
         <v>1</v>
@@ -15505,10 +15553,10 @@
         <v>10</v>
       </c>
       <c r="J301">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K301" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -15516,34 +15564,34 @@
         <v>18</v>
       </c>
       <c r="B302" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C302" s="4" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D302" s="4" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E302" s="4" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F302" s="4" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G302" t="s">
+        <v>1358</v>
+      </c>
+      <c r="H302">
+        <v>1</v>
+      </c>
+      <c r="I302" t="s">
+        <v>10</v>
+      </c>
+      <c r="J302">
+        <v>37</v>
+      </c>
+      <c r="K302" t="s">
         <v>1353</v>
-      </c>
-      <c r="D302" s="4" t="s">
-        <v>1354</v>
-      </c>
-      <c r="E302" s="4" t="s">
-        <v>1355</v>
-      </c>
-      <c r="F302" s="4" t="s">
-        <v>1356</v>
-      </c>
-      <c r="G302" t="s">
-        <v>24</v>
-      </c>
-      <c r="H302">
-        <v>1</v>
-      </c>
-      <c r="I302" t="s">
-        <v>10</v>
-      </c>
-      <c r="J302">
-        <v>2</v>
-      </c>
-      <c r="K302" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -15551,22 +15599,22 @@
         <v>18</v>
       </c>
       <c r="B303" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="E303" s="4" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="F303" s="4" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="G303" t="s">
-        <v>24</v>
+        <v>212</v>
       </c>
       <c r="H303">
         <v>1</v>
@@ -15575,10 +15623,10 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K303" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -15586,19 +15634,19 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
       <c r="E304" s="4" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="F304" s="4" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="G304" t="s">
         <v>24</v>
@@ -15610,10 +15658,10 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K304" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -15621,19 +15669,19 @@
         <v>18</v>
       </c>
       <c r="B305" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>1365</v>
+        <v>1369</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>1366</v>
+        <v>1370</v>
       </c>
       <c r="E305" s="4" t="s">
-        <v>1367</v>
+        <v>1371</v>
       </c>
       <c r="F305" s="4" t="s">
-        <v>1368</v>
+        <v>1372</v>
       </c>
       <c r="G305" t="s">
         <v>24</v>
@@ -15645,10 +15693,10 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K305" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -15656,22 +15704,22 @@
         <v>18</v>
       </c>
       <c r="B306" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>1370</v>
+        <v>1374</v>
       </c>
       <c r="E306" s="4" t="s">
-        <v>1371</v>
+        <v>1375</v>
       </c>
       <c r="F306" s="4" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="G306" t="s">
-        <v>194</v>
+        <v>24</v>
       </c>
       <c r="H306">
         <v>1</v>
@@ -15680,10 +15728,10 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K306" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -15691,19 +15739,19 @@
         <v>18</v>
       </c>
       <c r="B307" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>1373</v>
+        <v>1377</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>1374</v>
+        <v>1378</v>
       </c>
       <c r="E307" s="4" t="s">
-        <v>1375</v>
+        <v>1379</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>1376</v>
+        <v>1380</v>
       </c>
       <c r="G307" t="s">
         <v>24</v>
@@ -15715,10 +15763,10 @@
         <v>10</v>
       </c>
       <c r="J307">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K307" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
@@ -15726,22 +15774,22 @@
         <v>18</v>
       </c>
       <c r="B308" t="s">
-        <v>1377</v>
+        <v>1363</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="E308" s="4" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="G308" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="H308">
         <v>1</v>
@@ -15750,10 +15798,10 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K308" t="s">
-        <v>1382</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -15761,22 +15809,22 @@
         <v>18</v>
       </c>
       <c r="B309" t="s">
-        <v>1377</v>
+        <v>1363</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="E309" s="4" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="G309" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="H309">
         <v>1</v>
@@ -15785,10 +15833,10 @@
         <v>10</v>
       </c>
       <c r="J309">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K309" t="s">
-        <v>1382</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
@@ -15796,22 +15844,22 @@
         <v>18</v>
       </c>
       <c r="B310" t="s">
-        <v>1377</v>
+        <v>1363</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="E310" s="4" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="G310" t="s">
-        <v>180</v>
+        <v>24</v>
       </c>
       <c r="H310">
         <v>1</v>
@@ -15820,10 +15868,10 @@
         <v>10</v>
       </c>
       <c r="J310">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K310" t="s">
-        <v>1382</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
@@ -15831,22 +15879,22 @@
         <v>18</v>
       </c>
       <c r="B311" t="s">
-        <v>1377</v>
+        <v>1393</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E311" s="4" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="F311" s="4" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="G311" t="s">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="H311">
         <v>1</v>
@@ -15855,10 +15903,10 @@
         <v>10</v>
       </c>
       <c r="J311">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K311" t="s">
-        <v>1382</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
@@ -15866,34 +15914,34 @@
         <v>18</v>
       </c>
       <c r="B312" t="s">
-        <v>1377</v>
+        <v>1393</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>1395</v>
+        <v>1399</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>1396</v>
+        <v>1400</v>
       </c>
       <c r="E312" s="4" t="s">
-        <v>1397</v>
+        <v>1401</v>
       </c>
       <c r="F312" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="G312" t="s">
+        <v>141</v>
+      </c>
+      <c r="H312">
+        <v>1</v>
+      </c>
+      <c r="I312" t="s">
+        <v>10</v>
+      </c>
+      <c r="J312">
+        <v>16</v>
+      </c>
+      <c r="K312" t="s">
         <v>1398</v>
-      </c>
-      <c r="G312" t="s">
-        <v>866</v>
-      </c>
-      <c r="H312">
-        <v>1</v>
-      </c>
-      <c r="I312" t="s">
-        <v>10</v>
-      </c>
-      <c r="J312">
-        <v>1</v>
-      </c>
-      <c r="K312" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
@@ -15901,22 +15949,22 @@
         <v>18</v>
       </c>
       <c r="B313" t="s">
-        <v>1377</v>
+        <v>1393</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>1399</v>
+        <v>1403</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>1400</v>
+        <v>1404</v>
       </c>
       <c r="E313" s="4" t="s">
-        <v>1401</v>
+        <v>1405</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>1402</v>
+        <v>1406</v>
       </c>
       <c r="G313" t="s">
-        <v>398</v>
+        <v>180</v>
       </c>
       <c r="H313">
         <v>1</v>
@@ -15925,10 +15973,10 @@
         <v>10</v>
       </c>
       <c r="J313">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K313" t="s">
-        <v>1382</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
@@ -15936,22 +15984,22 @@
         <v>18</v>
       </c>
       <c r="B314" t="s">
-        <v>1403</v>
+        <v>1393</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="D314" s="4" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="E314" s="4" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="G314" t="s">
-        <v>1408</v>
+        <v>180</v>
       </c>
       <c r="H314">
         <v>1</v>
@@ -15960,10 +16008,10 @@
         <v>10</v>
       </c>
       <c r="J314">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K314" t="s">
-        <v>1409</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="315" spans="1:11" x14ac:dyDescent="0.25">
@@ -15971,22 +16019,22 @@
         <v>18</v>
       </c>
       <c r="B315" t="s">
-        <v>1403</v>
+        <v>1393</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="D315" s="4" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="E315" s="4" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="G315" t="s">
-        <v>424</v>
+        <v>866</v>
       </c>
       <c r="H315">
         <v>1</v>
@@ -15995,10 +16043,10 @@
         <v>10</v>
       </c>
       <c r="J315">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="K315" t="s">
-        <v>1409</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="316" spans="1:11" x14ac:dyDescent="0.25">
@@ -16006,22 +16054,22 @@
         <v>18</v>
       </c>
       <c r="B316" t="s">
-        <v>1403</v>
+        <v>1393</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="D316" s="4" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="E316" s="4" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="G316" t="s">
-        <v>1418</v>
+        <v>398</v>
       </c>
       <c r="H316">
         <v>1</v>
@@ -16030,10 +16078,10 @@
         <v>10</v>
       </c>
       <c r="J316">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="K316" t="s">
-        <v>1409</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="317" spans="1:11" x14ac:dyDescent="0.25">
@@ -16041,22 +16089,22 @@
         <v>18</v>
       </c>
       <c r="B317" t="s">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D317" s="4" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="E317" s="4" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="F317" s="4" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="G317" t="s">
-        <v>24</v>
+        <v>1424</v>
       </c>
       <c r="H317">
         <v>1</v>
@@ -16068,7 +16116,7 @@
         <v>9</v>
       </c>
       <c r="K317" t="s">
-        <v>1409</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="318" spans="1:11" x14ac:dyDescent="0.25">
@@ -16076,34 +16124,34 @@
         <v>18</v>
       </c>
       <c r="B318" t="s">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="D318" s="4" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E318" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="G318" t="s">
+        <v>424</v>
+      </c>
+      <c r="H318">
+        <v>1</v>
+      </c>
+      <c r="I318" t="s">
+        <v>10</v>
+      </c>
+      <c r="J318">
+        <v>91</v>
+      </c>
+      <c r="K318" t="s">
         <v>1425</v>
-      </c>
-      <c r="F318" s="4" t="s">
-        <v>1426</v>
-      </c>
-      <c r="G318" t="s">
-        <v>1427</v>
-      </c>
-      <c r="H318">
-        <v>1</v>
-      </c>
-      <c r="I318" t="s">
-        <v>10</v>
-      </c>
-      <c r="J318">
-        <v>168</v>
-      </c>
-      <c r="K318" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="319" spans="1:11" x14ac:dyDescent="0.25">
@@ -16111,22 +16159,22 @@
         <v>18</v>
       </c>
       <c r="B319" t="s">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="D319" s="4" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="E319" s="4" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="F319" s="4" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="G319" t="s">
-        <v>703</v>
+        <v>1434</v>
       </c>
       <c r="H319">
         <v>1</v>
@@ -16135,10 +16183,10 @@
         <v>10</v>
       </c>
       <c r="J319">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="K319" t="s">
-        <v>1409</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="320" spans="1:11" x14ac:dyDescent="0.25">
@@ -16146,22 +16194,22 @@
         <v>18</v>
       </c>
       <c r="B320" t="s">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="D320" s="4" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="E320" s="4" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="G320" t="s">
-        <v>1436</v>
+        <v>24</v>
       </c>
       <c r="H320">
         <v>1</v>
@@ -16170,10 +16218,10 @@
         <v>10</v>
       </c>
       <c r="J320">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="K320" t="s">
-        <v>1409</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="321" spans="1:11" x14ac:dyDescent="0.25">
@@ -16181,34 +16229,139 @@
         <v>18</v>
       </c>
       <c r="B321" t="s">
-        <v>1403</v>
+        <v>1419</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="D321" s="4" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="E321" s="4" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="G321" t="s">
+        <v>1443</v>
+      </c>
+      <c r="H321">
+        <v>1</v>
+      </c>
+      <c r="I321" t="s">
+        <v>10</v>
+      </c>
+      <c r="J321">
+        <v>175</v>
+      </c>
+      <c r="K321" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>18</v>
+      </c>
+      <c r="B322" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>1445</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G322" t="s">
+        <v>703</v>
+      </c>
+      <c r="H322">
+        <v>1</v>
+      </c>
+      <c r="I322" t="s">
+        <v>10</v>
+      </c>
+      <c r="J322">
+        <v>11</v>
+      </c>
+      <c r="K322" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>18</v>
+      </c>
+      <c r="B323" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G323" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H323">
+        <v>1</v>
+      </c>
+      <c r="I323" t="s">
+        <v>10</v>
+      </c>
+      <c r="J323">
+        <v>41</v>
+      </c>
+      <c r="K323" t="s">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>18</v>
+      </c>
+      <c r="B324" t="s">
+        <v>1419</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E324" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G324" t="s">
         <v>24</v>
       </c>
-      <c r="H321">
-        <v>1</v>
-      </c>
-      <c r="I321" t="s">
-        <v>10</v>
-      </c>
-      <c r="J321">
-        <v>9</v>
-      </c>
-      <c r="K321" t="s">
-        <v>1409</v>
+      <c r="H324">
+        <v>1</v>
+      </c>
+      <c r="I324" t="s">
+        <v>10</v>
+      </c>
+      <c r="J324">
+        <v>11</v>
+      </c>
+      <c r="K324" t="s">
+        <v>1425</v>
       </c>
     </row>
   </sheetData>

--- a/docs/phase5/output/P5_단위시험_목록.xlsx
+++ b/docs/phase5/output/P5_단위시험_목록.xlsx
@@ -20,13 +20,13 @@
     <t>실행시각</t>
   </si>
   <si>
-    <t>2026-09-15 10:39</t>
+    <t>2026-09-15 11:24</t>
   </si>
   <si>
     <t>결과파일</t>
   </si>
   <si>
-    <t>JS_DESKTOP-DP7KRE4_2026-09-15_10_39_19.trx</t>
+    <t>JS_DESKTOP-DP7KRE4_2026-09-15_11_24_19.trx</t>
   </si>
   <si>
     <t>대상</t>
@@ -6803,7 +6803,7 @@
         <v>10</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="s">
         <v>256</v>
@@ -8938,7 +8938,7 @@
         <v>10</v>
       </c>
       <c r="J112">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K112" t="s">
         <v>504</v>
@@ -9043,7 +9043,7 @@
         <v>10</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K115" t="s">
         <v>504</v>
@@ -10128,7 +10128,7 @@
         <v>10</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="s">
         <v>656</v>
@@ -10303,7 +10303,7 @@
         <v>10</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" t="s">
         <v>656</v>
@@ -10723,7 +10723,7 @@
         <v>10</v>
       </c>
       <c r="J163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K163" t="s">
         <v>656</v>
@@ -12088,7 +12088,7 @@
         <v>10</v>
       </c>
       <c r="J202">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K202" t="s">
         <v>844</v>
@@ -12368,7 +12368,7 @@
         <v>10</v>
       </c>
       <c r="J210">
-        <v>1019</v>
+        <v>962</v>
       </c>
       <c r="K210" t="s">
         <v>957</v>
@@ -12578,7 +12578,7 @@
         <v>10</v>
       </c>
       <c r="J216">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="K216" t="s">
         <v>983</v>
@@ -12613,7 +12613,7 @@
         <v>10</v>
       </c>
       <c r="J217">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="K217" t="s">
         <v>983</v>
@@ -12648,7 +12648,7 @@
         <v>10</v>
       </c>
       <c r="J218">
-        <v>291</v>
+        <v>256</v>
       </c>
       <c r="K218" t="s">
         <v>994</v>
@@ -12683,7 +12683,7 @@
         <v>10</v>
       </c>
       <c r="J219">
-        <v>968</v>
+        <v>1051</v>
       </c>
       <c r="K219" t="s">
         <v>994</v>
@@ -12718,7 +12718,7 @@
         <v>10</v>
       </c>
       <c r="J220">
-        <v>1333</v>
+        <v>1026</v>
       </c>
       <c r="K220" t="s">
         <v>1004</v>
@@ -12753,7 +12753,7 @@
         <v>10</v>
       </c>
       <c r="J221">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K221" t="s">
         <v>1004</v>
@@ -12788,7 +12788,7 @@
         <v>10</v>
       </c>
       <c r="J222">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="K222" t="s">
         <v>1004</v>
@@ -12823,7 +12823,7 @@
         <v>10</v>
       </c>
       <c r="J223">
-        <v>1574</v>
+        <v>1356</v>
       </c>
       <c r="K223" t="s">
         <v>1004</v>
@@ -12858,7 +12858,7 @@
         <v>10</v>
       </c>
       <c r="J224">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="K224" t="s">
         <v>1004</v>
@@ -12893,7 +12893,7 @@
         <v>10</v>
       </c>
       <c r="J225">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="K225" t="s">
         <v>1004</v>
@@ -12928,7 +12928,7 @@
         <v>10</v>
       </c>
       <c r="J226">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="K226" t="s">
         <v>1004</v>
@@ -13033,7 +13033,7 @@
         <v>10</v>
       </c>
       <c r="J229">
-        <v>404</v>
+        <v>196</v>
       </c>
       <c r="K229" t="s">
         <v>1004</v>
@@ -13068,7 +13068,7 @@
         <v>10</v>
       </c>
       <c r="J230">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K230" t="s">
         <v>1004</v>
@@ -13103,7 +13103,7 @@
         <v>10</v>
       </c>
       <c r="J231">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="K231" t="s">
         <v>1004</v>
@@ -13138,7 +13138,7 @@
         <v>10</v>
       </c>
       <c r="J232">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="K232" t="s">
         <v>1004</v>
@@ -13173,7 +13173,7 @@
         <v>10</v>
       </c>
       <c r="J233">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K233" t="s">
         <v>1061</v>
@@ -13208,7 +13208,7 @@
         <v>10</v>
       </c>
       <c r="J234">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="K234" t="s">
         <v>1061</v>
@@ -13243,7 +13243,7 @@
         <v>10</v>
       </c>
       <c r="J235">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K235" t="s">
         <v>1061</v>
@@ -13278,7 +13278,7 @@
         <v>10</v>
       </c>
       <c r="J236">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="K236" t="s">
         <v>1061</v>
@@ -13313,7 +13313,7 @@
         <v>10</v>
       </c>
       <c r="J237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237" t="s">
         <v>1079</v>
@@ -13383,7 +13383,7 @@
         <v>10</v>
       </c>
       <c r="J239">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K239" t="s">
         <v>1089</v>
@@ -13488,7 +13488,7 @@
         <v>10</v>
       </c>
       <c r="J242">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="K242" t="s">
         <v>1089</v>
@@ -13523,7 +13523,7 @@
         <v>10</v>
       </c>
       <c r="J243">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="K243" t="s">
         <v>1089</v>
@@ -13558,7 +13558,7 @@
         <v>10</v>
       </c>
       <c r="J244">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="K244" t="s">
         <v>1111</v>
@@ -13593,7 +13593,7 @@
         <v>10</v>
       </c>
       <c r="J245">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K245" t="s">
         <v>1089</v>
@@ -13628,7 +13628,7 @@
         <v>10</v>
       </c>
       <c r="J246">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K246" t="s">
         <v>1111</v>
@@ -13663,7 +13663,7 @@
         <v>10</v>
       </c>
       <c r="J247">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K247" t="s">
         <v>1111</v>
@@ -13698,7 +13698,7 @@
         <v>10</v>
       </c>
       <c r="J248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K248" t="s">
         <v>1079</v>
@@ -13768,7 +13768,7 @@
         <v>10</v>
       </c>
       <c r="J250">
-        <v>169</v>
+        <v>92</v>
       </c>
       <c r="K250" t="s">
         <v>1089</v>
@@ -13803,7 +13803,7 @@
         <v>10</v>
       </c>
       <c r="J251">
-        <v>117</v>
+        <v>136</v>
       </c>
       <c r="K251" t="s">
         <v>1089</v>
@@ -13838,7 +13838,7 @@
         <v>10</v>
       </c>
       <c r="J252">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="K252" t="s">
         <v>1089</v>
@@ -13873,7 +13873,7 @@
         <v>10</v>
       </c>
       <c r="J253">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="K253" t="s">
         <v>1111</v>
@@ -13908,7 +13908,7 @@
         <v>10</v>
       </c>
       <c r="J254">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="K254" t="s">
         <v>1089</v>
@@ -13943,7 +13943,7 @@
         <v>10</v>
       </c>
       <c r="J255">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="K255" t="s">
         <v>1089</v>
@@ -13978,7 +13978,7 @@
         <v>10</v>
       </c>
       <c r="J256">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="K256" t="s">
         <v>1160</v>
@@ -14013,7 +14013,7 @@
         <v>10</v>
       </c>
       <c r="J257">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="K257" t="s">
         <v>1160</v>
@@ -14048,7 +14048,7 @@
         <v>10</v>
       </c>
       <c r="J258">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="K258" t="s">
         <v>1160</v>
@@ -14083,7 +14083,7 @@
         <v>10</v>
       </c>
       <c r="J259">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K259" t="s">
         <v>1174</v>
@@ -14118,7 +14118,7 @@
         <v>10</v>
       </c>
       <c r="J260">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="K260" t="s">
         <v>1174</v>
@@ -14153,7 +14153,7 @@
         <v>10</v>
       </c>
       <c r="J261">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="K261" t="s">
         <v>1174</v>
@@ -14188,7 +14188,7 @@
         <v>10</v>
       </c>
       <c r="J262">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="K262" t="s">
         <v>1174</v>
@@ -14223,7 +14223,7 @@
         <v>10</v>
       </c>
       <c r="J263">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="K263" t="s">
         <v>1174</v>
@@ -14293,7 +14293,7 @@
         <v>10</v>
       </c>
       <c r="J265">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K265" t="s">
         <v>1174</v>
@@ -14328,7 +14328,7 @@
         <v>10</v>
       </c>
       <c r="J266">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="K266" t="s">
         <v>1174</v>
@@ -14363,7 +14363,7 @@
         <v>10</v>
       </c>
       <c r="J267">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="K267" t="s">
         <v>1174</v>
@@ -14468,7 +14468,7 @@
         <v>10</v>
       </c>
       <c r="J270">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="K270" t="s">
         <v>1209</v>
@@ -14538,7 +14538,7 @@
         <v>10</v>
       </c>
       <c r="J272">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="K272" t="s">
         <v>1209</v>
@@ -14573,7 +14573,7 @@
         <v>10</v>
       </c>
       <c r="J273">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="K273" t="s">
         <v>1231</v>
@@ -14608,7 +14608,7 @@
         <v>10</v>
       </c>
       <c r="J274">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="K274" t="s">
         <v>1231</v>
@@ -14643,7 +14643,7 @@
         <v>10</v>
       </c>
       <c r="J275">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="K275" t="s">
         <v>1231</v>
@@ -14678,7 +14678,7 @@
         <v>10</v>
       </c>
       <c r="J276">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K276" t="s">
         <v>1231</v>
@@ -14713,7 +14713,7 @@
         <v>10</v>
       </c>
       <c r="J277">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K277" t="s">
         <v>1231</v>
@@ -14748,7 +14748,7 @@
         <v>10</v>
       </c>
       <c r="J278">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="K278" t="s">
         <v>1231</v>
@@ -14818,7 +14818,7 @@
         <v>10</v>
       </c>
       <c r="J280">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="K280" t="s">
         <v>1257</v>
@@ -14853,7 +14853,7 @@
         <v>10</v>
       </c>
       <c r="J281">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K281" t="s">
         <v>1257</v>
@@ -14888,7 +14888,7 @@
         <v>10</v>
       </c>
       <c r="J282">
-        <v>2142</v>
+        <v>2209</v>
       </c>
       <c r="K282" t="s">
         <v>1271</v>
@@ -14923,7 +14923,7 @@
         <v>10</v>
       </c>
       <c r="J283">
-        <v>314</v>
+        <v>261</v>
       </c>
       <c r="K283" t="s">
         <v>1271</v>
@@ -14993,7 +14993,7 @@
         <v>10</v>
       </c>
       <c r="J285">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="K285" t="s">
         <v>1271</v>
@@ -15028,7 +15028,7 @@
         <v>10</v>
       </c>
       <c r="J286">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="K286" t="s">
         <v>1289</v>
@@ -15063,7 +15063,7 @@
         <v>10</v>
       </c>
       <c r="J287">
-        <v>201</v>
+        <v>320</v>
       </c>
       <c r="K287" t="s">
         <v>1289</v>
@@ -15098,7 +15098,7 @@
         <v>10</v>
       </c>
       <c r="J288">
-        <v>240</v>
+        <v>283</v>
       </c>
       <c r="K288" t="s">
         <v>1289</v>
@@ -15133,7 +15133,7 @@
         <v>10</v>
       </c>
       <c r="J289">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="K289" t="s">
         <v>1289</v>
@@ -15168,7 +15168,7 @@
         <v>10</v>
       </c>
       <c r="J290">
-        <v>231</v>
+        <v>197</v>
       </c>
       <c r="K290" t="s">
         <v>1289</v>
@@ -15203,7 +15203,7 @@
         <v>10</v>
       </c>
       <c r="J291">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="K291" t="s">
         <v>1289</v>
@@ -15238,7 +15238,7 @@
         <v>10</v>
       </c>
       <c r="J292">
-        <v>348</v>
+        <v>309</v>
       </c>
       <c r="K292" t="s">
         <v>1289</v>
@@ -15273,7 +15273,7 @@
         <v>10</v>
       </c>
       <c r="J293">
-        <v>524</v>
+        <v>586</v>
       </c>
       <c r="K293" t="s">
         <v>1289</v>
@@ -15308,7 +15308,7 @@
         <v>10</v>
       </c>
       <c r="J294">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="K294" t="s">
         <v>1289</v>
@@ -15343,7 +15343,7 @@
         <v>10</v>
       </c>
       <c r="J295">
-        <v>484</v>
+        <v>244</v>
       </c>
       <c r="K295" t="s">
         <v>1289</v>
@@ -15378,7 +15378,7 @@
         <v>10</v>
       </c>
       <c r="J296">
-        <v>290</v>
+        <v>393</v>
       </c>
       <c r="K296" t="s">
         <v>1289</v>
@@ -15448,7 +15448,7 @@
         <v>10</v>
       </c>
       <c r="J298">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="K298" t="s">
         <v>1338</v>
@@ -15483,7 +15483,7 @@
         <v>10</v>
       </c>
       <c r="J299">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="K299" t="s">
         <v>1338</v>
@@ -15588,7 +15588,7 @@
         <v>10</v>
       </c>
       <c r="J302">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="K302" t="s">
         <v>1353</v>
@@ -15623,7 +15623,7 @@
         <v>10</v>
       </c>
       <c r="J303">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K303" t="s">
         <v>1353</v>
@@ -15658,7 +15658,7 @@
         <v>10</v>
       </c>
       <c r="J304">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K304" t="s">
         <v>1368</v>
@@ -15693,7 +15693,7 @@
         <v>10</v>
       </c>
       <c r="J305">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K305" t="s">
         <v>1368</v>
@@ -15728,7 +15728,7 @@
         <v>10</v>
       </c>
       <c r="J306">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K306" t="s">
         <v>1368</v>
@@ -15763,7 +15763,7 @@
         <v>10</v>
       </c>
       <c r="J307">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K307" t="s">
         <v>1368</v>
@@ -15798,7 +15798,7 @@
         <v>10</v>
       </c>
       <c r="J308">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K308" t="s">
         <v>1368</v>
@@ -15903,7 +15903,7 @@
         <v>10</v>
       </c>
       <c r="J311">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K311" t="s">
         <v>1398</v>
@@ -15938,7 +15938,7 @@
         <v>10</v>
       </c>
       <c r="J312">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K312" t="s">
         <v>1398</v>
@@ -16113,7 +16113,7 @@
         <v>10</v>
       </c>
       <c r="J317">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K317" t="s">
         <v>1425</v>
@@ -16148,7 +16148,7 @@
         <v>10</v>
       </c>
       <c r="J318">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K318" t="s">
         <v>1425</v>
@@ -16183,7 +16183,7 @@
         <v>10</v>
       </c>
       <c r="J319">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K319" t="s">
         <v>1425</v>
@@ -16218,7 +16218,7 @@
         <v>10</v>
       </c>
       <c r="J320">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K320" t="s">
         <v>1425</v>
@@ -16253,7 +16253,7 @@
         <v>10</v>
       </c>
       <c r="J321">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="K321" t="s">
         <v>1425</v>
@@ -16288,7 +16288,7 @@
         <v>10</v>
       </c>
       <c r="J322">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K322" t="s">
         <v>1425</v>
@@ -16323,7 +16323,7 @@
         <v>10</v>
       </c>
       <c r="J323">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K323" t="s">
         <v>1425</v>
@@ -16358,7 +16358,7 @@
         <v>10</v>
       </c>
       <c r="J324">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K324" t="s">
         <v>1425</v>
